--- a/release/fast_retailing/FastRetailing_Answer_Key.xlsx
+++ b/release/fast_retailing/FastRetailing_Answer_Key.xlsx
@@ -1565,340 +1565,390 @@
     </comment>
     <comment ref="B82" authorId="0" shapeId="0">
       <text>
-        <t>Presented as −reported cash repayments of lease liabilities. Not total lease cost, ROU amortization, or liability movement.</t>
+        <t>Reported operating cash flow minus PP&amp;E capex. Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
       </text>
     </comment>
     <comment ref="C82" authorId="0" shapeId="0">
       <text>
-        <t>Presented as −reported cash repayments of lease liabilities. Not total lease cost, ROU amortization, or liability movement.</t>
+        <t>Reported operating cash flow minus PP&amp;E capex. Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
       </text>
     </comment>
     <comment ref="D82" authorId="0" shapeId="0">
       <text>
-        <t>Presented as −reported cash repayments of lease liabilities. Not total lease cost, ROU amortization, or liability movement.</t>
+        <t>Reported operating cash flow minus PP&amp;E capex. Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
       </text>
     </comment>
     <comment ref="E82" authorId="0" shapeId="0">
       <text>
-        <t>Presented as −reported cash repayments of lease liabilities. Not total lease cost, ROU amortization, or liability movement.</t>
+        <t>Reported operating cash flow minus PP&amp;E capex. Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
       </text>
     </comment>
     <comment ref="F82" authorId="0" shapeId="0">
       <text>
-        <t>Presented as −reported cash repayments of lease liabilities. Not total lease cost, ROU amortization, or liability movement.</t>
+        <t>Reported operating cash flow minus PP&amp;E capex. Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
       </text>
     </comment>
     <comment ref="B83" authorId="0" shapeId="0">
       <text>
-        <t>Presented lease repayments divided by same-period Revenue. Cash intensity only — not liability stock or ROU amortization.</t>
+        <t>Operating cash after PP&amp;E capex divided by same-period Revenue. Excludes other investing flows; not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
       </text>
     </comment>
     <comment ref="C83" authorId="0" shapeId="0">
       <text>
-        <t>Presented lease repayments divided by same-period Revenue. Cash intensity only — not liability stock or ROU amortization.</t>
+        <t>Operating cash after PP&amp;E capex divided by same-period Revenue. Excludes other investing flows; not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
       </text>
     </comment>
     <comment ref="D83" authorId="0" shapeId="0">
       <text>
-        <t>Presented lease repayments divided by same-period Revenue. Cash intensity only — not liability stock or ROU amortization.</t>
+        <t>Operating cash after PP&amp;E capex divided by same-period Revenue. Excludes other investing flows; not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
       </text>
     </comment>
     <comment ref="E83" authorId="0" shapeId="0">
       <text>
-        <t>Presented lease repayments divided by same-period Revenue. Cash intensity only — not liability stock or ROU amortization.</t>
+        <t>Operating cash after PP&amp;E capex divided by same-period Revenue. Excludes other investing flows; not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
       </text>
     </comment>
     <comment ref="F83" authorId="0" shapeId="0">
       <text>
-        <t>Presented lease repayments divided by same-period Revenue. Cash intensity only — not liability stock or ROU amortization.</t>
+        <t>Operating cash after PP&amp;E capex divided by same-period Revenue. Excludes other investing flows; not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
+      </text>
+    </comment>
+    <comment ref="B87" authorId="0" shapeId="0">
+      <text>
+        <t>Presented as −reported cash repayments of lease liabilities. Not total lease cost, ROU amortization, or liability movement.</t>
       </text>
     </comment>
     <comment ref="C87" authorId="0" shapeId="0">
       <text>
-        <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
+        <t>Presented as −reported cash repayments of lease liabilities. Not total lease cost, ROU amortization, or liability movement.</t>
       </text>
     </comment>
     <comment ref="D87" authorId="0" shapeId="0">
       <text>
-        <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
+        <t>Presented as −reported cash repayments of lease liabilities. Not total lease cost, ROU amortization, or liability movement.</t>
       </text>
     </comment>
     <comment ref="E87" authorId="0" shapeId="0">
       <text>
-        <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
+        <t>Presented as −reported cash repayments of lease liabilities. Not total lease cost, ROU amortization, or liability movement.</t>
       </text>
     </comment>
     <comment ref="F87" authorId="0" shapeId="0">
       <text>
-        <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
+        <t>Presented as −reported cash repayments of lease liabilities. Not total lease cost, ROU amortization, or liability movement.</t>
+      </text>
+    </comment>
+    <comment ref="B88" authorId="0" shapeId="0">
+      <text>
+        <t>Presented lease repayments divided by same-period Revenue. Cash intensity only — not liability stock or ROU amortization.</t>
       </text>
     </comment>
     <comment ref="C88" authorId="0" shapeId="0">
       <text>
-        <t>Percentage change in reported goodwill.</t>
+        <t>Presented lease repayments divided by same-period Revenue. Cash intensity only — not liability stock or ROU amortization.</t>
       </text>
     </comment>
     <comment ref="D88" authorId="0" shapeId="0">
       <text>
-        <t>Percentage change in reported goodwill.</t>
+        <t>Presented lease repayments divided by same-period Revenue. Cash intensity only — not liability stock or ROU amortization.</t>
       </text>
     </comment>
     <comment ref="E88" authorId="0" shapeId="0">
       <text>
-        <t>Percentage change in reported goodwill.</t>
+        <t>Presented lease repayments divided by same-period Revenue. Cash intensity only — not liability stock or ROU amortization.</t>
       </text>
     </comment>
     <comment ref="F88" authorId="0" shapeId="0">
       <text>
+        <t>Presented lease repayments divided by same-period Revenue. Cash intensity only — not liability stock or ROU amortization.</t>
+      </text>
+    </comment>
+    <comment ref="C92" authorId="0" shapeId="0">
+      <text>
+        <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
+      </text>
+    </comment>
+    <comment ref="D92" authorId="0" shapeId="0">
+      <text>
+        <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
+      </text>
+    </comment>
+    <comment ref="E92" authorId="0" shapeId="0">
+      <text>
+        <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
+      </text>
+    </comment>
+    <comment ref="F92" authorId="0" shapeId="0">
+      <text>
+        <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
+      </text>
+    </comment>
+    <comment ref="C93" authorId="0" shapeId="0">
+      <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="C89" authorId="0" shapeId="0">
+    <comment ref="D93" authorId="0" shapeId="0">
+      <text>
+        <t>Percentage change in reported goodwill.</t>
+      </text>
+    </comment>
+    <comment ref="E93" authorId="0" shapeId="0">
+      <text>
+        <t>Percentage change in reported goodwill.</t>
+      </text>
+    </comment>
+    <comment ref="F93" authorId="0" shapeId="0">
+      <text>
+        <t>Percentage change in reported goodwill.</t>
+      </text>
+    </comment>
+    <comment ref="C94" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="D89" authorId="0" shapeId="0">
+    <comment ref="D94" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="E89" authorId="0" shapeId="0">
+    <comment ref="E94" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="F89" authorId="0" shapeId="0">
+    <comment ref="F94" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="C90" authorId="0" shapeId="0">
+    <comment ref="C95" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D90" authorId="0" shapeId="0">
+    <comment ref="D95" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E90" authorId="0" shapeId="0">
+    <comment ref="E95" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="F90" authorId="0" shapeId="0">
+    <comment ref="F95" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C92" authorId="0" shapeId="0">
+    <comment ref="C97" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D92" authorId="0" shapeId="0">
+    <comment ref="D97" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E92" authorId="0" shapeId="0">
+    <comment ref="E97" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="F92" authorId="0" shapeId="0">
+    <comment ref="F97" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C93" authorId="0" shapeId="0">
+    <comment ref="C98" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D93" authorId="0" shapeId="0">
+    <comment ref="D98" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E93" authorId="0" shapeId="0">
+    <comment ref="E98" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="F93" authorId="0" shapeId="0">
+    <comment ref="F98" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C94" authorId="0" shapeId="0">
+    <comment ref="C99" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D94" authorId="0" shapeId="0">
+    <comment ref="D99" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E94" authorId="0" shapeId="0">
+    <comment ref="E99" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="F94" authorId="0" shapeId="0">
+    <comment ref="F99" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C95" authorId="0" shapeId="0">
+    <comment ref="C100" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D95" authorId="0" shapeId="0">
+    <comment ref="D100" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E95" authorId="0" shapeId="0">
+    <comment ref="E100" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="F95" authorId="0" shapeId="0">
+    <comment ref="F100" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C97" authorId="0" shapeId="0">
+    <comment ref="C102" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="D97" authorId="0" shapeId="0">
+    <comment ref="D102" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="E97" authorId="0" shapeId="0">
+    <comment ref="E102" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="F97" authorId="0" shapeId="0">
+    <comment ref="F102" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="C98" authorId="0" shapeId="0">
+    <comment ref="C103" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="D98" authorId="0" shapeId="0">
+    <comment ref="D103" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="E98" authorId="0" shapeId="0">
+    <comment ref="E103" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="F98" authorId="0" shapeId="0">
+    <comment ref="F103" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="C99" authorId="0" shapeId="0">
+    <comment ref="C104" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="D99" authorId="0" shapeId="0">
+    <comment ref="D104" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="E99" authorId="0" shapeId="0">
+    <comment ref="E104" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="F99" authorId="0" shapeId="0">
+    <comment ref="F104" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="C100" authorId="0" shapeId="0">
+    <comment ref="C105" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="D100" authorId="0" shapeId="0">
+    <comment ref="D105" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="E100" authorId="0" shapeId="0">
+    <comment ref="E105" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="F100" authorId="0" shapeId="0">
+    <comment ref="F105" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="B102" authorId="0" shapeId="0">
+    <comment ref="B107" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="C102" authorId="0" shapeId="0">
+    <comment ref="C107" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="D102" authorId="0" shapeId="0">
+    <comment ref="D107" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="E102" authorId="0" shapeId="0">
+    <comment ref="E107" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="F102" authorId="0" shapeId="0">
+    <comment ref="F107" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="B103" authorId="0" shapeId="0">
+    <comment ref="B108" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="C103" authorId="0" shapeId="0">
+    <comment ref="C108" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="D103" authorId="0" shapeId="0">
+    <comment ref="D108" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="E103" authorId="0" shapeId="0">
+    <comment ref="E108" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="F103" authorId="0" shapeId="0">
+    <comment ref="F108" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
@@ -3001,7 +3051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5750,7 +5800,7 @@
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>C87:F87</t>
+          <t>C92:F92</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
@@ -5780,7 +5830,7 @@
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>C88:F88</t>
+          <t>C93:F93</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -5810,7 +5860,7 @@
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>C89:F89</t>
+          <t>C94:F94</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
@@ -5840,7 +5890,7 @@
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>C90:F90</t>
+          <t>C95:F95</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
@@ -5870,7 +5920,7 @@
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>C92:F92</t>
+          <t>C97:F97</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
@@ -5900,7 +5950,7 @@
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>C93:F93</t>
+          <t>C98:F98</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
@@ -5930,7 +5980,7 @@
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>C94:F94</t>
+          <t>C99:F99</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
@@ -5960,7 +6010,7 @@
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>C95:F95</t>
+          <t>C100:F100</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -5990,7 +6040,7 @@
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>C97:F97</t>
+          <t>C102:F102</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
@@ -6020,7 +6070,7 @@
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>C98:F98</t>
+          <t>C103:F103</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -6050,7 +6100,7 @@
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>C99:F99</t>
+          <t>C104:F104</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
@@ -6080,7 +6130,7 @@
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>C100:F100</t>
+          <t>C105:F105</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
@@ -6110,7 +6160,7 @@
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>B102:F102</t>
+          <t>B107:F107</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
@@ -6140,7 +6190,7 @@
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>B103:F103</t>
+          <t>B108:F108</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -6470,7 +6520,7 @@
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>B82:F82</t>
+          <t>B87:F87</t>
         </is>
       </c>
       <c r="F118" s="11" t="inlineStr">
@@ -6500,12 +6550,72 @@
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
+          <t>B88:F88</t>
+        </is>
+      </c>
+      <c r="F119" s="11" t="inlineStr">
+        <is>
+          <t>lease_repayments, revenue_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="11" t="n">
+        <v>124</v>
+      </c>
+      <c r="B120" s="11" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex</t>
+        </is>
+      </c>
+      <c r="C120" s="11" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D120" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E120" s="11" t="inlineStr">
+        <is>
+          <t>B82:F82</t>
+        </is>
+      </c>
+      <c r="F120" s="11" t="inlineStr">
+        <is>
+          <t>ppe_capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="11" t="n">
+        <v>125</v>
+      </c>
+      <c r="B121" s="11" t="inlineStr">
+        <is>
+          <t>Operating cash after PP&amp;E capex / Revenue</t>
+        </is>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D121" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E121" s="11" t="inlineStr">
+        <is>
           <t>B83:F83</t>
         </is>
       </c>
-      <c r="F119" s="11" t="inlineStr">
-        <is>
-          <t>lease_repayments, revenue_link</t>
+      <c r="F121" s="11" t="inlineStr">
+        <is>
+          <t>cash_after_ppe_capex, revenue_link</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S492"/>
+  <dimension ref="A1:S502"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37834,11 +37944,11 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>C87</t>
+          <t>C92</t>
         </is>
       </c>
       <c r="I382">
-        <f>C86-B86</f>
+        <f>C91-B91</f>
         <v/>
       </c>
       <c r="J382" t="n">
@@ -37910,11 +38020,11 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>D87</t>
+          <t>D92</t>
         </is>
       </c>
       <c r="I383">
-        <f>D86-C86</f>
+        <f>D91-C91</f>
         <v/>
       </c>
       <c r="J383" t="n">
@@ -37986,11 +38096,11 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>E87</t>
+          <t>E92</t>
         </is>
       </c>
       <c r="I384">
-        <f>E86-D86</f>
+        <f>E91-D91</f>
         <v/>
       </c>
       <c r="J384" t="n">
@@ -38062,11 +38172,11 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>F87</t>
+          <t>F92</t>
         </is>
       </c>
       <c r="I385">
-        <f>F86-E86</f>
+        <f>F91-E91</f>
         <v/>
       </c>
       <c r="J385" t="n">
@@ -38138,11 +38248,11 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>C88</t>
+          <t>C93</t>
         </is>
       </c>
       <c r="I386">
-        <f>IF(B86=0,NA(),C86/B86-1)</f>
+        <f>IF(B91=0,NA(),C91/B91-1)</f>
         <v/>
       </c>
       <c r="J386" t="n">
@@ -38219,11 +38329,11 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>D88</t>
+          <t>D93</t>
         </is>
       </c>
       <c r="I387">
-        <f>IF(C86=0,NA(),D86/C86-1)</f>
+        <f>IF(C91=0,NA(),D91/C91-1)</f>
         <v/>
       </c>
       <c r="J387" t="n">
@@ -38300,11 +38410,11 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>E88</t>
+          <t>E93</t>
         </is>
       </c>
       <c r="I388">
-        <f>IF(D86=0,NA(),E86/D86-1)</f>
+        <f>IF(D91=0,NA(),E91/D91-1)</f>
         <v/>
       </c>
       <c r="J388" t="n">
@@ -38381,11 +38491,11 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>F88</t>
+          <t>F93</t>
         </is>
       </c>
       <c r="I389">
-        <f>IF(E86=0,NA(),F86/E86-1)</f>
+        <f>IF(E91=0,NA(),F91/E91-1)</f>
         <v/>
       </c>
       <c r="J389" t="n">
@@ -38462,11 +38572,11 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>C89</t>
+          <t>C94</t>
         </is>
       </c>
       <c r="I390">
-        <f>(B86+C86)/2</f>
+        <f>(B91+C91)/2</f>
         <v/>
       </c>
       <c r="J390" t="n">
@@ -38538,11 +38648,11 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>D89</t>
+          <t>D94</t>
         </is>
       </c>
       <c r="I391">
-        <f>(C86+D86)/2</f>
+        <f>(C91+D91)/2</f>
         <v/>
       </c>
       <c r="J391" t="n">
@@ -38614,11 +38724,11 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>E89</t>
+          <t>E94</t>
         </is>
       </c>
       <c r="I392">
-        <f>(D86+E86)/2</f>
+        <f>(D91+E91)/2</f>
         <v/>
       </c>
       <c r="J392" t="n">
@@ -38690,11 +38800,11 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>F89</t>
+          <t>F94</t>
         </is>
       </c>
       <c r="I393">
-        <f>(E86+F86)/2</f>
+        <f>(E91+F91)/2</f>
         <v/>
       </c>
       <c r="J393" t="n">
@@ -38766,11 +38876,11 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>C90</t>
+          <t>C95</t>
         </is>
       </c>
       <c r="I394">
-        <f>IF('Condensed Financials'!C44=0,NA(),C89/'Condensed Financials'!C44)</f>
+        <f>IF('Condensed Financials'!C44=0,NA(),C94/'Condensed Financials'!C44)</f>
         <v/>
       </c>
       <c r="J394" t="n">
@@ -38847,11 +38957,11 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>D90</t>
+          <t>D95</t>
         </is>
       </c>
       <c r="I395">
-        <f>IF('Condensed Financials'!D44=0,NA(),D89/'Condensed Financials'!D44)</f>
+        <f>IF('Condensed Financials'!D44=0,NA(),D94/'Condensed Financials'!D44)</f>
         <v/>
       </c>
       <c r="J395" t="n">
@@ -38928,11 +39038,11 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>E90</t>
+          <t>E95</t>
         </is>
       </c>
       <c r="I396">
-        <f>IF('Condensed Financials'!E44=0,NA(),E89/'Condensed Financials'!E44)</f>
+        <f>IF('Condensed Financials'!E44=0,NA(),E94/'Condensed Financials'!E44)</f>
         <v/>
       </c>
       <c r="J396" t="n">
@@ -39009,11 +39119,11 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>F90</t>
+          <t>F95</t>
         </is>
       </c>
       <c r="I397">
-        <f>IF('Condensed Financials'!F44=0,NA(),F89/'Condensed Financials'!F44)</f>
+        <f>IF('Condensed Financials'!F44=0,NA(),F94/'Condensed Financials'!F44)</f>
         <v/>
       </c>
       <c r="J397" t="n">
@@ -39090,11 +39200,11 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>C92</t>
+          <t>C97</t>
         </is>
       </c>
       <c r="I398">
-        <f>C91-B91</f>
+        <f>C96-B96</f>
         <v/>
       </c>
       <c r="J398" t="n">
@@ -39166,11 +39276,11 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>D92</t>
+          <t>D97</t>
         </is>
       </c>
       <c r="I399">
-        <f>D91-C91</f>
+        <f>D96-C96</f>
         <v/>
       </c>
       <c r="J399" t="n">
@@ -39242,11 +39352,11 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>E92</t>
+          <t>E97</t>
         </is>
       </c>
       <c r="I400">
-        <f>E91-D91</f>
+        <f>E96-D96</f>
         <v/>
       </c>
       <c r="J400" t="n">
@@ -39318,11 +39428,11 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>F92</t>
+          <t>F97</t>
         </is>
       </c>
       <c r="I401">
-        <f>F91-E91</f>
+        <f>F96-E96</f>
         <v/>
       </c>
       <c r="J401" t="n">
@@ -39394,11 +39504,11 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>C93</t>
+          <t>C98</t>
         </is>
       </c>
       <c r="I402">
-        <f>IF(B91=0,NA(),C91/B91-1)</f>
+        <f>IF(B96=0,NA(),C96/B96-1)</f>
         <v/>
       </c>
       <c r="J402" t="n">
@@ -39475,11 +39585,11 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>D93</t>
+          <t>D98</t>
         </is>
       </c>
       <c r="I403">
-        <f>IF(C91=0,NA(),D91/C91-1)</f>
+        <f>IF(C96=0,NA(),D96/C96-1)</f>
         <v/>
       </c>
       <c r="J403" t="n">
@@ -39556,11 +39666,11 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>E93</t>
+          <t>E98</t>
         </is>
       </c>
       <c r="I404">
-        <f>IF(D91=0,NA(),E91/D91-1)</f>
+        <f>IF(D96=0,NA(),E96/D96-1)</f>
         <v/>
       </c>
       <c r="J404" t="n">
@@ -39637,11 +39747,11 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>F93</t>
+          <t>F98</t>
         </is>
       </c>
       <c r="I405">
-        <f>IF(E91=0,NA(),F91/E91-1)</f>
+        <f>IF(E96=0,NA(),F96/E96-1)</f>
         <v/>
       </c>
       <c r="J405" t="n">
@@ -39718,11 +39828,11 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>C94</t>
+          <t>C99</t>
         </is>
       </c>
       <c r="I406">
-        <f>(B91+C91)/2</f>
+        <f>(B96+C96)/2</f>
         <v/>
       </c>
       <c r="J406" t="n">
@@ -39794,11 +39904,11 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>D94</t>
+          <t>D99</t>
         </is>
       </c>
       <c r="I407">
-        <f>(C91+D91)/2</f>
+        <f>(C96+D96)/2</f>
         <v/>
       </c>
       <c r="J407" t="n">
@@ -39870,11 +39980,11 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>E94</t>
+          <t>E99</t>
         </is>
       </c>
       <c r="I408">
-        <f>(D91+E91)/2</f>
+        <f>(D96+E96)/2</f>
         <v/>
       </c>
       <c r="J408" t="n">
@@ -39946,11 +40056,11 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>F94</t>
+          <t>F99</t>
         </is>
       </c>
       <c r="I409">
-        <f>(E91+F91)/2</f>
+        <f>(E96+F96)/2</f>
         <v/>
       </c>
       <c r="J409" t="n">
@@ -40022,11 +40132,11 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>C95</t>
+          <t>C100</t>
         </is>
       </c>
       <c r="I410">
-        <f>IF('Condensed Financials'!C44=0,NA(),C94/'Condensed Financials'!C44)</f>
+        <f>IF('Condensed Financials'!C44=0,NA(),C99/'Condensed Financials'!C44)</f>
         <v/>
       </c>
       <c r="J410" t="n">
@@ -40103,11 +40213,11 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>D95</t>
+          <t>D100</t>
         </is>
       </c>
       <c r="I411">
-        <f>IF('Condensed Financials'!D44=0,NA(),D94/'Condensed Financials'!D44)</f>
+        <f>IF('Condensed Financials'!D44=0,NA(),D99/'Condensed Financials'!D44)</f>
         <v/>
       </c>
       <c r="J411" t="n">
@@ -40184,11 +40294,11 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>E95</t>
+          <t>E100</t>
         </is>
       </c>
       <c r="I412">
-        <f>IF('Condensed Financials'!E44=0,NA(),E94/'Condensed Financials'!E44)</f>
+        <f>IF('Condensed Financials'!E44=0,NA(),E99/'Condensed Financials'!E44)</f>
         <v/>
       </c>
       <c r="J412" t="n">
@@ -40265,11 +40375,11 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>F95</t>
+          <t>F100</t>
         </is>
       </c>
       <c r="I413">
-        <f>IF('Condensed Financials'!F44=0,NA(),F94/'Condensed Financials'!F44)</f>
+        <f>IF('Condensed Financials'!F44=0,NA(),F99/'Condensed Financials'!F44)</f>
         <v/>
       </c>
       <c r="J413" t="n">
@@ -40346,11 +40456,11 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>C97</t>
+          <t>C102</t>
         </is>
       </c>
       <c r="I414">
-        <f>C96-B96</f>
+        <f>C101-B101</f>
         <v/>
       </c>
       <c r="J414" t="n">
@@ -40422,11 +40532,11 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>D97</t>
+          <t>D102</t>
         </is>
       </c>
       <c r="I415">
-        <f>D96-C96</f>
+        <f>D101-C101</f>
         <v/>
       </c>
       <c r="J415" t="n">
@@ -40498,11 +40608,11 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>E97</t>
+          <t>E102</t>
         </is>
       </c>
       <c r="I416">
-        <f>E96-D96</f>
+        <f>E101-D101</f>
         <v/>
       </c>
       <c r="J416" t="n">
@@ -40574,11 +40684,11 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>F97</t>
+          <t>F102</t>
         </is>
       </c>
       <c r="I417">
-        <f>F96-E96</f>
+        <f>F101-E101</f>
         <v/>
       </c>
       <c r="J417" t="n">
@@ -40650,11 +40760,11 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>C98</t>
+          <t>C103</t>
         </is>
       </c>
       <c r="I418">
-        <f>IF(B96=0,NA(),C96/B96-1)</f>
+        <f>IF(B101=0,NA(),C101/B101-1)</f>
         <v/>
       </c>
       <c r="J418" t="n">
@@ -40731,11 +40841,11 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>D98</t>
+          <t>D103</t>
         </is>
       </c>
       <c r="I419">
-        <f>IF(C96=0,NA(),D96/C96-1)</f>
+        <f>IF(C101=0,NA(),D101/C101-1)</f>
         <v/>
       </c>
       <c r="J419" t="n">
@@ -40812,11 +40922,11 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>E98</t>
+          <t>E103</t>
         </is>
       </c>
       <c r="I420">
-        <f>IF(D96=0,NA(),E96/D96-1)</f>
+        <f>IF(D101=0,NA(),E101/D101-1)</f>
         <v/>
       </c>
       <c r="J420" t="n">
@@ -40893,11 +41003,11 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>F98</t>
+          <t>F103</t>
         </is>
       </c>
       <c r="I421">
-        <f>IF(E96=0,NA(),F96/E96-1)</f>
+        <f>IF(E101=0,NA(),F101/E101-1)</f>
         <v/>
       </c>
       <c r="J421" t="n">
@@ -40974,11 +41084,11 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>C99</t>
+          <t>C104</t>
         </is>
       </c>
       <c r="I422">
-        <f>(B96+C96)/2</f>
+        <f>(B101+C101)/2</f>
         <v/>
       </c>
       <c r="J422" t="n">
@@ -41050,11 +41160,11 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>D99</t>
+          <t>D104</t>
         </is>
       </c>
       <c r="I423">
-        <f>(C96+D96)/2</f>
+        <f>(C101+D101)/2</f>
         <v/>
       </c>
       <c r="J423" t="n">
@@ -41126,11 +41236,11 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>E99</t>
+          <t>E104</t>
         </is>
       </c>
       <c r="I424">
-        <f>(D96+E96)/2</f>
+        <f>(D101+E101)/2</f>
         <v/>
       </c>
       <c r="J424" t="n">
@@ -41202,11 +41312,11 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>F99</t>
+          <t>F104</t>
         </is>
       </c>
       <c r="I425">
-        <f>(E96+F96)/2</f>
+        <f>(E101+F101)/2</f>
         <v/>
       </c>
       <c r="J425" t="n">
@@ -41278,11 +41388,11 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="I426">
-        <f>IF('Condensed Financials'!C44=0,NA(),C99/'Condensed Financials'!C44)</f>
+        <f>IF('Condensed Financials'!C44=0,NA(),C104/'Condensed Financials'!C44)</f>
         <v/>
       </c>
       <c r="J426" t="n">
@@ -41359,11 +41469,11 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>D100</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I427">
-        <f>IF('Condensed Financials'!D44=0,NA(),D99/'Condensed Financials'!D44)</f>
+        <f>IF('Condensed Financials'!D44=0,NA(),D104/'Condensed Financials'!D44)</f>
         <v/>
       </c>
       <c r="J427" t="n">
@@ -41440,11 +41550,11 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>E100</t>
+          <t>E105</t>
         </is>
       </c>
       <c r="I428">
-        <f>IF('Condensed Financials'!E44=0,NA(),E99/'Condensed Financials'!E44)</f>
+        <f>IF('Condensed Financials'!E44=0,NA(),E104/'Condensed Financials'!E44)</f>
         <v/>
       </c>
       <c r="J428" t="n">
@@ -41521,11 +41631,11 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>F100</t>
+          <t>F105</t>
         </is>
       </c>
       <c r="I429">
-        <f>IF('Condensed Financials'!F44=0,NA(),F99/'Condensed Financials'!F44)</f>
+        <f>IF('Condensed Financials'!F44=0,NA(),F104/'Condensed Financials'!F44)</f>
         <v/>
       </c>
       <c r="J429" t="n">
@@ -41602,11 +41712,11 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>B102</t>
+          <t>B107</t>
         </is>
       </c>
       <c r="I430">
-        <f>-B101</f>
+        <f>-B106</f>
         <v/>
       </c>
       <c r="J430" t="n">
@@ -41678,11 +41788,11 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>C102</t>
+          <t>C107</t>
         </is>
       </c>
       <c r="I431">
-        <f>-C101</f>
+        <f>-C106</f>
         <v/>
       </c>
       <c r="J431" t="n">
@@ -41754,11 +41864,11 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>D102</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I432">
-        <f>-D101</f>
+        <f>-D106</f>
         <v/>
       </c>
       <c r="J432" t="n">
@@ -41830,11 +41940,11 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>E102</t>
+          <t>E107</t>
         </is>
       </c>
       <c r="I433">
-        <f>-E101</f>
+        <f>-E106</f>
         <v/>
       </c>
       <c r="J433" t="n">
@@ -41906,11 +42016,11 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>F102</t>
+          <t>F107</t>
         </is>
       </c>
       <c r="I434">
-        <f>-F101</f>
+        <f>-F106</f>
         <v/>
       </c>
       <c r="J434" t="n">
@@ -41982,11 +42092,11 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>B103</t>
+          <t>B108</t>
         </is>
       </c>
       <c r="I435">
-        <f>IF('Condensed Financials'!B44=0,NA(),B102/'Condensed Financials'!B44)</f>
+        <f>IF('Condensed Financials'!B44=0,NA(),B107/'Condensed Financials'!B44)</f>
         <v/>
       </c>
       <c r="J435" t="n">
@@ -42063,11 +42173,11 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>C103</t>
+          <t>C108</t>
         </is>
       </c>
       <c r="I436">
-        <f>IF('Condensed Financials'!C44=0,NA(),C102/'Condensed Financials'!C44)</f>
+        <f>IF('Condensed Financials'!C44=0,NA(),C107/'Condensed Financials'!C44)</f>
         <v/>
       </c>
       <c r="J436" t="n">
@@ -42144,11 +42254,11 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>D103</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I437">
-        <f>IF('Condensed Financials'!D44=0,NA(),D102/'Condensed Financials'!D44)</f>
+        <f>IF('Condensed Financials'!D44=0,NA(),D107/'Condensed Financials'!D44)</f>
         <v/>
       </c>
       <c r="J437" t="n">
@@ -42225,11 +42335,11 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>E103</t>
+          <t>E108</t>
         </is>
       </c>
       <c r="I438">
-        <f>IF('Condensed Financials'!E44=0,NA(),E102/'Condensed Financials'!E44)</f>
+        <f>IF('Condensed Financials'!E44=0,NA(),E107/'Condensed Financials'!E44)</f>
         <v/>
       </c>
       <c r="J438" t="n">
@@ -42306,11 +42416,11 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>F103</t>
+          <t>F108</t>
         </is>
       </c>
       <c r="I439">
-        <f>IF('Condensed Financials'!F44=0,NA(),F102/'Condensed Financials'!F44)</f>
+        <f>IF('Condensed Financials'!F44=0,NA(),F107/'Condensed Financials'!F44)</f>
         <v/>
       </c>
       <c r="J439" t="n">
@@ -45707,7 +45817,7 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>lease_repayments__20210831</t>
+          <t>cash_after_ppe_capex__20210831</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -45715,22 +45825,22 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Lease Repayments (−reported)</t>
+          <t>Operating cash after PP&amp;E capex</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Presented as −reported cash repayments of lease liabilities. Not total lease cost, ROU amortization, or liability movement.</t>
+          <t>Reported operating cash flow minus PP&amp;E capex. Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>lease_repayment.lease_repayments.2021-08-31</t>
+          <t>capex.cash_after_ppe_capex.2021-08-31</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>lease_repayment</t>
+          <t>capex</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
@@ -45744,18 +45854,23 @@
         </is>
       </c>
       <c r="I483">
-        <f>-B81</f>
+        <f>B81-B77</f>
         <v/>
       </c>
       <c r="J483" t="n">
-        <v>148248</v>
+        <v>372468</v>
       </c>
       <c r="K483" t="n">
         <v>0.01</v>
       </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>ppe_capex__20210831</t>
+        </is>
+      </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Lease Repayments = −(reported repayments of lease liabilities).|Do not apply absolute value; keep the −reported sign convention consistently.|This is reported repayment cash only — not total lease cost, ROU amortization, or the change in lease liability.|Explicit zero reported repayments remain valid (zero repayments).</t>
+          <t>Operating cash after PP&amp;E capex = reported operating cash flow − PP&amp;E capex.|Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.|Uses the −reported PP&amp;E payment presentation already on this schedule.</t>
         </is>
       </c>
       <c r="O483" t="inlineStr">
@@ -45765,11 +45880,11 @@
       </c>
       <c r="P483" t="inlineStr">
         <is>
-          <t>lease_repayments</t>
+          <t>cash_after_ppe_capex</t>
         </is>
       </c>
       <c r="Q483" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R483" t="n">
         <v>0</v>
@@ -45783,7 +45898,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>lease_repayments__20220831</t>
+          <t>cash_after_ppe_capex__20220831</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -45791,22 +45906,22 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Lease Repayments (−reported)</t>
+          <t>Operating cash after PP&amp;E capex</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Presented as −reported cash repayments of lease liabilities. Not total lease cost, ROU amortization, or liability movement.</t>
+          <t>Reported operating cash flow minus PP&amp;E capex. Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>lease_repayment.lease_repayments.2022-08-31</t>
+          <t>capex.cash_after_ppe_capex.2022-08-31</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>lease_repayment</t>
+          <t>capex</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
@@ -45820,18 +45935,23 @@
         </is>
       </c>
       <c r="I484">
-        <f>-C81</f>
+        <f>C81-C77</f>
         <v/>
       </c>
       <c r="J484" t="n">
-        <v>136889</v>
+        <v>379546</v>
       </c>
       <c r="K484" t="n">
         <v>0.01</v>
       </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>ppe_capex__20220831</t>
+        </is>
+      </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Lease Repayments = −(reported repayments of lease liabilities).|Do not apply absolute value; keep the −reported sign convention consistently.|This is reported repayment cash only — not total lease cost, ROU amortization, or the change in lease liability.|Explicit zero reported repayments remain valid (zero repayments).</t>
+          <t>Operating cash after PP&amp;E capex = reported operating cash flow − PP&amp;E capex.|Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.|Uses the −reported PP&amp;E payment presentation already on this schedule.</t>
         </is>
       </c>
       <c r="O484" t="inlineStr">
@@ -45841,11 +45961,11 @@
       </c>
       <c r="P484" t="inlineStr">
         <is>
-          <t>lease_repayments</t>
+          <t>cash_after_ppe_capex</t>
         </is>
       </c>
       <c r="Q484" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R484" t="n">
         <v>1</v>
@@ -45859,7 +45979,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>lease_repayments__20230831</t>
+          <t>cash_after_ppe_capex__20230831</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -45867,22 +45987,22 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Lease Repayments (−reported)</t>
+          <t>Operating cash after PP&amp;E capex</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>Presented as −reported cash repayments of lease liabilities. Not total lease cost, ROU amortization, or liability movement.</t>
+          <t>Reported operating cash flow minus PP&amp;E capex. Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>lease_repayment.lease_repayments.2023-08-31</t>
+          <t>capex.cash_after_ppe_capex.2023-08-31</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>lease_repayment</t>
+          <t>capex</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
@@ -45896,18 +46016,23 @@
         </is>
       </c>
       <c r="I485">
-        <f>-D81</f>
+        <f>D81-D77</f>
         <v/>
       </c>
       <c r="J485" t="n">
-        <v>140646</v>
+        <v>401452</v>
       </c>
       <c r="K485" t="n">
         <v>0.01</v>
       </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>ppe_capex__20230831</t>
+        </is>
+      </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Lease Repayments = −(reported repayments of lease liabilities).|Do not apply absolute value; keep the −reported sign convention consistently.|This is reported repayment cash only — not total lease cost, ROU amortization, or the change in lease liability.|Explicit zero reported repayments remain valid (zero repayments).</t>
+          <t>Operating cash after PP&amp;E capex = reported operating cash flow − PP&amp;E capex.|Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.|Uses the −reported PP&amp;E payment presentation already on this schedule.</t>
         </is>
       </c>
       <c r="O485" t="inlineStr">
@@ -45917,11 +46042,11 @@
       </c>
       <c r="P485" t="inlineStr">
         <is>
-          <t>lease_repayments</t>
+          <t>cash_after_ppe_capex</t>
         </is>
       </c>
       <c r="Q485" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R485" t="n">
         <v>2</v>
@@ -45935,7 +46060,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>lease_repayments__20240831</t>
+          <t>cash_after_ppe_capex__20240831</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -45943,22 +46068,22 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Lease Repayments (−reported)</t>
+          <t>Operating cash after PP&amp;E capex</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>Presented as −reported cash repayments of lease liabilities. Not total lease cost, ROU amortization, or liability movement.</t>
+          <t>Reported operating cash flow minus PP&amp;E capex. Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>lease_repayment.lease_repayments.2024-08-31</t>
+          <t>capex.cash_after_ppe_capex.2024-08-31</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>lease_repayment</t>
+          <t>capex</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
@@ -45972,18 +46097,23 @@
         </is>
       </c>
       <c r="I486">
-        <f>-E81</f>
+        <f>E81-E77</f>
         <v/>
       </c>
       <c r="J486" t="n">
-        <v>146403</v>
+        <v>577793</v>
       </c>
       <c r="K486" t="n">
         <v>0.01</v>
       </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>ppe_capex__20240831</t>
+        </is>
+      </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Lease Repayments = −(reported repayments of lease liabilities).|Do not apply absolute value; keep the −reported sign convention consistently.|This is reported repayment cash only — not total lease cost, ROU amortization, or the change in lease liability.|Explicit zero reported repayments remain valid (zero repayments).</t>
+          <t>Operating cash after PP&amp;E capex = reported operating cash flow − PP&amp;E capex.|Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.|Uses the −reported PP&amp;E payment presentation already on this schedule.</t>
         </is>
       </c>
       <c r="O486" t="inlineStr">
@@ -45993,11 +46123,11 @@
       </c>
       <c r="P486" t="inlineStr">
         <is>
-          <t>lease_repayments</t>
+          <t>cash_after_ppe_capex</t>
         </is>
       </c>
       <c r="Q486" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R486" t="n">
         <v>3</v>
@@ -46011,7 +46141,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>lease_repayments__20250831</t>
+          <t>cash_after_ppe_capex__20250831</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -46019,22 +46149,22 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Lease Repayments (−reported)</t>
+          <t>Operating cash after PP&amp;E capex</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Presented as −reported cash repayments of lease liabilities. Not total lease cost, ROU amortization, or liability movement.</t>
+          <t>Reported operating cash flow minus PP&amp;E capex. Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>lease_repayment.lease_repayments.2025-08-31</t>
+          <t>capex.cash_after_ppe_capex.2025-08-31</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>lease_repayment</t>
+          <t>capex</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
@@ -46048,18 +46178,23 @@
         </is>
       </c>
       <c r="I487">
-        <f>-F81</f>
+        <f>F81-F77</f>
         <v/>
       </c>
       <c r="J487" t="n">
-        <v>140483</v>
+        <v>445083</v>
       </c>
       <c r="K487" t="n">
         <v>0.01</v>
       </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>ppe_capex__20250831</t>
+        </is>
+      </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Lease Repayments = −(reported repayments of lease liabilities).|Do not apply absolute value; keep the −reported sign convention consistently.|This is reported repayment cash only — not total lease cost, ROU amortization, or the change in lease liability.|Explicit zero reported repayments remain valid (zero repayments).</t>
+          <t>Operating cash after PP&amp;E capex = reported operating cash flow − PP&amp;E capex.|Excludes other investing flows and is not comprehensive free cash flow or a maintenance/growth-capex estimate.|Uses the −reported PP&amp;E payment presentation already on this schedule.</t>
         </is>
       </c>
       <c r="O487" t="inlineStr">
@@ -46069,11 +46204,11 @@
       </c>
       <c r="P487" t="inlineStr">
         <is>
-          <t>lease_repayments</t>
+          <t>cash_after_ppe_capex</t>
         </is>
       </c>
       <c r="Q487" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="R487" t="n">
         <v>4</v>
@@ -46087,7 +46222,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>lease_repayments_to_revenue__20210831</t>
+          <t>cash_after_ppe_capex_to_revenue__20210831</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -46095,22 +46230,22 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Lease Repayments / Revenue</t>
+          <t>Operating cash after PP&amp;E capex / Revenue</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>Presented lease repayments divided by same-period Revenue. Cash intensity only — not liability stock or ROU amortization.</t>
+          <t>Operating cash after PP&amp;E capex divided by same-period Revenue. Excludes other investing flows; not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>lease_repayment.lease_repayments_to_revenue.2021-08-31</t>
+          <t>capex.cash_after_ppe_capex_to_revenue.2021-08-31</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>lease_repayment</t>
+          <t>capex</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
@@ -46128,19 +46263,19 @@
         <v/>
       </c>
       <c r="J488" t="n">
-        <v>0.06950237037926069</v>
+        <v>0.1746223145703313</v>
       </c>
       <c r="K488" t="n">
         <v>0.01</v>
       </c>
       <c r="L488" t="inlineStr">
         <is>
-          <t>lease_repayments__20210831,revenue_link__20210831</t>
+          <t>cash_after_ppe_capex__20210831,revenue_link__20210831</t>
         </is>
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Lease Repayments / Revenue uses the −reported repayment presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Revenue intensity of repayment cash only — not total lease cost, ROU amortization, or liability movement.</t>
+          <t>Operating cash after PP&amp;E capex / Revenue uses CFO minus PP&amp;E capex.|A zero Revenue denominator makes the ratio undefined (#N/A).|Not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
         </is>
       </c>
       <c r="O488" t="inlineStr">
@@ -46150,11 +46285,11 @@
       </c>
       <c r="P488" t="inlineStr">
         <is>
-          <t>lease_repayments_to_revenue</t>
+          <t>cash_after_ppe_capex_to_revenue</t>
         </is>
       </c>
       <c r="Q488" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="R488" t="n">
         <v>0</v>
@@ -46168,7 +46303,7 @@
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>lease_repayments_to_revenue__20220831</t>
+          <t>cash_after_ppe_capex_to_revenue__20220831</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -46176,22 +46311,22 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Lease Repayments / Revenue</t>
+          <t>Operating cash after PP&amp;E capex / Revenue</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Presented lease repayments divided by same-period Revenue. Cash intensity only — not liability stock or ROU amortization.</t>
+          <t>Operating cash after PP&amp;E capex divided by same-period Revenue. Excludes other investing flows; not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>lease_repayment.lease_repayments_to_revenue.2022-08-31</t>
+          <t>capex.cash_after_ppe_capex_to_revenue.2022-08-31</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>lease_repayment</t>
+          <t>capex</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
@@ -46209,19 +46344,19 @@
         <v/>
       </c>
       <c r="J489" t="n">
-        <v>0.05948793675433115</v>
+        <v>0.1649395381905001</v>
       </c>
       <c r="K489" t="n">
         <v>0.01</v>
       </c>
       <c r="L489" t="inlineStr">
         <is>
-          <t>lease_repayments__20220831,revenue_link__20220831</t>
+          <t>cash_after_ppe_capex__20220831,revenue_link__20220831</t>
         </is>
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Lease Repayments / Revenue uses the −reported repayment presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Revenue intensity of repayment cash only — not total lease cost, ROU amortization, or liability movement.</t>
+          <t>Operating cash after PP&amp;E capex / Revenue uses CFO minus PP&amp;E capex.|A zero Revenue denominator makes the ratio undefined (#N/A).|Not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
         </is>
       </c>
       <c r="O489" t="inlineStr">
@@ -46231,11 +46366,11 @@
       </c>
       <c r="P489" t="inlineStr">
         <is>
-          <t>lease_repayments_to_revenue</t>
+          <t>cash_after_ppe_capex_to_revenue</t>
         </is>
       </c>
       <c r="Q489" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="R489" t="n">
         <v>1</v>
@@ -46249,7 +46384,7 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>lease_repayments_to_revenue__20230831</t>
+          <t>cash_after_ppe_capex_to_revenue__20230831</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -46257,22 +46392,22 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Lease Repayments / Revenue</t>
+          <t>Operating cash after PP&amp;E capex / Revenue</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>Presented lease repayments divided by same-period Revenue. Cash intensity only — not liability stock or ROU amortization.</t>
+          <t>Operating cash after PP&amp;E capex divided by same-period Revenue. Excludes other investing flows; not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>lease_repayment.lease_repayments_to_revenue.2023-08-31</t>
+          <t>capex.cash_after_ppe_capex_to_revenue.2023-08-31</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>lease_repayment</t>
+          <t>capex</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
@@ -46290,19 +46425,19 @@
         <v/>
       </c>
       <c r="J490" t="n">
-        <v>0.05083791875605671</v>
+        <v>0.1451088844365036</v>
       </c>
       <c r="K490" t="n">
         <v>0.01</v>
       </c>
       <c r="L490" t="inlineStr">
         <is>
-          <t>lease_repayments__20230831,revenue_link__20230831</t>
+          <t>cash_after_ppe_capex__20230831,revenue_link__20230831</t>
         </is>
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Lease Repayments / Revenue uses the −reported repayment presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Revenue intensity of repayment cash only — not total lease cost, ROU amortization, or liability movement.</t>
+          <t>Operating cash after PP&amp;E capex / Revenue uses CFO minus PP&amp;E capex.|A zero Revenue denominator makes the ratio undefined (#N/A).|Not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
         </is>
       </c>
       <c r="O490" t="inlineStr">
@@ -46312,11 +46447,11 @@
       </c>
       <c r="P490" t="inlineStr">
         <is>
-          <t>lease_repayments_to_revenue</t>
+          <t>cash_after_ppe_capex_to_revenue</t>
         </is>
       </c>
       <c r="Q490" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="R490" t="n">
         <v>2</v>
@@ -46330,7 +46465,7 @@
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>lease_repayments_to_revenue__20240831</t>
+          <t>cash_after_ppe_capex_to_revenue__20240831</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -46338,22 +46473,22 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Lease Repayments / Revenue</t>
+          <t>Operating cash after PP&amp;E capex / Revenue</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Presented lease repayments divided by same-period Revenue. Cash intensity only — not liability stock or ROU amortization.</t>
+          <t>Operating cash after PP&amp;E capex divided by same-period Revenue. Excludes other investing flows; not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>lease_repayment.lease_repayments_to_revenue.2024-08-31</t>
+          <t>capex.cash_after_ppe_capex_to_revenue.2024-08-31</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>lease_repayment</t>
+          <t>capex</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
@@ -46371,19 +46506,19 @@
         <v/>
       </c>
       <c r="J491" t="n">
-        <v>0.04716840709367377</v>
+        <v>0.1861544875438007</v>
       </c>
       <c r="K491" t="n">
         <v>0.01</v>
       </c>
       <c r="L491" t="inlineStr">
         <is>
-          <t>lease_repayments__20240831,revenue_link__20240831</t>
+          <t>cash_after_ppe_capex__20240831,revenue_link__20240831</t>
         </is>
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Lease Repayments / Revenue uses the −reported repayment presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Revenue intensity of repayment cash only — not total lease cost, ROU amortization, or liability movement.</t>
+          <t>Operating cash after PP&amp;E capex / Revenue uses CFO minus PP&amp;E capex.|A zero Revenue denominator makes the ratio undefined (#N/A).|Not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
         </is>
       </c>
       <c r="O491" t="inlineStr">
@@ -46393,11 +46528,11 @@
       </c>
       <c r="P491" t="inlineStr">
         <is>
-          <t>lease_repayments_to_revenue</t>
+          <t>cash_after_ppe_capex_to_revenue</t>
         </is>
       </c>
       <c r="Q491" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="R491" t="n">
         <v>3</v>
@@ -46411,7 +46546,7 @@
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>lease_repayments_to_revenue__20250831</t>
+          <t>cash_after_ppe_capex_to_revenue__20250831</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -46419,22 +46554,22 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Lease Repayments / Revenue</t>
+          <t>Operating cash after PP&amp;E capex / Revenue</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>Presented lease repayments divided by same-period Revenue. Cash intensity only — not liability stock or ROU amortization.</t>
+          <t>Operating cash after PP&amp;E capex divided by same-period Revenue. Excludes other investing flows; not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>lease_repayment.lease_repayments_to_revenue.2025-08-31</t>
+          <t>capex.cash_after_ppe_capex_to_revenue.2025-08-31</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>lease_repayment</t>
+          <t>capex</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
@@ -46452,19 +46587,19 @@
         <v/>
       </c>
       <c r="J492" t="n">
-        <v>0.04131198024783718</v>
+        <v>0.1308860154228491</v>
       </c>
       <c r="K492" t="n">
         <v>0.01</v>
       </c>
       <c r="L492" t="inlineStr">
         <is>
-          <t>lease_repayments__20250831,revenue_link__20250831</t>
+          <t>cash_after_ppe_capex__20250831,revenue_link__20250831</t>
         </is>
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Lease Repayments / Revenue uses the −reported repayment presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Revenue intensity of repayment cash only — not total lease cost, ROU amortization, or liability movement.</t>
+          <t>Operating cash after PP&amp;E capex / Revenue uses CFO minus PP&amp;E capex.|A zero Revenue denominator makes the ratio undefined (#N/A).|Not comprehensive free cash flow or a maintenance/growth-capex estimate.</t>
         </is>
       </c>
       <c r="O492" t="inlineStr">
@@ -46474,16 +46609,801 @@
       </c>
       <c r="P492" t="inlineStr">
         <is>
-          <t>lease_repayments_to_revenue</t>
+          <t>cash_after_ppe_capex_to_revenue</t>
         </is>
       </c>
       <c r="Q492" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="R492" t="n">
         <v>4</v>
       </c>
       <c r="S492" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>lease_repayments__20210831</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>492</v>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Lease Repayments (−reported)</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Presented as −reported cash repayments of lease liabilities. Not total lease cost, ROU amortization, or liability movement.</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>lease_repayment.lease_repayments.2021-08-31</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>lease_repayment</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>B87</t>
+        </is>
+      </c>
+      <c r="I493">
+        <f>-B86</f>
+        <v/>
+      </c>
+      <c r="J493" t="n">
+        <v>148248</v>
+      </c>
+      <c r="K493" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>Lease Repayments = −(reported repayments of lease liabilities).|Do not apply absolute value; keep the −reported sign convention consistently.|This is reported repayment cash only — not total lease cost, ROU amortization, or the change in lease liability.|Explicit zero reported repayments remain valid (zero repayments).</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>lease_repayments</t>
+        </is>
+      </c>
+      <c r="Q493" t="n">
+        <v>122</v>
+      </c>
+      <c r="R493" t="n">
+        <v>0</v>
+      </c>
+      <c r="S493" t="inlineStr">
+        <is>
+          <t>2021-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>lease_repayments__20220831</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>493</v>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Lease Repayments (−reported)</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Presented as −reported cash repayments of lease liabilities. Not total lease cost, ROU amortization, or liability movement.</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>lease_repayment.lease_repayments.2022-08-31</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>lease_repayment</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>C87</t>
+        </is>
+      </c>
+      <c r="I494">
+        <f>-C86</f>
+        <v/>
+      </c>
+      <c r="J494" t="n">
+        <v>136889</v>
+      </c>
+      <c r="K494" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>Lease Repayments = −(reported repayments of lease liabilities).|Do not apply absolute value; keep the −reported sign convention consistently.|This is reported repayment cash only — not total lease cost, ROU amortization, or the change in lease liability.|Explicit zero reported repayments remain valid (zero repayments).</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t>lease_repayments</t>
+        </is>
+      </c>
+      <c r="Q494" t="n">
+        <v>122</v>
+      </c>
+      <c r="R494" t="n">
+        <v>1</v>
+      </c>
+      <c r="S494" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>lease_repayments__20230831</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>494</v>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Lease Repayments (−reported)</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Presented as −reported cash repayments of lease liabilities. Not total lease cost, ROU amortization, or liability movement.</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>lease_repayment.lease_repayments.2023-08-31</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>lease_repayment</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>D87</t>
+        </is>
+      </c>
+      <c r="I495">
+        <f>-D86</f>
+        <v/>
+      </c>
+      <c r="J495" t="n">
+        <v>140646</v>
+      </c>
+      <c r="K495" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>Lease Repayments = −(reported repayments of lease liabilities).|Do not apply absolute value; keep the −reported sign convention consistently.|This is reported repayment cash only — not total lease cost, ROU amortization, or the change in lease liability.|Explicit zero reported repayments remain valid (zero repayments).</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>lease_repayments</t>
+        </is>
+      </c>
+      <c r="Q495" t="n">
+        <v>122</v>
+      </c>
+      <c r="R495" t="n">
+        <v>2</v>
+      </c>
+      <c r="S495" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>lease_repayments__20240831</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>495</v>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Lease Repayments (−reported)</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Presented as −reported cash repayments of lease liabilities. Not total lease cost, ROU amortization, or liability movement.</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>lease_repayment.lease_repayments.2024-08-31</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>lease_repayment</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>E87</t>
+        </is>
+      </c>
+      <c r="I496">
+        <f>-E86</f>
+        <v/>
+      </c>
+      <c r="J496" t="n">
+        <v>146403</v>
+      </c>
+      <c r="K496" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>Lease Repayments = −(reported repayments of lease liabilities).|Do not apply absolute value; keep the −reported sign convention consistently.|This is reported repayment cash only — not total lease cost, ROU amortization, or the change in lease liability.|Explicit zero reported repayments remain valid (zero repayments).</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P496" t="inlineStr">
+        <is>
+          <t>lease_repayments</t>
+        </is>
+      </c>
+      <c r="Q496" t="n">
+        <v>122</v>
+      </c>
+      <c r="R496" t="n">
+        <v>3</v>
+      </c>
+      <c r="S496" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>lease_repayments__20250831</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>496</v>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Lease Repayments (−reported)</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Presented as −reported cash repayments of lease liabilities. Not total lease cost, ROU amortization, or liability movement.</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>lease_repayment.lease_repayments.2025-08-31</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>lease_repayment</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>F87</t>
+        </is>
+      </c>
+      <c r="I497">
+        <f>-F86</f>
+        <v/>
+      </c>
+      <c r="J497" t="n">
+        <v>140483</v>
+      </c>
+      <c r="K497" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>Lease Repayments = −(reported repayments of lease liabilities).|Do not apply absolute value; keep the −reported sign convention consistently.|This is reported repayment cash only — not total lease cost, ROU amortization, or the change in lease liability.|Explicit zero reported repayments remain valid (zero repayments).</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>lease_repayments</t>
+        </is>
+      </c>
+      <c r="Q497" t="n">
+        <v>122</v>
+      </c>
+      <c r="R497" t="n">
+        <v>4</v>
+      </c>
+      <c r="S497" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>lease_repayments_to_revenue__20210831</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>497</v>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Lease Repayments / Revenue</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Presented lease repayments divided by same-period Revenue. Cash intensity only — not liability stock or ROU amortization.</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>lease_repayment.lease_repayments_to_revenue.2021-08-31</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>lease_repayment</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>B88</t>
+        </is>
+      </c>
+      <c r="I498">
+        <f>IF('Condensed Financials'!B44=0,NA(),B87/'Condensed Financials'!B44)</f>
+        <v/>
+      </c>
+      <c r="J498" t="n">
+        <v>0.06950237037926069</v>
+      </c>
+      <c r="K498" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>lease_repayments__20210831,revenue_link__20210831</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>Lease Repayments / Revenue uses the −reported repayment presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Revenue intensity of repayment cash only — not total lease cost, ROU amortization, or liability movement.</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>lease_repayments_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q498" t="n">
+        <v>123</v>
+      </c>
+      <c r="R498" t="n">
+        <v>0</v>
+      </c>
+      <c r="S498" t="inlineStr">
+        <is>
+          <t>2021-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>lease_repayments_to_revenue__20220831</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>498</v>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Lease Repayments / Revenue</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Presented lease repayments divided by same-period Revenue. Cash intensity only — not liability stock or ROU amortization.</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>lease_repayment.lease_repayments_to_revenue.2022-08-31</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>lease_repayment</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>C88</t>
+        </is>
+      </c>
+      <c r="I499">
+        <f>IF('Condensed Financials'!C44=0,NA(),C87/'Condensed Financials'!C44)</f>
+        <v/>
+      </c>
+      <c r="J499" t="n">
+        <v>0.05948793675433115</v>
+      </c>
+      <c r="K499" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>lease_repayments__20220831,revenue_link__20220831</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>Lease Repayments / Revenue uses the −reported repayment presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Revenue intensity of repayment cash only — not total lease cost, ROU amortization, or liability movement.</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>lease_repayments_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q499" t="n">
+        <v>123</v>
+      </c>
+      <c r="R499" t="n">
+        <v>1</v>
+      </c>
+      <c r="S499" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>lease_repayments_to_revenue__20230831</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>499</v>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Lease Repayments / Revenue</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Presented lease repayments divided by same-period Revenue. Cash intensity only — not liability stock or ROU amortization.</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>lease_repayment.lease_repayments_to_revenue.2023-08-31</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>lease_repayment</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>D88</t>
+        </is>
+      </c>
+      <c r="I500">
+        <f>IF('Condensed Financials'!D44=0,NA(),D87/'Condensed Financials'!D44)</f>
+        <v/>
+      </c>
+      <c r="J500" t="n">
+        <v>0.05083791875605671</v>
+      </c>
+      <c r="K500" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>lease_repayments__20230831,revenue_link__20230831</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>Lease Repayments / Revenue uses the −reported repayment presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Revenue intensity of repayment cash only — not total lease cost, ROU amortization, or liability movement.</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>lease_repayments_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q500" t="n">
+        <v>123</v>
+      </c>
+      <c r="R500" t="n">
+        <v>2</v>
+      </c>
+      <c r="S500" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>lease_repayments_to_revenue__20240831</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>500</v>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Lease Repayments / Revenue</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>Presented lease repayments divided by same-period Revenue. Cash intensity only — not liability stock or ROU amortization.</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>lease_repayment.lease_repayments_to_revenue.2024-08-31</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>lease_repayment</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>E88</t>
+        </is>
+      </c>
+      <c r="I501">
+        <f>IF('Condensed Financials'!E44=0,NA(),E87/'Condensed Financials'!E44)</f>
+        <v/>
+      </c>
+      <c r="J501" t="n">
+        <v>0.04716840709367377</v>
+      </c>
+      <c r="K501" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>lease_repayments__20240831,revenue_link__20240831</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>Lease Repayments / Revenue uses the −reported repayment presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Revenue intensity of repayment cash only — not total lease cost, ROU amortization, or liability movement.</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>lease_repayments_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q501" t="n">
+        <v>123</v>
+      </c>
+      <c r="R501" t="n">
+        <v>3</v>
+      </c>
+      <c r="S501" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>lease_repayments_to_revenue__20250831</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>501</v>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Lease Repayments / Revenue</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Presented lease repayments divided by same-period Revenue. Cash intensity only — not liability stock or ROU amortization.</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>lease_repayment.lease_repayments_to_revenue.2025-08-31</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>lease_repayment</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>F88</t>
+        </is>
+      </c>
+      <c r="I502">
+        <f>IF('Condensed Financials'!F44=0,NA(),F87/'Condensed Financials'!F44)</f>
+        <v/>
+      </c>
+      <c r="J502" t="n">
+        <v>0.04131198024783718</v>
+      </c>
+      <c r="K502" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>lease_repayments__20250831,revenue_link__20250831</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>Lease Repayments / Revenue uses the −reported repayment presentation.|A zero Revenue denominator makes the ratio undefined (#N/A).|Revenue intensity of repayment cash only — not total lease cost, ROU amortization, or liability movement.</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>lease_repayments_to_revenue</t>
+        </is>
+      </c>
+      <c r="Q502" t="n">
+        <v>123</v>
+      </c>
+      <c r="R502" t="n">
+        <v>4</v>
+      </c>
+      <c r="S502" t="inlineStr">
         <is>
           <t>2025-08-31</t>
         </is>
@@ -50874,7 +51794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -52532,68 +53452,68 @@
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t>LEASE REPAYMENT CONTEXT</t>
+          <t>OPERATING CASH AFTER PP&amp;E CAPEX</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>Repayments of Lease Liabilities (reported)</t>
+          <t>Operating Cash Flow (reported)</t>
         </is>
       </c>
       <c r="B81" s="13">
-        <f>'Cash Flow Statement'!B47</f>
+        <f>'Cash Flow Statement'!B30</f>
         <v/>
       </c>
       <c r="C81" s="13">
-        <f>'Cash Flow Statement'!C47</f>
+        <f>'Cash Flow Statement'!C30</f>
         <v/>
       </c>
       <c r="D81" s="13">
-        <f>'Cash Flow Statement'!D47</f>
+        <f>'Cash Flow Statement'!D30</f>
         <v/>
       </c>
       <c r="E81" s="13">
-        <f>'Cash Flow Statement'!E47</f>
+        <f>'Cash Flow Statement'!E30</f>
         <v/>
       </c>
       <c r="F81" s="13">
-        <f>'Cash Flow Statement'!F47</f>
+        <f>'Cash Flow Statement'!F30</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t>Lease Repayments (−reported)</t>
+          <t>Operating cash after PP&amp;E capex</t>
         </is>
       </c>
       <c r="B82" s="16">
-        <f>-B81</f>
+        <f>B81-B77</f>
         <v/>
       </c>
       <c r="C82" s="16">
-        <f>-C81</f>
+        <f>C81-C77</f>
         <v/>
       </c>
       <c r="D82" s="16">
-        <f>-D81</f>
+        <f>D81-D77</f>
         <v/>
       </c>
       <c r="E82" s="16">
-        <f>-E81</f>
+        <f>E81-E77</f>
         <v/>
       </c>
       <c r="F82" s="16">
-        <f>-F81</f>
+        <f>F81-F77</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>Lease Repayments / Revenue</t>
+          <t>Operating cash after PP&amp;E capex / Revenue</t>
         </is>
       </c>
       <c r="B83" s="15">
@@ -52621,160 +53541,130 @@
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+          <t>LEASE REPAYMENT CONTEXT</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Repayments of Lease Liabilities (reported)</t>
         </is>
       </c>
       <c r="B86" s="13">
-        <f>'Balance Sheet'!B37</f>
+        <f>'Cash Flow Statement'!B47</f>
         <v/>
       </c>
       <c r="C86" s="13">
-        <f>'Balance Sheet'!C37</f>
+        <f>'Cash Flow Statement'!C47</f>
         <v/>
       </c>
       <c r="D86" s="13">
-        <f>'Balance Sheet'!D37</f>
+        <f>'Cash Flow Statement'!D47</f>
         <v/>
       </c>
       <c r="E86" s="13">
-        <f>'Balance Sheet'!E37</f>
+        <f>'Cash Flow Statement'!E47</f>
         <v/>
       </c>
       <c r="F86" s="13">
-        <f>'Balance Sheet'!F37</f>
+        <f>'Cash Flow Statement'!F47</f>
         <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>Change in Goodwill</t>
-        </is>
+          <t>Lease Repayments (−reported)</t>
+        </is>
+      </c>
+      <c r="B87" s="16">
+        <f>-B86</f>
+        <v/>
       </c>
       <c r="C87" s="16">
-        <f>C86-B86</f>
+        <f>-C86</f>
         <v/>
       </c>
       <c r="D87" s="16">
-        <f>D86-C86</f>
+        <f>-D86</f>
         <v/>
       </c>
       <c r="E87" s="16">
-        <f>E86-D86</f>
+        <f>-E86</f>
         <v/>
       </c>
       <c r="F87" s="16">
-        <f>F86-E86</f>
+        <f>-F86</f>
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
+          <t>Lease Repayments / Revenue</t>
+        </is>
+      </c>
+      <c r="B88" s="15">
+        <f>IF('Condensed Financials'!B44=0,NA(),B87/'Condensed Financials'!B44)</f>
+        <v/>
       </c>
       <c r="C88" s="15">
-        <f>IF(B86=0,NA(),C86/B86-1)</f>
+        <f>IF('Condensed Financials'!C44=0,NA(),C87/'Condensed Financials'!C44)</f>
         <v/>
       </c>
       <c r="D88" s="15">
-        <f>IF(C86=0,NA(),D86/C86-1)</f>
+        <f>IF('Condensed Financials'!D44=0,NA(),D87/'Condensed Financials'!D44)</f>
         <v/>
       </c>
       <c r="E88" s="15">
-        <f>IF(D86=0,NA(),E86/D86-1)</f>
+        <f>IF('Condensed Financials'!E44=0,NA(),E87/'Condensed Financials'!E44)</f>
         <v/>
       </c>
       <c r="F88" s="15">
-        <f>IF(E86=0,NA(),F86/E86-1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="11" t="inlineStr">
-        <is>
-          <t>Average Goodwill</t>
-        </is>
-      </c>
-      <c r="C89" s="16">
-        <f>(B86+C86)/2</f>
-        <v/>
-      </c>
-      <c r="D89" s="16">
-        <f>(C86+D86)/2</f>
-        <v/>
-      </c>
-      <c r="E89" s="16">
-        <f>(D86+E86)/2</f>
-        <v/>
-      </c>
-      <c r="F89" s="16">
-        <f>(E86+F86)/2</f>
-        <v/>
-      </c>
-    </row>
+        <f>IF('Condensed Financials'!F44=0,NA(),F87/'Condensed Financials'!F44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89"/>
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
-      <c r="C90" s="15">
-        <f>IF('Condensed Financials'!C44=0,NA(),C89/'Condensed Financials'!C44)</f>
-        <v/>
-      </c>
-      <c r="D90" s="15">
-        <f>IF('Condensed Financials'!D44=0,NA(),D89/'Condensed Financials'!D44)</f>
-        <v/>
-      </c>
-      <c r="E90" s="15">
-        <f>IF('Condensed Financials'!E44=0,NA(),E89/'Condensed Financials'!E44)</f>
-        <v/>
-      </c>
-      <c r="F90" s="15">
-        <f>IF('Condensed Financials'!F44=0,NA(),F89/'Condensed Financials'!F44)</f>
-        <v/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
+          <t>Goodwill</t>
         </is>
       </c>
       <c r="B91" s="13">
-        <f>'Balance Sheet'!B38</f>
+        <f>'Balance Sheet'!B37</f>
         <v/>
       </c>
       <c r="C91" s="13">
-        <f>'Balance Sheet'!C38</f>
+        <f>'Balance Sheet'!C37</f>
         <v/>
       </c>
       <c r="D91" s="13">
-        <f>'Balance Sheet'!D38</f>
+        <f>'Balance Sheet'!D37</f>
         <v/>
       </c>
       <c r="E91" s="13">
-        <f>'Balance Sheet'!E38</f>
+        <f>'Balance Sheet'!E37</f>
         <v/>
       </c>
       <c r="F91" s="13">
-        <f>'Balance Sheet'!F38</f>
+        <f>'Balance Sheet'!F37</f>
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>Change in Intangible Assets</t>
+          <t>Change in Goodwill</t>
         </is>
       </c>
       <c r="C92" s="16">
@@ -52797,7 +53687,7 @@
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>Intangible Assets Growth</t>
+          <t>Goodwill Growth</t>
         </is>
       </c>
       <c r="C93" s="15">
@@ -52820,7 +53710,7 @@
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
+          <t>Average Goodwill</t>
         </is>
       </c>
       <c r="C94" s="16">
@@ -52843,7 +53733,7 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>Average Intangible Assets / Revenue</t>
+          <t>Average Goodwill / Revenue</t>
         </is>
       </c>
       <c r="C95" s="15">
@@ -52866,34 +53756,34 @@
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
+          <t>Intangible Assets</t>
         </is>
       </c>
       <c r="B96" s="13">
-        <f>B86+B91</f>
+        <f>'Balance Sheet'!B38</f>
         <v/>
       </c>
       <c r="C96" s="13">
-        <f>C86+C91</f>
+        <f>'Balance Sheet'!C38</f>
         <v/>
       </c>
       <c r="D96" s="13">
-        <f>D86+D91</f>
+        <f>'Balance Sheet'!D38</f>
         <v/>
       </c>
       <c r="E96" s="13">
-        <f>E86+E91</f>
+        <f>'Balance Sheet'!E38</f>
         <v/>
       </c>
       <c r="F96" s="13">
-        <f>F86+F91</f>
+        <f>'Balance Sheet'!F38</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
+          <t>Change in Intangible Assets</t>
         </is>
       </c>
       <c r="C97" s="16">
@@ -52916,7 +53806,7 @@
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
+          <t>Intangible Assets Growth</t>
         </is>
       </c>
       <c r="C98" s="15">
@@ -52939,7 +53829,7 @@
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
+          <t>Average Intangible Assets</t>
         </is>
       </c>
       <c r="C99" s="16">
@@ -52962,7 +53852,7 @@
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles / Revenue</t>
+          <t>Average Intangible Assets / Revenue</t>
         </is>
       </c>
       <c r="C100" s="15">
@@ -52985,81 +53875,200 @@
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>Payments for Intangible Assets (reported)</t>
+          <t>Goodwill &amp; Intangibles</t>
         </is>
       </c>
       <c r="B101" s="13">
-        <f>'Cash Flow Statement'!B38</f>
+        <f>B91+B96</f>
         <v/>
       </c>
       <c r="C101" s="13">
-        <f>'Cash Flow Statement'!C38</f>
+        <f>C91+C96</f>
         <v/>
       </c>
       <c r="D101" s="13">
-        <f>'Cash Flow Statement'!D38</f>
+        <f>D91+D96</f>
         <v/>
       </c>
       <c r="E101" s="13">
-        <f>'Cash Flow Statement'!E38</f>
+        <f>E91+E96</f>
         <v/>
       </c>
       <c r="F101" s="13">
-        <f>'Cash Flow Statement'!F38</f>
+        <f>F91+F96</f>
         <v/>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t>Intangible Payments (−reported)</t>
-        </is>
-      </c>
-      <c r="B102" s="16">
-        <f>-B101</f>
-        <v/>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
       </c>
       <c r="C102" s="16">
-        <f>-C101</f>
+        <f>C101-B101</f>
         <v/>
       </c>
       <c r="D102" s="16">
-        <f>-D101</f>
+        <f>D101-C101</f>
         <v/>
       </c>
       <c r="E102" s="16">
-        <f>-E101</f>
+        <f>E101-D101</f>
         <v/>
       </c>
       <c r="F102" s="16">
-        <f>-F101</f>
+        <f>F101-E101</f>
         <v/>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C103" s="15">
+        <f>IF(B101=0,NA(),C101/B101-1)</f>
+        <v/>
+      </c>
+      <c r="D103" s="15">
+        <f>IF(C101=0,NA(),D101/C101-1)</f>
+        <v/>
+      </c>
+      <c r="E103" s="15">
+        <f>IF(D101=0,NA(),E101/D101-1)</f>
+        <v/>
+      </c>
+      <c r="F103" s="15">
+        <f>IF(E101=0,NA(),F101/E101-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C104" s="16">
+        <f>(B101+C101)/2</f>
+        <v/>
+      </c>
+      <c r="D104" s="16">
+        <f>(C101+D101)/2</f>
+        <v/>
+      </c>
+      <c r="E104" s="16">
+        <f>(D101+E101)/2</f>
+        <v/>
+      </c>
+      <c r="F104" s="16">
+        <f>(E101+F101)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles / Revenue</t>
+        </is>
+      </c>
+      <c r="C105" s="15">
+        <f>IF('Condensed Financials'!C44=0,NA(),C104/'Condensed Financials'!C44)</f>
+        <v/>
+      </c>
+      <c r="D105" s="15">
+        <f>IF('Condensed Financials'!D44=0,NA(),D104/'Condensed Financials'!D44)</f>
+        <v/>
+      </c>
+      <c r="E105" s="15">
+        <f>IF('Condensed Financials'!E44=0,NA(),E104/'Condensed Financials'!E44)</f>
+        <v/>
+      </c>
+      <c r="F105" s="15">
+        <f>IF('Condensed Financials'!F44=0,NA(),F104/'Condensed Financials'!F44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>Payments for Intangible Assets (reported)</t>
+        </is>
+      </c>
+      <c r="B106" s="13">
+        <f>'Cash Flow Statement'!B38</f>
+        <v/>
+      </c>
+      <c r="C106" s="13">
+        <f>'Cash Flow Statement'!C38</f>
+        <v/>
+      </c>
+      <c r="D106" s="13">
+        <f>'Cash Flow Statement'!D38</f>
+        <v/>
+      </c>
+      <c r="E106" s="13">
+        <f>'Cash Flow Statement'!E38</f>
+        <v/>
+      </c>
+      <c r="F106" s="13">
+        <f>'Cash Flow Statement'!F38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>Intangible Payments (−reported)</t>
+        </is>
+      </c>
+      <c r="B107" s="16">
+        <f>-B106</f>
+        <v/>
+      </c>
+      <c r="C107" s="16">
+        <f>-C106</f>
+        <v/>
+      </c>
+      <c r="D107" s="16">
+        <f>-D106</f>
+        <v/>
+      </c>
+      <c r="E107" s="16">
+        <f>-E106</f>
+        <v/>
+      </c>
+      <c r="F107" s="16">
+        <f>-F106</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
           <t>Intangible Payments / Revenue</t>
         </is>
       </c>
-      <c r="B103" s="15">
-        <f>IF('Condensed Financials'!B44=0,NA(),B102/'Condensed Financials'!B44)</f>
-        <v/>
-      </c>
-      <c r="C103" s="15">
-        <f>IF('Condensed Financials'!C44=0,NA(),C102/'Condensed Financials'!C44)</f>
-        <v/>
-      </c>
-      <c r="D103" s="15">
-        <f>IF('Condensed Financials'!D44=0,NA(),D102/'Condensed Financials'!D44)</f>
-        <v/>
-      </c>
-      <c r="E103" s="15">
-        <f>IF('Condensed Financials'!E44=0,NA(),E102/'Condensed Financials'!E44)</f>
-        <v/>
-      </c>
-      <c r="F103" s="15">
-        <f>IF('Condensed Financials'!F44=0,NA(),F102/'Condensed Financials'!F44)</f>
+      <c r="B108" s="15">
+        <f>IF('Condensed Financials'!B44=0,NA(),B107/'Condensed Financials'!B44)</f>
+        <v/>
+      </c>
+      <c r="C108" s="15">
+        <f>IF('Condensed Financials'!C44=0,NA(),C107/'Condensed Financials'!C44)</f>
+        <v/>
+      </c>
+      <c r="D108" s="15">
+        <f>IF('Condensed Financials'!D44=0,NA(),D107/'Condensed Financials'!D44)</f>
+        <v/>
+      </c>
+      <c r="E108" s="15">
+        <f>IF('Condensed Financials'!E44=0,NA(),E107/'Condensed Financials'!E44)</f>
+        <v/>
+      </c>
+      <c r="F108" s="15">
+        <f>IF('Condensed Financials'!F44=0,NA(),F107/'Condensed Financials'!F44)</f>
         <v/>
       </c>
     </row>

--- a/release/fast_retailing/FastRetailing_Answer_Key.xlsx
+++ b/release/fast_retailing/FastRetailing_Answer_Key.xlsx
@@ -1663,292 +1663,392 @@
         <t>Presented lease repayments divided by same-period Revenue. Cash intensity only — not liability stock or ROU amortization.</t>
       </text>
     </comment>
-    <comment ref="C92" authorId="0" shapeId="0">
+    <comment ref="B95" authorId="0" shapeId="0">
+      <text>
+        <t>CFO + CFI + CFF + FX using reported signed cash-flow totals in statement units, including the FX effect. Keep reported signs; do not reverse flows, omit FX, substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="C95" authorId="0" shapeId="0">
+      <text>
+        <t>CFO + CFI + CFF + FX using reported signed cash-flow totals in statement units, including the FX effect. Keep reported signs; do not reverse flows, omit FX, substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="D95" authorId="0" shapeId="0">
+      <text>
+        <t>CFO + CFI + CFF + FX using reported signed cash-flow totals in statement units, including the FX effect. Keep reported signs; do not reverse flows, omit FX, substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="E95" authorId="0" shapeId="0">
+      <text>
+        <t>CFO + CFI + CFF + FX using reported signed cash-flow totals in statement units, including the FX effect. Keep reported signs; do not reverse flows, omit FX, substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="F95" authorId="0" shapeId="0">
+      <text>
+        <t>CFO + CFI + CFF + FX using reported signed cash-flow totals in statement units, including the FX effect. Keep reported signs; do not reverse flows, omit FX, substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="B97" authorId="0" shapeId="0">
+      <text>
+        <t>Calculated cash movement from flows minus reported cash change, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="C97" authorId="0" shapeId="0">
+      <text>
+        <t>Calculated cash movement from flows minus reported cash change, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="D97" authorId="0" shapeId="0">
+      <text>
+        <t>Calculated cash movement from flows minus reported cash change, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="E97" authorId="0" shapeId="0">
+      <text>
+        <t>Calculated cash movement from flows minus reported cash change, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="F97" authorId="0" shapeId="0">
+      <text>
+        <t>Calculated cash movement from flows minus reported cash change, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="B99" authorId="0" shapeId="0">
+      <text>
+        <t>Reported cash beginning plus cash movement from flows (CFO + CFI + CFF + FX), in statement units. Keep signed flows and FX as reported; do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="C99" authorId="0" shapeId="0">
+      <text>
+        <t>Reported cash beginning plus cash movement from flows (CFO + CFI + CFF + FX), in statement units. Keep signed flows and FX as reported; do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="D99" authorId="0" shapeId="0">
+      <text>
+        <t>Reported cash beginning plus cash movement from flows (CFO + CFI + CFF + FX), in statement units. Keep signed flows and FX as reported; do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="E99" authorId="0" shapeId="0">
+      <text>
+        <t>Reported cash beginning plus cash movement from flows (CFO + CFI + CFF + FX), in statement units. Keep signed flows and FX as reported; do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="F99" authorId="0" shapeId="0">
+      <text>
+        <t>Reported cash beginning plus cash movement from flows (CFO + CFI + CFF + FX), in statement units. Keep signed flows and FX as reported; do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="B101" authorId="0" shapeId="0">
+      <text>
+        <t>Cash ending from flows minus reported cash ending, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="C101" authorId="0" shapeId="0">
+      <text>
+        <t>Cash ending from flows minus reported cash ending, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="D101" authorId="0" shapeId="0">
+      <text>
+        <t>Cash ending from flows minus reported cash ending, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="E101" authorId="0" shapeId="0">
+      <text>
+        <t>Cash ending from flows minus reported cash ending, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="F101" authorId="0" shapeId="0">
+      <text>
+        <t>Cash ending from flows minus reported cash ending, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+      </text>
+    </comment>
+    <comment ref="C105" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="D92" authorId="0" shapeId="0">
+    <comment ref="D105" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="E92" authorId="0" shapeId="0">
+    <comment ref="E105" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="F92" authorId="0" shapeId="0">
+    <comment ref="F105" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="C93" authorId="0" shapeId="0">
+    <comment ref="C106" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="D93" authorId="0" shapeId="0">
+    <comment ref="D106" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="E93" authorId="0" shapeId="0">
+    <comment ref="E106" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="F93" authorId="0" shapeId="0">
+    <comment ref="F106" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="C94" authorId="0" shapeId="0">
+    <comment ref="C107" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="D94" authorId="0" shapeId="0">
+    <comment ref="D107" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="E94" authorId="0" shapeId="0">
+    <comment ref="E107" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="F94" authorId="0" shapeId="0">
+    <comment ref="F107" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="C95" authorId="0" shapeId="0">
+    <comment ref="C108" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D95" authorId="0" shapeId="0">
+    <comment ref="D108" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E95" authorId="0" shapeId="0">
+    <comment ref="E108" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="F95" authorId="0" shapeId="0">
+    <comment ref="F108" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C97" authorId="0" shapeId="0">
+    <comment ref="C110" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D97" authorId="0" shapeId="0">
+    <comment ref="D110" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E97" authorId="0" shapeId="0">
+    <comment ref="E110" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="F97" authorId="0" shapeId="0">
+    <comment ref="F110" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C98" authorId="0" shapeId="0">
+    <comment ref="C111" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D98" authorId="0" shapeId="0">
+    <comment ref="D111" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E98" authorId="0" shapeId="0">
+    <comment ref="E111" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="F98" authorId="0" shapeId="0">
+    <comment ref="F111" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C99" authorId="0" shapeId="0">
+    <comment ref="C112" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D99" authorId="0" shapeId="0">
+    <comment ref="D112" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E99" authorId="0" shapeId="0">
+    <comment ref="E112" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="F99" authorId="0" shapeId="0">
+    <comment ref="F112" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C100" authorId="0" shapeId="0">
+    <comment ref="C113" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D100" authorId="0" shapeId="0">
+    <comment ref="D113" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E100" authorId="0" shapeId="0">
+    <comment ref="E113" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="F100" authorId="0" shapeId="0">
+    <comment ref="F113" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C102" authorId="0" shapeId="0">
+    <comment ref="C115" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="D102" authorId="0" shapeId="0">
+    <comment ref="D115" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="E102" authorId="0" shapeId="0">
+    <comment ref="E115" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="F102" authorId="0" shapeId="0">
+    <comment ref="F115" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="C103" authorId="0" shapeId="0">
+    <comment ref="C116" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="D103" authorId="0" shapeId="0">
+    <comment ref="D116" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="E103" authorId="0" shapeId="0">
+    <comment ref="E116" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="F103" authorId="0" shapeId="0">
+    <comment ref="F116" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="C104" authorId="0" shapeId="0">
+    <comment ref="C117" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="D104" authorId="0" shapeId="0">
+    <comment ref="D117" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="E104" authorId="0" shapeId="0">
+    <comment ref="E117" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="F104" authorId="0" shapeId="0">
+    <comment ref="F117" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="C105" authorId="0" shapeId="0">
+    <comment ref="C118" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="D105" authorId="0" shapeId="0">
+    <comment ref="D118" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="E105" authorId="0" shapeId="0">
+    <comment ref="E118" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="F105" authorId="0" shapeId="0">
+    <comment ref="F118" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="B107" authorId="0" shapeId="0">
+    <comment ref="B120" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="C107" authorId="0" shapeId="0">
+    <comment ref="C120" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="D107" authorId="0" shapeId="0">
+    <comment ref="D120" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="E107" authorId="0" shapeId="0">
+    <comment ref="E120" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="F107" authorId="0" shapeId="0">
+    <comment ref="F120" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="B108" authorId="0" shapeId="0">
+    <comment ref="B121" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="C108" authorId="0" shapeId="0">
+    <comment ref="C121" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="D108" authorId="0" shapeId="0">
+    <comment ref="D121" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="E108" authorId="0" shapeId="0">
+    <comment ref="E121" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="F108" authorId="0" shapeId="0">
+    <comment ref="F121" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
@@ -3051,7 +3151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5800,7 +5900,7 @@
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>C92:F92</t>
+          <t>C105:F105</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
@@ -5830,7 +5930,7 @@
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>C93:F93</t>
+          <t>C106:F106</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -5860,7 +5960,7 @@
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>C94:F94</t>
+          <t>C107:F107</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
@@ -5890,7 +5990,7 @@
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>C95:F95</t>
+          <t>C108:F108</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
@@ -5920,7 +6020,7 @@
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>C97:F97</t>
+          <t>C110:F110</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
@@ -5950,7 +6050,7 @@
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>C98:F98</t>
+          <t>C111:F111</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
@@ -5980,7 +6080,7 @@
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>C99:F99</t>
+          <t>C112:F112</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
@@ -6010,7 +6110,7 @@
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>C100:F100</t>
+          <t>C113:F113</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -6040,7 +6140,7 @@
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>C102:F102</t>
+          <t>C115:F115</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
@@ -6070,7 +6170,7 @@
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>C103:F103</t>
+          <t>C116:F116</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -6100,7 +6200,7 @@
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>C104:F104</t>
+          <t>C117:F117</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
@@ -6130,7 +6230,7 @@
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>C105:F105</t>
+          <t>C118:F118</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
@@ -6160,7 +6260,7 @@
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>B107:F107</t>
+          <t>B120:F120</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
@@ -6190,7 +6290,7 @@
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>B108:F108</t>
+          <t>B121:F121</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -6616,6 +6716,126 @@
       <c r="F121" s="11" t="inlineStr">
         <is>
           <t>cash_after_ppe_capex, revenue_link</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="11" t="n">
+        <v>135</v>
+      </c>
+      <c r="B122" s="11" t="inlineStr">
+        <is>
+          <t>Cash movement from flows</t>
+        </is>
+      </c>
+      <c r="C122" s="11" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D122" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E122" s="11" t="inlineStr">
+        <is>
+          <t>B95:F95</t>
+        </is>
+      </c>
+      <c r="F122" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="11" t="n">
+        <v>136</v>
+      </c>
+      <c r="B123" s="11" t="inlineStr">
+        <is>
+          <t>Cash movement difference</t>
+        </is>
+      </c>
+      <c r="C123" s="11" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D123" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E123" s="11" t="inlineStr">
+        <is>
+          <t>B97:F97</t>
+        </is>
+      </c>
+      <c r="F123" s="11" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="11" t="n">
+        <v>137</v>
+      </c>
+      <c r="B124" s="11" t="inlineStr">
+        <is>
+          <t>Cash ending from flows</t>
+        </is>
+      </c>
+      <c r="C124" s="11" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D124" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E124" s="11" t="inlineStr">
+        <is>
+          <t>B99:F99</t>
+        </is>
+      </c>
+      <c r="F124" s="11" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="11" t="n">
+        <v>138</v>
+      </c>
+      <c r="B125" s="11" t="inlineStr">
+        <is>
+          <t>Cash ending difference</t>
+        </is>
+      </c>
+      <c r="C125" s="11" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D125" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="inlineStr">
+        <is>
+          <t>B101:F101</t>
+        </is>
+      </c>
+      <c r="F125" s="11" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows</t>
         </is>
       </c>
     </row>
@@ -7633,7 +7853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S502"/>
+  <dimension ref="A1:S522"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37944,11 +38164,11 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>C92</t>
+          <t>C105</t>
         </is>
       </c>
       <c r="I382">
-        <f>C91-B91</f>
+        <f>C104-B104</f>
         <v/>
       </c>
       <c r="J382" t="n">
@@ -38020,11 +38240,11 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>D92</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I383">
-        <f>D91-C91</f>
+        <f>D104-C104</f>
         <v/>
       </c>
       <c r="J383" t="n">
@@ -38096,11 +38316,11 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>E92</t>
+          <t>E105</t>
         </is>
       </c>
       <c r="I384">
-        <f>E91-D91</f>
+        <f>E104-D104</f>
         <v/>
       </c>
       <c r="J384" t="n">
@@ -38172,11 +38392,11 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>F92</t>
+          <t>F105</t>
         </is>
       </c>
       <c r="I385">
-        <f>F91-E91</f>
+        <f>F104-E104</f>
         <v/>
       </c>
       <c r="J385" t="n">
@@ -38248,11 +38468,11 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>C93</t>
+          <t>C106</t>
         </is>
       </c>
       <c r="I386">
-        <f>IF(B91=0,NA(),C91/B91-1)</f>
+        <f>IF(B104=0,NA(),C104/B104-1)</f>
         <v/>
       </c>
       <c r="J386" t="n">
@@ -38329,11 +38549,11 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>D93</t>
+          <t>D106</t>
         </is>
       </c>
       <c r="I387">
-        <f>IF(C91=0,NA(),D91/C91-1)</f>
+        <f>IF(C104=0,NA(),D104/C104-1)</f>
         <v/>
       </c>
       <c r="J387" t="n">
@@ -38410,11 +38630,11 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>E93</t>
+          <t>E106</t>
         </is>
       </c>
       <c r="I388">
-        <f>IF(D91=0,NA(),E91/D91-1)</f>
+        <f>IF(D104=0,NA(),E104/D104-1)</f>
         <v/>
       </c>
       <c r="J388" t="n">
@@ -38491,11 +38711,11 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>F93</t>
+          <t>F106</t>
         </is>
       </c>
       <c r="I389">
-        <f>IF(E91=0,NA(),F91/E91-1)</f>
+        <f>IF(E104=0,NA(),F104/E104-1)</f>
         <v/>
       </c>
       <c r="J389" t="n">
@@ -38572,11 +38792,11 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>C94</t>
+          <t>C107</t>
         </is>
       </c>
       <c r="I390">
-        <f>(B91+C91)/2</f>
+        <f>(B104+C104)/2</f>
         <v/>
       </c>
       <c r="J390" t="n">
@@ -38648,11 +38868,11 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>D94</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I391">
-        <f>(C91+D91)/2</f>
+        <f>(C104+D104)/2</f>
         <v/>
       </c>
       <c r="J391" t="n">
@@ -38724,11 +38944,11 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>E94</t>
+          <t>E107</t>
         </is>
       </c>
       <c r="I392">
-        <f>(D91+E91)/2</f>
+        <f>(D104+E104)/2</f>
         <v/>
       </c>
       <c r="J392" t="n">
@@ -38800,11 +39020,11 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>F94</t>
+          <t>F107</t>
         </is>
       </c>
       <c r="I393">
-        <f>(E91+F91)/2</f>
+        <f>(E104+F104)/2</f>
         <v/>
       </c>
       <c r="J393" t="n">
@@ -38876,11 +39096,11 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>C95</t>
+          <t>C108</t>
         </is>
       </c>
       <c r="I394">
-        <f>IF('Condensed Financials'!C44=0,NA(),C94/'Condensed Financials'!C44)</f>
+        <f>IF('Condensed Financials'!C44=0,NA(),C107/'Condensed Financials'!C44)</f>
         <v/>
       </c>
       <c r="J394" t="n">
@@ -38957,11 +39177,11 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>D95</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I395">
-        <f>IF('Condensed Financials'!D44=0,NA(),D94/'Condensed Financials'!D44)</f>
+        <f>IF('Condensed Financials'!D44=0,NA(),D107/'Condensed Financials'!D44)</f>
         <v/>
       </c>
       <c r="J395" t="n">
@@ -39038,11 +39258,11 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>E95</t>
+          <t>E108</t>
         </is>
       </c>
       <c r="I396">
-        <f>IF('Condensed Financials'!E44=0,NA(),E94/'Condensed Financials'!E44)</f>
+        <f>IF('Condensed Financials'!E44=0,NA(),E107/'Condensed Financials'!E44)</f>
         <v/>
       </c>
       <c r="J396" t="n">
@@ -39119,11 +39339,11 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>F95</t>
+          <t>F108</t>
         </is>
       </c>
       <c r="I397">
-        <f>IF('Condensed Financials'!F44=0,NA(),F94/'Condensed Financials'!F44)</f>
+        <f>IF('Condensed Financials'!F44=0,NA(),F107/'Condensed Financials'!F44)</f>
         <v/>
       </c>
       <c r="J397" t="n">
@@ -39200,11 +39420,11 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>C97</t>
+          <t>C110</t>
         </is>
       </c>
       <c r="I398">
-        <f>C96-B96</f>
+        <f>C109-B109</f>
         <v/>
       </c>
       <c r="J398" t="n">
@@ -39276,11 +39496,11 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>D97</t>
+          <t>D110</t>
         </is>
       </c>
       <c r="I399">
-        <f>D96-C96</f>
+        <f>D109-C109</f>
         <v/>
       </c>
       <c r="J399" t="n">
@@ -39352,11 +39572,11 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>E97</t>
+          <t>E110</t>
         </is>
       </c>
       <c r="I400">
-        <f>E96-D96</f>
+        <f>E109-D109</f>
         <v/>
       </c>
       <c r="J400" t="n">
@@ -39428,11 +39648,11 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>F97</t>
+          <t>F110</t>
         </is>
       </c>
       <c r="I401">
-        <f>F96-E96</f>
+        <f>F109-E109</f>
         <v/>
       </c>
       <c r="J401" t="n">
@@ -39504,11 +39724,11 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>C98</t>
+          <t>C111</t>
         </is>
       </c>
       <c r="I402">
-        <f>IF(B96=0,NA(),C96/B96-1)</f>
+        <f>IF(B109=0,NA(),C109/B109-1)</f>
         <v/>
       </c>
       <c r="J402" t="n">
@@ -39585,11 +39805,11 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>D98</t>
+          <t>D111</t>
         </is>
       </c>
       <c r="I403">
-        <f>IF(C96=0,NA(),D96/C96-1)</f>
+        <f>IF(C109=0,NA(),D109/C109-1)</f>
         <v/>
       </c>
       <c r="J403" t="n">
@@ -39666,11 +39886,11 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>E98</t>
+          <t>E111</t>
         </is>
       </c>
       <c r="I404">
-        <f>IF(D96=0,NA(),E96/D96-1)</f>
+        <f>IF(D109=0,NA(),E109/D109-1)</f>
         <v/>
       </c>
       <c r="J404" t="n">
@@ -39747,11 +39967,11 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>F98</t>
+          <t>F111</t>
         </is>
       </c>
       <c r="I405">
-        <f>IF(E96=0,NA(),F96/E96-1)</f>
+        <f>IF(E109=0,NA(),F109/E109-1)</f>
         <v/>
       </c>
       <c r="J405" t="n">
@@ -39828,11 +40048,11 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>C99</t>
+          <t>C112</t>
         </is>
       </c>
       <c r="I406">
-        <f>(B96+C96)/2</f>
+        <f>(B109+C109)/2</f>
         <v/>
       </c>
       <c r="J406" t="n">
@@ -39904,11 +40124,11 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>D99</t>
+          <t>D112</t>
         </is>
       </c>
       <c r="I407">
-        <f>(C96+D96)/2</f>
+        <f>(C109+D109)/2</f>
         <v/>
       </c>
       <c r="J407" t="n">
@@ -39980,11 +40200,11 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>E99</t>
+          <t>E112</t>
         </is>
       </c>
       <c r="I408">
-        <f>(D96+E96)/2</f>
+        <f>(D109+E109)/2</f>
         <v/>
       </c>
       <c r="J408" t="n">
@@ -40056,11 +40276,11 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>F99</t>
+          <t>F112</t>
         </is>
       </c>
       <c r="I409">
-        <f>(E96+F96)/2</f>
+        <f>(E109+F109)/2</f>
         <v/>
       </c>
       <c r="J409" t="n">
@@ -40132,11 +40352,11 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>C100</t>
+          <t>C113</t>
         </is>
       </c>
       <c r="I410">
-        <f>IF('Condensed Financials'!C44=0,NA(),C99/'Condensed Financials'!C44)</f>
+        <f>IF('Condensed Financials'!C44=0,NA(),C112/'Condensed Financials'!C44)</f>
         <v/>
       </c>
       <c r="J410" t="n">
@@ -40213,11 +40433,11 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>D100</t>
+          <t>D113</t>
         </is>
       </c>
       <c r="I411">
-        <f>IF('Condensed Financials'!D44=0,NA(),D99/'Condensed Financials'!D44)</f>
+        <f>IF('Condensed Financials'!D44=0,NA(),D112/'Condensed Financials'!D44)</f>
         <v/>
       </c>
       <c r="J411" t="n">
@@ -40294,11 +40514,11 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>E100</t>
+          <t>E113</t>
         </is>
       </c>
       <c r="I412">
-        <f>IF('Condensed Financials'!E44=0,NA(),E99/'Condensed Financials'!E44)</f>
+        <f>IF('Condensed Financials'!E44=0,NA(),E112/'Condensed Financials'!E44)</f>
         <v/>
       </c>
       <c r="J412" t="n">
@@ -40375,11 +40595,11 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>F100</t>
+          <t>F113</t>
         </is>
       </c>
       <c r="I413">
-        <f>IF('Condensed Financials'!F44=0,NA(),F99/'Condensed Financials'!F44)</f>
+        <f>IF('Condensed Financials'!F44=0,NA(),F112/'Condensed Financials'!F44)</f>
         <v/>
       </c>
       <c r="J413" t="n">
@@ -40456,11 +40676,11 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>C102</t>
+          <t>C115</t>
         </is>
       </c>
       <c r="I414">
-        <f>C101-B101</f>
+        <f>C114-B114</f>
         <v/>
       </c>
       <c r="J414" t="n">
@@ -40532,11 +40752,11 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>D102</t>
+          <t>D115</t>
         </is>
       </c>
       <c r="I415">
-        <f>D101-C101</f>
+        <f>D114-C114</f>
         <v/>
       </c>
       <c r="J415" t="n">
@@ -40608,11 +40828,11 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>E102</t>
+          <t>E115</t>
         </is>
       </c>
       <c r="I416">
-        <f>E101-D101</f>
+        <f>E114-D114</f>
         <v/>
       </c>
       <c r="J416" t="n">
@@ -40684,11 +40904,11 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>F102</t>
+          <t>F115</t>
         </is>
       </c>
       <c r="I417">
-        <f>F101-E101</f>
+        <f>F114-E114</f>
         <v/>
       </c>
       <c r="J417" t="n">
@@ -40760,11 +40980,11 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>C103</t>
+          <t>C116</t>
         </is>
       </c>
       <c r="I418">
-        <f>IF(B101=0,NA(),C101/B101-1)</f>
+        <f>IF(B114=0,NA(),C114/B114-1)</f>
         <v/>
       </c>
       <c r="J418" t="n">
@@ -40841,11 +41061,11 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>D103</t>
+          <t>D116</t>
         </is>
       </c>
       <c r="I419">
-        <f>IF(C101=0,NA(),D101/C101-1)</f>
+        <f>IF(C114=0,NA(),D114/C114-1)</f>
         <v/>
       </c>
       <c r="J419" t="n">
@@ -40922,11 +41142,11 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>E103</t>
+          <t>E116</t>
         </is>
       </c>
       <c r="I420">
-        <f>IF(D101=0,NA(),E101/D101-1)</f>
+        <f>IF(D114=0,NA(),E114/D114-1)</f>
         <v/>
       </c>
       <c r="J420" t="n">
@@ -41003,11 +41223,11 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>F103</t>
+          <t>F116</t>
         </is>
       </c>
       <c r="I421">
-        <f>IF(E101=0,NA(),F101/E101-1)</f>
+        <f>IF(E114=0,NA(),F114/E114-1)</f>
         <v/>
       </c>
       <c r="J421" t="n">
@@ -41084,11 +41304,11 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>C104</t>
+          <t>C117</t>
         </is>
       </c>
       <c r="I422">
-        <f>(B101+C101)/2</f>
+        <f>(B114+C114)/2</f>
         <v/>
       </c>
       <c r="J422" t="n">
@@ -41160,11 +41380,11 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>D104</t>
+          <t>D117</t>
         </is>
       </c>
       <c r="I423">
-        <f>(C101+D101)/2</f>
+        <f>(C114+D114)/2</f>
         <v/>
       </c>
       <c r="J423" t="n">
@@ -41236,11 +41456,11 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>E104</t>
+          <t>E117</t>
         </is>
       </c>
       <c r="I424">
-        <f>(D101+E101)/2</f>
+        <f>(D114+E114)/2</f>
         <v/>
       </c>
       <c r="J424" t="n">
@@ -41312,11 +41532,11 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>F104</t>
+          <t>F117</t>
         </is>
       </c>
       <c r="I425">
-        <f>(E101+F101)/2</f>
+        <f>(E114+F114)/2</f>
         <v/>
       </c>
       <c r="J425" t="n">
@@ -41388,11 +41608,11 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C118</t>
         </is>
       </c>
       <c r="I426">
-        <f>IF('Condensed Financials'!C44=0,NA(),C104/'Condensed Financials'!C44)</f>
+        <f>IF('Condensed Financials'!C44=0,NA(),C117/'Condensed Financials'!C44)</f>
         <v/>
       </c>
       <c r="J426" t="n">
@@ -41469,11 +41689,11 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D118</t>
         </is>
       </c>
       <c r="I427">
-        <f>IF('Condensed Financials'!D44=0,NA(),D104/'Condensed Financials'!D44)</f>
+        <f>IF('Condensed Financials'!D44=0,NA(),D117/'Condensed Financials'!D44)</f>
         <v/>
       </c>
       <c r="J427" t="n">
@@ -41550,11 +41770,11 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>E105</t>
+          <t>E118</t>
         </is>
       </c>
       <c r="I428">
-        <f>IF('Condensed Financials'!E44=0,NA(),E104/'Condensed Financials'!E44)</f>
+        <f>IF('Condensed Financials'!E44=0,NA(),E117/'Condensed Financials'!E44)</f>
         <v/>
       </c>
       <c r="J428" t="n">
@@ -41631,11 +41851,11 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>F105</t>
+          <t>F118</t>
         </is>
       </c>
       <c r="I429">
-        <f>IF('Condensed Financials'!F44=0,NA(),F104/'Condensed Financials'!F44)</f>
+        <f>IF('Condensed Financials'!F44=0,NA(),F117/'Condensed Financials'!F44)</f>
         <v/>
       </c>
       <c r="J429" t="n">
@@ -41712,11 +41932,11 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>B107</t>
+          <t>B120</t>
         </is>
       </c>
       <c r="I430">
-        <f>-B106</f>
+        <f>-B119</f>
         <v/>
       </c>
       <c r="J430" t="n">
@@ -41788,11 +42008,11 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>C107</t>
+          <t>C120</t>
         </is>
       </c>
       <c r="I431">
-        <f>-C106</f>
+        <f>-C119</f>
         <v/>
       </c>
       <c r="J431" t="n">
@@ -41864,11 +42084,11 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D120</t>
         </is>
       </c>
       <c r="I432">
-        <f>-D106</f>
+        <f>-D119</f>
         <v/>
       </c>
       <c r="J432" t="n">
@@ -41940,11 +42160,11 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>E107</t>
+          <t>E120</t>
         </is>
       </c>
       <c r="I433">
-        <f>-E106</f>
+        <f>-E119</f>
         <v/>
       </c>
       <c r="J433" t="n">
@@ -42016,11 +42236,11 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>F107</t>
+          <t>F120</t>
         </is>
       </c>
       <c r="I434">
-        <f>-F106</f>
+        <f>-F119</f>
         <v/>
       </c>
       <c r="J434" t="n">
@@ -42092,11 +42312,11 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>B108</t>
+          <t>B121</t>
         </is>
       </c>
       <c r="I435">
-        <f>IF('Condensed Financials'!B44=0,NA(),B107/'Condensed Financials'!B44)</f>
+        <f>IF('Condensed Financials'!B44=0,NA(),B120/'Condensed Financials'!B44)</f>
         <v/>
       </c>
       <c r="J435" t="n">
@@ -42173,11 +42393,11 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>C108</t>
+          <t>C121</t>
         </is>
       </c>
       <c r="I436">
-        <f>IF('Condensed Financials'!C44=0,NA(),C107/'Condensed Financials'!C44)</f>
+        <f>IF('Condensed Financials'!C44=0,NA(),C120/'Condensed Financials'!C44)</f>
         <v/>
       </c>
       <c r="J436" t="n">
@@ -42254,11 +42474,11 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D121</t>
         </is>
       </c>
       <c r="I437">
-        <f>IF('Condensed Financials'!D44=0,NA(),D107/'Condensed Financials'!D44)</f>
+        <f>IF('Condensed Financials'!D44=0,NA(),D120/'Condensed Financials'!D44)</f>
         <v/>
       </c>
       <c r="J437" t="n">
@@ -42335,11 +42555,11 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>E108</t>
+          <t>E121</t>
         </is>
       </c>
       <c r="I438">
-        <f>IF('Condensed Financials'!E44=0,NA(),E107/'Condensed Financials'!E44)</f>
+        <f>IF('Condensed Financials'!E44=0,NA(),E120/'Condensed Financials'!E44)</f>
         <v/>
       </c>
       <c r="J438" t="n">
@@ -42416,11 +42636,11 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>F108</t>
+          <t>F121</t>
         </is>
       </c>
       <c r="I439">
-        <f>IF('Condensed Financials'!F44=0,NA(),F107/'Condensed Financials'!F44)</f>
+        <f>IF('Condensed Financials'!F44=0,NA(),F120/'Condensed Financials'!F44)</f>
         <v/>
       </c>
       <c r="J439" t="n">
@@ -47404,6 +47624,1601 @@
         <v>4</v>
       </c>
       <c r="S502" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20210831</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>502</v>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Cash movement from flows</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>CFO + CFI + CFF + FX using reported signed cash-flow totals in statement units, including the FX effect. Keep reported signs; do not reverse flows, omit FX, substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_movement_from_flows.2021-08-31</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>B95</t>
+        </is>
+      </c>
+      <c r="I503">
+        <f>B91+B92+B93+B94</f>
+        <v/>
+      </c>
+      <c r="J503" t="n">
+        <v>84204</v>
+      </c>
+      <c r="K503" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>Cash movement from flows = reported CFO + CFI + CFF + FX.|Use signed statement-unit totals, including FX.|Do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows</t>
+        </is>
+      </c>
+      <c r="Q503" t="n">
+        <v>135</v>
+      </c>
+      <c r="R503" t="n">
+        <v>0</v>
+      </c>
+      <c r="S503" t="inlineStr">
+        <is>
+          <t>2021-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20220831</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>503</v>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Cash movement from flows</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>CFO + CFI + CFF + FX using reported signed cash-flow totals in statement units, including the FX effect. Keep reported signs; do not reverse flows, omit FX, substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_movement_from_flows.2022-08-31</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>C95</t>
+        </is>
+      </c>
+      <c r="I504">
+        <f>C91+C92+C93+C94</f>
+        <v/>
+      </c>
+      <c r="J504" t="n">
+        <v>180556</v>
+      </c>
+      <c r="K504" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>Cash movement from flows = reported CFO + CFI + CFF + FX.|Use signed statement-unit totals, including FX.|Do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows</t>
+        </is>
+      </c>
+      <c r="Q504" t="n">
+        <v>135</v>
+      </c>
+      <c r="R504" t="n">
+        <v>1</v>
+      </c>
+      <c r="S504" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20230831</t>
+        </is>
+      </c>
+      <c r="B505" t="n">
+        <v>504</v>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Cash movement from flows</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>CFO + CFI + CFF + FX using reported signed cash-flow totals in statement units, including the FX effect. Keep reported signs; do not reverse flows, omit FX, substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_movement_from_flows.2023-08-31</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>D95</t>
+        </is>
+      </c>
+      <c r="I505">
+        <f>D91+D92+D93+D94</f>
+        <v/>
+      </c>
+      <c r="J505" t="n">
+        <v>-455013</v>
+      </c>
+      <c r="K505" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>Cash movement from flows = reported CFO + CFI + CFF + FX.|Use signed statement-unit totals, including FX.|Do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows</t>
+        </is>
+      </c>
+      <c r="Q505" t="n">
+        <v>135</v>
+      </c>
+      <c r="R505" t="n">
+        <v>2</v>
+      </c>
+      <c r="S505" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20240831</t>
+        </is>
+      </c>
+      <c r="B506" t="n">
+        <v>505</v>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Cash movement from flows</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>CFO + CFI + CFF + FX using reported signed cash-flow totals in statement units, including the FX effect. Keep reported signs; do not reverse flows, omit FX, substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_movement_from_flows.2024-08-31</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>E95</t>
+        </is>
+      </c>
+      <c r="I506">
+        <f>E91+E92+E93+E94</f>
+        <v/>
+      </c>
+      <c r="J506" t="n">
+        <v>290280</v>
+      </c>
+      <c r="K506" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>Cash movement from flows = reported CFO + CFI + CFF + FX.|Use signed statement-unit totals, including FX.|Do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P506" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows</t>
+        </is>
+      </c>
+      <c r="Q506" t="n">
+        <v>135</v>
+      </c>
+      <c r="R506" t="n">
+        <v>3</v>
+      </c>
+      <c r="S506" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20250831</t>
+        </is>
+      </c>
+      <c r="B507" t="n">
+        <v>506</v>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Cash movement from flows</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>CFO + CFI + CFF + FX using reported signed cash-flow totals in statement units, including the FX effect. Keep reported signs; do not reverse flows, omit FX, substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_movement_from_flows.2025-08-31</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>F95</t>
+        </is>
+      </c>
+      <c r="I507">
+        <f>F91+F92+F93+F94</f>
+        <v/>
+      </c>
+      <c r="J507" t="n">
+        <v>-300321</v>
+      </c>
+      <c r="K507" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>Cash movement from flows = reported CFO + CFI + CFF + FX.|Use signed statement-unit totals, including FX.|Do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P507" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows</t>
+        </is>
+      </c>
+      <c r="Q507" t="n">
+        <v>135</v>
+      </c>
+      <c r="R507" t="n">
+        <v>4</v>
+      </c>
+      <c r="S507" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>cash_movement_difference__20210831</t>
+        </is>
+      </c>
+      <c r="B508" t="n">
+        <v>507</v>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Cash movement difference</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Calculated cash movement from flows minus reported cash change, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_movement_difference.2021-08-31</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>B97</t>
+        </is>
+      </c>
+      <c r="I508">
+        <f>B95-B96</f>
+        <v/>
+      </c>
+      <c r="J508" t="n">
+        <v>0</v>
+      </c>
+      <c r="K508" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L508" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20210831</t>
+        </is>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>Cash movement difference = cash movement from flows − reported cash change.|Preserve nonzero calculated-minus-reported gaps in statement units.|Do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>cash_movement_difference</t>
+        </is>
+      </c>
+      <c r="Q508" t="n">
+        <v>136</v>
+      </c>
+      <c r="R508" t="n">
+        <v>0</v>
+      </c>
+      <c r="S508" t="inlineStr">
+        <is>
+          <t>2021-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>cash_movement_difference__20220831</t>
+        </is>
+      </c>
+      <c r="B509" t="n">
+        <v>508</v>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Cash movement difference</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Calculated cash movement from flows minus reported cash change, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_movement_difference.2022-08-31</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>C97</t>
+        </is>
+      </c>
+      <c r="I509">
+        <f>C95-C96</f>
+        <v/>
+      </c>
+      <c r="J509" t="n">
+        <v>0</v>
+      </c>
+      <c r="K509" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L509" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20220831</t>
+        </is>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>Cash movement difference = cash movement from flows − reported cash change.|Preserve nonzero calculated-minus-reported gaps in statement units.|Do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>cash_movement_difference</t>
+        </is>
+      </c>
+      <c r="Q509" t="n">
+        <v>136</v>
+      </c>
+      <c r="R509" t="n">
+        <v>1</v>
+      </c>
+      <c r="S509" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>cash_movement_difference__20230831</t>
+        </is>
+      </c>
+      <c r="B510" t="n">
+        <v>509</v>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Cash movement difference</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Calculated cash movement from flows minus reported cash change, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_movement_difference.2023-08-31</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>D97</t>
+        </is>
+      </c>
+      <c r="I510">
+        <f>D95-D96</f>
+        <v/>
+      </c>
+      <c r="J510" t="n">
+        <v>-2</v>
+      </c>
+      <c r="K510" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L510" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20230831</t>
+        </is>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>Cash movement difference = cash movement from flows − reported cash change.|Preserve nonzero calculated-minus-reported gaps in statement units.|Do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>cash_movement_difference</t>
+        </is>
+      </c>
+      <c r="Q510" t="n">
+        <v>136</v>
+      </c>
+      <c r="R510" t="n">
+        <v>2</v>
+      </c>
+      <c r="S510" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>cash_movement_difference__20240831</t>
+        </is>
+      </c>
+      <c r="B511" t="n">
+        <v>510</v>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Cash movement difference</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Calculated cash movement from flows minus reported cash change, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_movement_difference.2024-08-31</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>E97</t>
+        </is>
+      </c>
+      <c r="I511">
+        <f>E95-E96</f>
+        <v/>
+      </c>
+      <c r="J511" t="n">
+        <v>1</v>
+      </c>
+      <c r="K511" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L511" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20240831</t>
+        </is>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>Cash movement difference = cash movement from flows − reported cash change.|Preserve nonzero calculated-minus-reported gaps in statement units.|Do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>cash_movement_difference</t>
+        </is>
+      </c>
+      <c r="Q511" t="n">
+        <v>136</v>
+      </c>
+      <c r="R511" t="n">
+        <v>3</v>
+      </c>
+      <c r="S511" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>cash_movement_difference__20250831</t>
+        </is>
+      </c>
+      <c r="B512" t="n">
+        <v>511</v>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Cash movement difference</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Calculated cash movement from flows minus reported cash change, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_movement_difference.2025-08-31</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>F97</t>
+        </is>
+      </c>
+      <c r="I512">
+        <f>F95-F96</f>
+        <v/>
+      </c>
+      <c r="J512" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K512" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L512" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20250831</t>
+        </is>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>Cash movement difference = cash movement from flows − reported cash change.|Preserve nonzero calculated-minus-reported gaps in statement units.|Do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>cash_movement_difference</t>
+        </is>
+      </c>
+      <c r="Q512" t="n">
+        <v>136</v>
+      </c>
+      <c r="R512" t="n">
+        <v>4</v>
+      </c>
+      <c r="S512" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows__20210831</t>
+        </is>
+      </c>
+      <c r="B513" t="n">
+        <v>512</v>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Cash ending from flows</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Reported cash beginning plus cash movement from flows (CFO + CFI + CFF + FX), in statement units. Keep signed flows and FX as reported; do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_ending_from_flows.2021-08-31</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>B99</t>
+        </is>
+      </c>
+      <c r="I513">
+        <f>B98+B95</f>
+        <v/>
+      </c>
+      <c r="J513" t="n">
+        <v>1177735</v>
+      </c>
+      <c r="K513" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L513" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20210831</t>
+        </is>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>Cash ending from flows = reported cash beginning + cash movement from flows.|Movement includes signed CFO, CFI, CFF, and FX in statement units.|Do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows</t>
+        </is>
+      </c>
+      <c r="Q513" t="n">
+        <v>137</v>
+      </c>
+      <c r="R513" t="n">
+        <v>0</v>
+      </c>
+      <c r="S513" t="inlineStr">
+        <is>
+          <t>2021-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows__20220831</t>
+        </is>
+      </c>
+      <c r="B514" t="n">
+        <v>513</v>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Cash ending from flows</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Reported cash beginning plus cash movement from flows (CFO + CFI + CFF + FX), in statement units. Keep signed flows and FX as reported; do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_ending_from_flows.2022-08-31</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>C99</t>
+        </is>
+      </c>
+      <c r="I514">
+        <f>C98+C95</f>
+        <v/>
+      </c>
+      <c r="J514" t="n">
+        <v>1358292</v>
+      </c>
+      <c r="K514" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L514" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20220831</t>
+        </is>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>Cash ending from flows = reported cash beginning + cash movement from flows.|Movement includes signed CFO, CFI, CFF, and FX in statement units.|Do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows</t>
+        </is>
+      </c>
+      <c r="Q514" t="n">
+        <v>137</v>
+      </c>
+      <c r="R514" t="n">
+        <v>1</v>
+      </c>
+      <c r="S514" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows__20230831</t>
+        </is>
+      </c>
+      <c r="B515" t="n">
+        <v>514</v>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Cash ending from flows</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Reported cash beginning plus cash movement from flows (CFO + CFI + CFF + FX), in statement units. Keep signed flows and FX as reported; do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_ending_from_flows.2023-08-31</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>D99</t>
+        </is>
+      </c>
+      <c r="I515">
+        <f>D98+D95</f>
+        <v/>
+      </c>
+      <c r="J515" t="n">
+        <v>903279</v>
+      </c>
+      <c r="K515" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L515" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20230831</t>
+        </is>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>Cash ending from flows = reported cash beginning + cash movement from flows.|Movement includes signed CFO, CFI, CFF, and FX in statement units.|Do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows</t>
+        </is>
+      </c>
+      <c r="Q515" t="n">
+        <v>137</v>
+      </c>
+      <c r="R515" t="n">
+        <v>2</v>
+      </c>
+      <c r="S515" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows__20240831</t>
+        </is>
+      </c>
+      <c r="B516" t="n">
+        <v>515</v>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Cash ending from flows</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Reported cash beginning plus cash movement from flows (CFO + CFI + CFF + FX), in statement units. Keep signed flows and FX as reported; do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_ending_from_flows.2024-08-31</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>E99</t>
+        </is>
+      </c>
+      <c r="I516">
+        <f>E98+E95</f>
+        <v/>
+      </c>
+      <c r="J516" t="n">
+        <v>1193560</v>
+      </c>
+      <c r="K516" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L516" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20240831</t>
+        </is>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>Cash ending from flows = reported cash beginning + cash movement from flows.|Movement includes signed CFO, CFI, CFF, and FX in statement units.|Do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O516" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P516" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows</t>
+        </is>
+      </c>
+      <c r="Q516" t="n">
+        <v>137</v>
+      </c>
+      <c r="R516" t="n">
+        <v>3</v>
+      </c>
+      <c r="S516" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows__20250831</t>
+        </is>
+      </c>
+      <c r="B517" t="n">
+        <v>516</v>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Cash ending from flows</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Reported cash beginning plus cash movement from flows (CFO + CFI + CFF + FX), in statement units. Keep signed flows and FX as reported; do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_ending_from_flows.2025-08-31</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>F99</t>
+        </is>
+      </c>
+      <c r="I517">
+        <f>F98+F95</f>
+        <v/>
+      </c>
+      <c r="J517" t="n">
+        <v>893239</v>
+      </c>
+      <c r="K517" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L517" t="inlineStr">
+        <is>
+          <t>cash_movement_from_flows__20250831</t>
+        </is>
+      </c>
+      <c r="M517" t="inlineStr">
+        <is>
+          <t>Cash ending from flows = reported cash beginning + cash movement from flows.|Movement includes signed CFO, CFI, CFF, and FX in statement units.|Do not substitute balance-sheet cash, insert a balancing plug, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O517" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P517" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows</t>
+        </is>
+      </c>
+      <c r="Q517" t="n">
+        <v>137</v>
+      </c>
+      <c r="R517" t="n">
+        <v>4</v>
+      </c>
+      <c r="S517" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>cash_ending_difference__20210831</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>517</v>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Cash ending difference</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Cash ending from flows minus reported cash ending, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_ending_difference.2021-08-31</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>B101</t>
+        </is>
+      </c>
+      <c r="I518">
+        <f>B99-B100</f>
+        <v/>
+      </c>
+      <c r="J518" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K518" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L518" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows__20210831</t>
+        </is>
+      </c>
+      <c r="M518" t="inlineStr">
+        <is>
+          <t>Cash ending difference = cash ending from flows − reported cash ending.|Preserve nonzero calculated-minus-reported gaps in statement units.|Do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O518" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P518" t="inlineStr">
+        <is>
+          <t>cash_ending_difference</t>
+        </is>
+      </c>
+      <c r="Q518" t="n">
+        <v>138</v>
+      </c>
+      <c r="R518" t="n">
+        <v>0</v>
+      </c>
+      <c r="S518" t="inlineStr">
+        <is>
+          <t>2021-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>cash_ending_difference__20220831</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>518</v>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Cash ending difference</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Cash ending from flows minus reported cash ending, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_ending_difference.2022-08-31</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>C101</t>
+        </is>
+      </c>
+      <c r="I519">
+        <f>C99-C100</f>
+        <v/>
+      </c>
+      <c r="J519" t="n">
+        <v>0</v>
+      </c>
+      <c r="K519" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L519" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows__20220831</t>
+        </is>
+      </c>
+      <c r="M519" t="inlineStr">
+        <is>
+          <t>Cash ending difference = cash ending from flows − reported cash ending.|Preserve nonzero calculated-minus-reported gaps in statement units.|Do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O519" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P519" t="inlineStr">
+        <is>
+          <t>cash_ending_difference</t>
+        </is>
+      </c>
+      <c r="Q519" t="n">
+        <v>138</v>
+      </c>
+      <c r="R519" t="n">
+        <v>1</v>
+      </c>
+      <c r="S519" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>cash_ending_difference__20230831</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>519</v>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Cash ending difference</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Cash ending from flows minus reported cash ending, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_ending_difference.2023-08-31</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>D101</t>
+        </is>
+      </c>
+      <c r="I520">
+        <f>D99-D100</f>
+        <v/>
+      </c>
+      <c r="J520" t="n">
+        <v>-1</v>
+      </c>
+      <c r="K520" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L520" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows__20230831</t>
+        </is>
+      </c>
+      <c r="M520" t="inlineStr">
+        <is>
+          <t>Cash ending difference = cash ending from flows − reported cash ending.|Preserve nonzero calculated-minus-reported gaps in statement units.|Do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O520" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P520" t="inlineStr">
+        <is>
+          <t>cash_ending_difference</t>
+        </is>
+      </c>
+      <c r="Q520" t="n">
+        <v>138</v>
+      </c>
+      <c r="R520" t="n">
+        <v>2</v>
+      </c>
+      <c r="S520" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>cash_ending_difference__20240831</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>520</v>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Cash ending difference</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Cash ending from flows minus reported cash ending, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_ending_difference.2024-08-31</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>E101</t>
+        </is>
+      </c>
+      <c r="I521">
+        <f>E99-E100</f>
+        <v/>
+      </c>
+      <c r="J521" t="n">
+        <v>0</v>
+      </c>
+      <c r="K521" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L521" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows__20240831</t>
+        </is>
+      </c>
+      <c r="M521" t="inlineStr">
+        <is>
+          <t>Cash ending difference = cash ending from flows − reported cash ending.|Preserve nonzero calculated-minus-reported gaps in statement units.|Do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O521" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P521" t="inlineStr">
+        <is>
+          <t>cash_ending_difference</t>
+        </is>
+      </c>
+      <c r="Q521" t="n">
+        <v>138</v>
+      </c>
+      <c r="R521" t="n">
+        <v>3</v>
+      </c>
+      <c r="S521" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>cash_ending_difference__20250831</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>521</v>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Cash ending difference</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Cash ending from flows minus reported cash ending, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>cash_rollforward.cash_ending_difference.2025-08-31</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>cash_rollforward</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>F101</t>
+        </is>
+      </c>
+      <c r="I522">
+        <f>F99-F100</f>
+        <v/>
+      </c>
+      <c r="J522" t="n">
+        <v>0</v>
+      </c>
+      <c r="K522" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L522" t="inlineStr">
+        <is>
+          <t>cash_ending_from_flows__20250831</t>
+        </is>
+      </c>
+      <c r="M522" t="inlineStr">
+        <is>
+          <t>Cash ending difference = cash ending from flows − reported cash ending.|Preserve nonzero calculated-minus-reported gaps in statement units.|Do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
+        </is>
+      </c>
+      <c r="O522" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P522" t="inlineStr">
+        <is>
+          <t>cash_ending_difference</t>
+        </is>
+      </c>
+      <c r="Q522" t="n">
+        <v>138</v>
+      </c>
+      <c r="R522" t="n">
+        <v>4</v>
+      </c>
+      <c r="S522" t="inlineStr">
         <is>
           <t>2025-08-31</t>
         </is>
@@ -51794,7 +53609,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -53630,430 +55445,416 @@
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+          <t>CASH ROLL-FORWARD CONTEXT</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Net cash from operating activities (reported)</t>
         </is>
       </c>
       <c r="B91" s="13">
-        <f>'Balance Sheet'!B37</f>
+        <f>'Cash Flow Statement'!B30</f>
         <v/>
       </c>
       <c r="C91" s="13">
-        <f>'Balance Sheet'!C37</f>
+        <f>'Cash Flow Statement'!C30</f>
         <v/>
       </c>
       <c r="D91" s="13">
-        <f>'Balance Sheet'!D37</f>
+        <f>'Cash Flow Statement'!D30</f>
         <v/>
       </c>
       <c r="E91" s="13">
-        <f>'Balance Sheet'!E37</f>
+        <f>'Cash Flow Statement'!E30</f>
         <v/>
       </c>
       <c r="F91" s="13">
-        <f>'Balance Sheet'!F37</f>
+        <f>'Cash Flow Statement'!F30</f>
         <v/>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>Change in Goodwill</t>
-        </is>
-      </c>
-      <c r="C92" s="16">
-        <f>C91-B91</f>
-        <v/>
-      </c>
-      <c r="D92" s="16">
-        <f>D91-C91</f>
-        <v/>
-      </c>
-      <c r="E92" s="16">
-        <f>E91-D91</f>
-        <v/>
-      </c>
-      <c r="F92" s="16">
-        <f>F91-E91</f>
+          <t>Net cash from investing activities (reported)</t>
+        </is>
+      </c>
+      <c r="B92" s="13">
+        <f>'Cash Flow Statement'!B32</f>
+        <v/>
+      </c>
+      <c r="C92" s="13">
+        <f>'Cash Flow Statement'!C32</f>
+        <v/>
+      </c>
+      <c r="D92" s="13">
+        <f>'Cash Flow Statement'!D32</f>
+        <v/>
+      </c>
+      <c r="E92" s="13">
+        <f>'Cash Flow Statement'!E32</f>
+        <v/>
+      </c>
+      <c r="F92" s="13">
+        <f>'Cash Flow Statement'!F32</f>
         <v/>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
-      </c>
-      <c r="C93" s="15">
-        <f>IF(B91=0,NA(),C91/B91-1)</f>
-        <v/>
-      </c>
-      <c r="D93" s="15">
-        <f>IF(C91=0,NA(),D91/C91-1)</f>
-        <v/>
-      </c>
-      <c r="E93" s="15">
-        <f>IF(D91=0,NA(),E91/D91-1)</f>
-        <v/>
-      </c>
-      <c r="F93" s="15">
-        <f>IF(E91=0,NA(),F91/E91-1)</f>
+          <t>Net cash from financing activities (reported)</t>
+        </is>
+      </c>
+      <c r="B93" s="13">
+        <f>'Cash Flow Statement'!B31</f>
+        <v/>
+      </c>
+      <c r="C93" s="13">
+        <f>'Cash Flow Statement'!C31</f>
+        <v/>
+      </c>
+      <c r="D93" s="13">
+        <f>'Cash Flow Statement'!D31</f>
+        <v/>
+      </c>
+      <c r="E93" s="13">
+        <f>'Cash Flow Statement'!E31</f>
+        <v/>
+      </c>
+      <c r="F93" s="13">
+        <f>'Cash Flow Statement'!F31</f>
         <v/>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill</t>
-        </is>
-      </c>
-      <c r="C94" s="16">
-        <f>(B91+C91)/2</f>
-        <v/>
-      </c>
-      <c r="D94" s="16">
-        <f>(C91+D91)/2</f>
-        <v/>
-      </c>
-      <c r="E94" s="16">
-        <f>(D91+E91)/2</f>
-        <v/>
-      </c>
-      <c r="F94" s="16">
-        <f>(E91+F91)/2</f>
+          <t>Effect of FX on cash (reported)</t>
+        </is>
+      </c>
+      <c r="B94" s="13">
+        <f>'Cash Flow Statement'!B18</f>
+        <v/>
+      </c>
+      <c r="C94" s="13">
+        <f>'Cash Flow Statement'!C18</f>
+        <v/>
+      </c>
+      <c r="D94" s="13">
+        <f>'Cash Flow Statement'!D18</f>
+        <v/>
+      </c>
+      <c r="E94" s="13">
+        <f>'Cash Flow Statement'!E18</f>
+        <v/>
+      </c>
+      <c r="F94" s="13">
+        <f>'Cash Flow Statement'!F18</f>
         <v/>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
-      <c r="C95" s="15">
-        <f>IF('Condensed Financials'!C44=0,NA(),C94/'Condensed Financials'!C44)</f>
-        <v/>
-      </c>
-      <c r="D95" s="15">
-        <f>IF('Condensed Financials'!D44=0,NA(),D94/'Condensed Financials'!D44)</f>
-        <v/>
-      </c>
-      <c r="E95" s="15">
-        <f>IF('Condensed Financials'!E44=0,NA(),E94/'Condensed Financials'!E44)</f>
-        <v/>
-      </c>
-      <c r="F95" s="15">
-        <f>IF('Condensed Financials'!F44=0,NA(),F94/'Condensed Financials'!F44)</f>
+          <t>Cash movement from flows</t>
+        </is>
+      </c>
+      <c r="B95" s="16">
+        <f>B91+B92+B93+B94</f>
+        <v/>
+      </c>
+      <c r="C95" s="16">
+        <f>C91+C92+C93+C94</f>
+        <v/>
+      </c>
+      <c r="D95" s="16">
+        <f>D91+D92+D93+D94</f>
+        <v/>
+      </c>
+      <c r="E95" s="16">
+        <f>E91+E92+E93+E94</f>
+        <v/>
+      </c>
+      <c r="F95" s="16">
+        <f>F91+F92+F93+F94</f>
         <v/>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
+          <t>Reported cash change</t>
         </is>
       </c>
       <c r="B96" s="13">
-        <f>'Balance Sheet'!B38</f>
+        <f>'Cash Flow Statement'!B33</f>
         <v/>
       </c>
       <c r="C96" s="13">
-        <f>'Balance Sheet'!C38</f>
+        <f>'Cash Flow Statement'!C33</f>
         <v/>
       </c>
       <c r="D96" s="13">
-        <f>'Balance Sheet'!D38</f>
+        <f>'Cash Flow Statement'!D33</f>
         <v/>
       </c>
       <c r="E96" s="13">
-        <f>'Balance Sheet'!E38</f>
+        <f>'Cash Flow Statement'!E33</f>
         <v/>
       </c>
       <c r="F96" s="13">
-        <f>'Balance Sheet'!F38</f>
+        <f>'Cash Flow Statement'!F33</f>
         <v/>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>Change in Intangible Assets</t>
-        </is>
+          <t>Cash movement difference</t>
+        </is>
+      </c>
+      <c r="B97" s="16">
+        <f>B95-B96</f>
+        <v/>
       </c>
       <c r="C97" s="16">
-        <f>C96-B96</f>
+        <f>C95-C96</f>
         <v/>
       </c>
       <c r="D97" s="16">
-        <f>D96-C96</f>
+        <f>D95-D96</f>
         <v/>
       </c>
       <c r="E97" s="16">
-        <f>E96-D96</f>
+        <f>E95-E96</f>
         <v/>
       </c>
       <c r="F97" s="16">
-        <f>F96-E96</f>
+        <f>F95-F96</f>
         <v/>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>Intangible Assets Growth</t>
-        </is>
-      </c>
-      <c r="C98" s="15">
-        <f>IF(B96=0,NA(),C96/B96-1)</f>
-        <v/>
-      </c>
-      <c r="D98" s="15">
-        <f>IF(C96=0,NA(),D96/C96-1)</f>
-        <v/>
-      </c>
-      <c r="E98" s="15">
-        <f>IF(D96=0,NA(),E96/D96-1)</f>
-        <v/>
-      </c>
-      <c r="F98" s="15">
-        <f>IF(E96=0,NA(),F96/E96-1)</f>
+          <t>Cash beginning (reported)</t>
+        </is>
+      </c>
+      <c r="B98" s="13">
+        <f>'Cash Flow Statement'!B12</f>
+        <v/>
+      </c>
+      <c r="C98" s="13">
+        <f>'Cash Flow Statement'!C12</f>
+        <v/>
+      </c>
+      <c r="D98" s="13">
+        <f>'Cash Flow Statement'!D12</f>
+        <v/>
+      </c>
+      <c r="E98" s="13">
+        <f>'Cash Flow Statement'!E12</f>
+        <v/>
+      </c>
+      <c r="F98" s="13">
+        <f>'Cash Flow Statement'!F12</f>
         <v/>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
-        </is>
+          <t>Cash ending from flows</t>
+        </is>
+      </c>
+      <c r="B99" s="16">
+        <f>B98+B95</f>
+        <v/>
       </c>
       <c r="C99" s="16">
-        <f>(B96+C96)/2</f>
+        <f>C98+C95</f>
         <v/>
       </c>
       <c r="D99" s="16">
-        <f>(C96+D96)/2</f>
+        <f>D98+D95</f>
         <v/>
       </c>
       <c r="E99" s="16">
-        <f>(D96+E96)/2</f>
+        <f>E98+E95</f>
         <v/>
       </c>
       <c r="F99" s="16">
-        <f>(E96+F96)/2</f>
+        <f>F98+F95</f>
         <v/>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t>Average Intangible Assets / Revenue</t>
-        </is>
-      </c>
-      <c r="C100" s="15">
-        <f>IF('Condensed Financials'!C44=0,NA(),C99/'Condensed Financials'!C44)</f>
-        <v/>
-      </c>
-      <c r="D100" s="15">
-        <f>IF('Condensed Financials'!D44=0,NA(),D99/'Condensed Financials'!D44)</f>
-        <v/>
-      </c>
-      <c r="E100" s="15">
-        <f>IF('Condensed Financials'!E44=0,NA(),E99/'Condensed Financials'!E44)</f>
-        <v/>
-      </c>
-      <c r="F100" s="15">
-        <f>IF('Condensed Financials'!F44=0,NA(),F99/'Condensed Financials'!F44)</f>
+          <t>Cash ending (reported)</t>
+        </is>
+      </c>
+      <c r="B100" s="13">
+        <f>'Cash Flow Statement'!B13</f>
+        <v/>
+      </c>
+      <c r="C100" s="13">
+        <f>'Cash Flow Statement'!C13</f>
+        <v/>
+      </c>
+      <c r="D100" s="13">
+        <f>'Cash Flow Statement'!D13</f>
+        <v/>
+      </c>
+      <c r="E100" s="13">
+        <f>'Cash Flow Statement'!E13</f>
+        <v/>
+      </c>
+      <c r="F100" s="13">
+        <f>'Cash Flow Statement'!F13</f>
         <v/>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="B101" s="13">
-        <f>B91+B96</f>
-        <v/>
-      </c>
-      <c r="C101" s="13">
-        <f>C91+C96</f>
-        <v/>
-      </c>
-      <c r="D101" s="13">
-        <f>D91+D96</f>
-        <v/>
-      </c>
-      <c r="E101" s="13">
-        <f>E91+E96</f>
-        <v/>
-      </c>
-      <c r="F101" s="13">
-        <f>F91+F96</f>
-        <v/>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="11" t="inlineStr">
-        <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C102" s="16">
-        <f>C101-B101</f>
-        <v/>
-      </c>
-      <c r="D102" s="16">
-        <f>D101-C101</f>
-        <v/>
-      </c>
-      <c r="E102" s="16">
-        <f>E101-D101</f>
-        <v/>
-      </c>
-      <c r="F102" s="16">
-        <f>F101-E101</f>
-        <v/>
-      </c>
-    </row>
+          <t>Cash ending difference</t>
+        </is>
+      </c>
+      <c r="B101" s="16">
+        <f>B99-B100</f>
+        <v/>
+      </c>
+      <c r="C101" s="16">
+        <f>C99-C100</f>
+        <v/>
+      </c>
+      <c r="D101" s="16">
+        <f>D99-D100</f>
+        <v/>
+      </c>
+      <c r="E101" s="16">
+        <f>E99-E100</f>
+        <v/>
+      </c>
+      <c r="F101" s="16">
+        <f>F99-F100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102"/>
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
-        </is>
-      </c>
-      <c r="C103" s="15">
-        <f>IF(B101=0,NA(),C101/B101-1)</f>
-        <v/>
-      </c>
-      <c r="D103" s="15">
-        <f>IF(C101=0,NA(),D101/C101-1)</f>
-        <v/>
-      </c>
-      <c r="E103" s="15">
-        <f>IF(D101=0,NA(),E101/D101-1)</f>
-        <v/>
-      </c>
-      <c r="F103" s="15">
-        <f>IF(E101=0,NA(),F101/E101-1)</f>
-        <v/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C104" s="16">
-        <f>(B101+C101)/2</f>
-        <v/>
-      </c>
-      <c r="D104" s="16">
-        <f>(C101+D101)/2</f>
-        <v/>
-      </c>
-      <c r="E104" s="16">
-        <f>(D101+E101)/2</f>
-        <v/>
-      </c>
-      <c r="F104" s="16">
-        <f>(E101+F101)/2</f>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B104" s="13">
+        <f>'Balance Sheet'!B37</f>
+        <v/>
+      </c>
+      <c r="C104" s="13">
+        <f>'Balance Sheet'!C37</f>
+        <v/>
+      </c>
+      <c r="D104" s="13">
+        <f>'Balance Sheet'!D37</f>
+        <v/>
+      </c>
+      <c r="E104" s="13">
+        <f>'Balance Sheet'!E37</f>
+        <v/>
+      </c>
+      <c r="F104" s="13">
+        <f>'Balance Sheet'!F37</f>
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles / Revenue</t>
-        </is>
-      </c>
-      <c r="C105" s="15">
-        <f>IF('Condensed Financials'!C44=0,NA(),C104/'Condensed Financials'!C44)</f>
-        <v/>
-      </c>
-      <c r="D105" s="15">
-        <f>IF('Condensed Financials'!D44=0,NA(),D104/'Condensed Financials'!D44)</f>
-        <v/>
-      </c>
-      <c r="E105" s="15">
-        <f>IF('Condensed Financials'!E44=0,NA(),E104/'Condensed Financials'!E44)</f>
-        <v/>
-      </c>
-      <c r="F105" s="15">
-        <f>IF('Condensed Financials'!F44=0,NA(),F104/'Condensed Financials'!F44)</f>
+          <t>Change in Goodwill</t>
+        </is>
+      </c>
+      <c r="C105" s="16">
+        <f>C104-B104</f>
+        <v/>
+      </c>
+      <c r="D105" s="16">
+        <f>D104-C104</f>
+        <v/>
+      </c>
+      <c r="E105" s="16">
+        <f>E104-D104</f>
+        <v/>
+      </c>
+      <c r="F105" s="16">
+        <f>F104-E104</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>Payments for Intangible Assets (reported)</t>
-        </is>
-      </c>
-      <c r="B106" s="13">
-        <f>'Cash Flow Statement'!B38</f>
-        <v/>
-      </c>
-      <c r="C106" s="13">
-        <f>'Cash Flow Statement'!C38</f>
-        <v/>
-      </c>
-      <c r="D106" s="13">
-        <f>'Cash Flow Statement'!D38</f>
-        <v/>
-      </c>
-      <c r="E106" s="13">
-        <f>'Cash Flow Statement'!E38</f>
-        <v/>
-      </c>
-      <c r="F106" s="13">
-        <f>'Cash Flow Statement'!F38</f>
+          <t>Goodwill Growth</t>
+        </is>
+      </c>
+      <c r="C106" s="15">
+        <f>IF(B104=0,NA(),C104/B104-1)</f>
+        <v/>
+      </c>
+      <c r="D106" s="15">
+        <f>IF(C104=0,NA(),D104/C104-1)</f>
+        <v/>
+      </c>
+      <c r="E106" s="15">
+        <f>IF(D104=0,NA(),E104/D104-1)</f>
+        <v/>
+      </c>
+      <c r="F106" s="15">
+        <f>IF(E104=0,NA(),F104/E104-1)</f>
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>Intangible Payments (−reported)</t>
-        </is>
-      </c>
-      <c r="B107" s="16">
-        <f>-B106</f>
-        <v/>
+          <t>Average Goodwill</t>
+        </is>
       </c>
       <c r="C107" s="16">
-        <f>-C106</f>
+        <f>(B104+C104)/2</f>
         <v/>
       </c>
       <c r="D107" s="16">
-        <f>-D106</f>
+        <f>(C104+D104)/2</f>
         <v/>
       </c>
       <c r="E107" s="16">
-        <f>-E106</f>
+        <f>(D104+E104)/2</f>
         <v/>
       </c>
       <c r="F107" s="16">
-        <f>-F106</f>
+        <f>(E104+F104)/2</f>
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>Intangible Payments / Revenue</t>
-        </is>
-      </c>
-      <c r="B108" s="15">
-        <f>IF('Condensed Financials'!B44=0,NA(),B107/'Condensed Financials'!B44)</f>
-        <v/>
+          <t>Average Goodwill / Revenue</t>
+        </is>
       </c>
       <c r="C108" s="15">
         <f>IF('Condensed Financials'!C44=0,NA(),C107/'Condensed Financials'!C44)</f>
@@ -54069,6 +55870,325 @@
       </c>
       <c r="F108" s="15">
         <f>IF('Condensed Financials'!F44=0,NA(),F107/'Condensed Financials'!F44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="11" t="inlineStr">
+        <is>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B109" s="13">
+        <f>'Balance Sheet'!B38</f>
+        <v/>
+      </c>
+      <c r="C109" s="13">
+        <f>'Balance Sheet'!C38</f>
+        <v/>
+      </c>
+      <c r="D109" s="13">
+        <f>'Balance Sheet'!D38</f>
+        <v/>
+      </c>
+      <c r="E109" s="13">
+        <f>'Balance Sheet'!E38</f>
+        <v/>
+      </c>
+      <c r="F109" s="13">
+        <f>'Balance Sheet'!F38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="11" t="inlineStr">
+        <is>
+          <t>Change in Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C110" s="16">
+        <f>C109-B109</f>
+        <v/>
+      </c>
+      <c r="D110" s="16">
+        <f>D109-C109</f>
+        <v/>
+      </c>
+      <c r="E110" s="16">
+        <f>E109-D109</f>
+        <v/>
+      </c>
+      <c r="F110" s="16">
+        <f>F109-E109</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>Intangible Assets Growth</t>
+        </is>
+      </c>
+      <c r="C111" s="15">
+        <f>IF(B109=0,NA(),C109/B109-1)</f>
+        <v/>
+      </c>
+      <c r="D111" s="15">
+        <f>IF(C109=0,NA(),D109/C109-1)</f>
+        <v/>
+      </c>
+      <c r="E111" s="15">
+        <f>IF(D109=0,NA(),E109/D109-1)</f>
+        <v/>
+      </c>
+      <c r="F111" s="15">
+        <f>IF(E109=0,NA(),F109/E109-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C112" s="16">
+        <f>(B109+C109)/2</f>
+        <v/>
+      </c>
+      <c r="D112" s="16">
+        <f>(C109+D109)/2</f>
+        <v/>
+      </c>
+      <c r="E112" s="16">
+        <f>(D109+E109)/2</f>
+        <v/>
+      </c>
+      <c r="F112" s="16">
+        <f>(E109+F109)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="11" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="C113" s="15">
+        <f>IF('Condensed Financials'!C44=0,NA(),C112/'Condensed Financials'!C44)</f>
+        <v/>
+      </c>
+      <c r="D113" s="15">
+        <f>IF('Condensed Financials'!D44=0,NA(),D112/'Condensed Financials'!D44)</f>
+        <v/>
+      </c>
+      <c r="E113" s="15">
+        <f>IF('Condensed Financials'!E44=0,NA(),E112/'Condensed Financials'!E44)</f>
+        <v/>
+      </c>
+      <c r="F113" s="15">
+        <f>IF('Condensed Financials'!F44=0,NA(),F112/'Condensed Financials'!F44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="11" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B114" s="13">
+        <f>B104+B109</f>
+        <v/>
+      </c>
+      <c r="C114" s="13">
+        <f>C104+C109</f>
+        <v/>
+      </c>
+      <c r="D114" s="13">
+        <f>D104+D109</f>
+        <v/>
+      </c>
+      <c r="E114" s="13">
+        <f>E104+E109</f>
+        <v/>
+      </c>
+      <c r="F114" s="13">
+        <f>F104+F109</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="11" t="inlineStr">
+        <is>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C115" s="16">
+        <f>C114-B114</f>
+        <v/>
+      </c>
+      <c r="D115" s="16">
+        <f>D114-C114</f>
+        <v/>
+      </c>
+      <c r="E115" s="16">
+        <f>E114-D114</f>
+        <v/>
+      </c>
+      <c r="F115" s="16">
+        <f>F114-E114</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C116" s="15">
+        <f>IF(B114=0,NA(),C114/B114-1)</f>
+        <v/>
+      </c>
+      <c r="D116" s="15">
+        <f>IF(C114=0,NA(),D114/C114-1)</f>
+        <v/>
+      </c>
+      <c r="E116" s="15">
+        <f>IF(D114=0,NA(),E114/D114-1)</f>
+        <v/>
+      </c>
+      <c r="F116" s="15">
+        <f>IF(E114=0,NA(),F114/E114-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C117" s="16">
+        <f>(B114+C114)/2</f>
+        <v/>
+      </c>
+      <c r="D117" s="16">
+        <f>(C114+D114)/2</f>
+        <v/>
+      </c>
+      <c r="E117" s="16">
+        <f>(D114+E114)/2</f>
+        <v/>
+      </c>
+      <c r="F117" s="16">
+        <f>(E114+F114)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="11" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles / Revenue</t>
+        </is>
+      </c>
+      <c r="C118" s="15">
+        <f>IF('Condensed Financials'!C44=0,NA(),C117/'Condensed Financials'!C44)</f>
+        <v/>
+      </c>
+      <c r="D118" s="15">
+        <f>IF('Condensed Financials'!D44=0,NA(),D117/'Condensed Financials'!D44)</f>
+        <v/>
+      </c>
+      <c r="E118" s="15">
+        <f>IF('Condensed Financials'!E44=0,NA(),E117/'Condensed Financials'!E44)</f>
+        <v/>
+      </c>
+      <c r="F118" s="15">
+        <f>IF('Condensed Financials'!F44=0,NA(),F117/'Condensed Financials'!F44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="11" t="inlineStr">
+        <is>
+          <t>Payments for Intangible Assets (reported)</t>
+        </is>
+      </c>
+      <c r="B119" s="13">
+        <f>'Cash Flow Statement'!B38</f>
+        <v/>
+      </c>
+      <c r="C119" s="13">
+        <f>'Cash Flow Statement'!C38</f>
+        <v/>
+      </c>
+      <c r="D119" s="13">
+        <f>'Cash Flow Statement'!D38</f>
+        <v/>
+      </c>
+      <c r="E119" s="13">
+        <f>'Cash Flow Statement'!E38</f>
+        <v/>
+      </c>
+      <c r="F119" s="13">
+        <f>'Cash Flow Statement'!F38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="11" t="inlineStr">
+        <is>
+          <t>Intangible Payments (−reported)</t>
+        </is>
+      </c>
+      <c r="B120" s="16">
+        <f>-B119</f>
+        <v/>
+      </c>
+      <c r="C120" s="16">
+        <f>-C119</f>
+        <v/>
+      </c>
+      <c r="D120" s="16">
+        <f>-D119</f>
+        <v/>
+      </c>
+      <c r="E120" s="16">
+        <f>-E119</f>
+        <v/>
+      </c>
+      <c r="F120" s="16">
+        <f>-F119</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>Intangible Payments / Revenue</t>
+        </is>
+      </c>
+      <c r="B121" s="15">
+        <f>IF('Condensed Financials'!B44=0,NA(),B120/'Condensed Financials'!B44)</f>
+        <v/>
+      </c>
+      <c r="C121" s="15">
+        <f>IF('Condensed Financials'!C44=0,NA(),C120/'Condensed Financials'!C44)</f>
+        <v/>
+      </c>
+      <c r="D121" s="15">
+        <f>IF('Condensed Financials'!D44=0,NA(),D120/'Condensed Financials'!D44)</f>
+        <v/>
+      </c>
+      <c r="E121" s="15">
+        <f>IF('Condensed Financials'!E44=0,NA(),E120/'Condensed Financials'!E44)</f>
+        <v/>
+      </c>
+      <c r="F121" s="15">
+        <f>IF('Condensed Financials'!F44=0,NA(),F120/'Condensed Financials'!F44)</f>
         <v/>
       </c>
     </row>

--- a/release/fast_retailing/FastRetailing_Answer_Key.xlsx
+++ b/release/fast_retailing/FastRetailing_Answer_Key.xlsx
@@ -1763,292 +1763,427 @@
         <t>Cash ending from flows minus reported cash ending, in statement units. A nonzero difference is a reported reconciliation gap; do not insert a balancing plug, assert a cause, substitute balance-sheet cash, or infer debt funding.</t>
       </text>
     </comment>
-    <comment ref="C105" authorId="0" shapeId="0">
+    <comment ref="B107" authorId="0" shapeId="0">
+      <text>
+        <t>Gross margin = reported gross profit / revenue. Zero revenue is undefined (#N/A). Do not infer price, mix, or cost causes.</t>
+      </text>
+    </comment>
+    <comment ref="C107" authorId="0" shapeId="0">
+      <text>
+        <t>Gross margin = reported gross profit / revenue. Zero revenue is undefined (#N/A). Do not infer price, mix, or cost causes.</t>
+      </text>
+    </comment>
+    <comment ref="D107" authorId="0" shapeId="0">
+      <text>
+        <t>Gross margin = reported gross profit / revenue. Zero revenue is undefined (#N/A). Do not infer price, mix, or cost causes.</t>
+      </text>
+    </comment>
+    <comment ref="E107" authorId="0" shapeId="0">
+      <text>
+        <t>Gross margin = reported gross profit / revenue. Zero revenue is undefined (#N/A). Do not infer price, mix, or cost causes.</t>
+      </text>
+    </comment>
+    <comment ref="F107" authorId="0" shapeId="0">
+      <text>
+        <t>Gross margin = reported gross profit / revenue. Zero revenue is undefined (#N/A). Do not infer price, mix, or cost causes.</t>
+      </text>
+    </comment>
+    <comment ref="B108" authorId="0" shapeId="0">
+      <text>
+        <t>Reported operating margin = reported operating profit / revenue. Distinct from BAV NOPAT margin; not normalized earnings. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="C108" authorId="0" shapeId="0">
+      <text>
+        <t>Reported operating margin = reported operating profit / revenue. Distinct from BAV NOPAT margin; not normalized earnings. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="D108" authorId="0" shapeId="0">
+      <text>
+        <t>Reported operating margin = reported operating profit / revenue. Distinct from BAV NOPAT margin; not normalized earnings. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="E108" authorId="0" shapeId="0">
+      <text>
+        <t>Reported operating margin = reported operating profit / revenue. Distinct from BAV NOPAT margin; not normalized earnings. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="F108" authorId="0" shapeId="0">
+      <text>
+        <t>Reported operating margin = reported operating profit / revenue. Distinct from BAV NOPAT margin; not normalized earnings. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="B109" authorId="0" shapeId="0">
+      <text>
+        <t>Net operating expense burden = (gross profit − operating profit) / revenue. That difference includes net intervening operating items; it is not necessarily SG&amp;A. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="C109" authorId="0" shapeId="0">
+      <text>
+        <t>Net operating expense burden = (gross profit − operating profit) / revenue. That difference includes net intervening operating items; it is not necessarily SG&amp;A. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="D109" authorId="0" shapeId="0">
+      <text>
+        <t>Net operating expense burden = (gross profit − operating profit) / revenue. That difference includes net intervening operating items; it is not necessarily SG&amp;A. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="E109" authorId="0" shapeId="0">
+      <text>
+        <t>Net operating expense burden = (gross profit − operating profit) / revenue. That difference includes net intervening operating items; it is not necessarily SG&amp;A. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="F109" authorId="0" shapeId="0">
+      <text>
+        <t>Net operating expense burden = (gross profit − operating profit) / revenue. That difference includes net intervening operating items; it is not necessarily SG&amp;A. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="C110" authorId="0" shapeId="0">
+      <text>
+        <t>Change in gross margin is a percentage-point movement: current gross margin minus prior gross margin. Do not infer price, mix, or cost causes.</t>
+      </text>
+    </comment>
+    <comment ref="D110" authorId="0" shapeId="0">
+      <text>
+        <t>Change in gross margin is a percentage-point movement: current gross margin minus prior gross margin. Do not infer price, mix, or cost causes.</t>
+      </text>
+    </comment>
+    <comment ref="E110" authorId="0" shapeId="0">
+      <text>
+        <t>Change in gross margin is a percentage-point movement: current gross margin minus prior gross margin. Do not infer price, mix, or cost causes.</t>
+      </text>
+    </comment>
+    <comment ref="F110" authorId="0" shapeId="0">
+      <text>
+        <t>Change in gross margin is a percentage-point movement: current gross margin minus prior gross margin. Do not infer price, mix, or cost causes.</t>
+      </text>
+    </comment>
+    <comment ref="C111" authorId="0" shapeId="0">
+      <text>
+        <t>Change in net operating expense burden is a percentage-point movement: current burden minus prior burden. A positive burden change reduces reported operating margin. Intervening items are not necessarily SG&amp;A.</t>
+      </text>
+    </comment>
+    <comment ref="D111" authorId="0" shapeId="0">
+      <text>
+        <t>Change in net operating expense burden is a percentage-point movement: current burden minus prior burden. A positive burden change reduces reported operating margin. Intervening items are not necessarily SG&amp;A.</t>
+      </text>
+    </comment>
+    <comment ref="E111" authorId="0" shapeId="0">
+      <text>
+        <t>Change in net operating expense burden is a percentage-point movement: current burden minus prior burden. A positive burden change reduces reported operating margin. Intervening items are not necessarily SG&amp;A.</t>
+      </text>
+    </comment>
+    <comment ref="F111" authorId="0" shapeId="0">
+      <text>
+        <t>Change in net operating expense burden is a percentage-point movement: current burden minus prior burden. A positive burden change reduces reported operating margin. Intervening items are not necessarily SG&amp;A.</t>
+      </text>
+    </comment>
+    <comment ref="C112" authorId="0" shapeId="0">
+      <text>
+        <t>Reconstructed operating-margin change = gross-margin change − burden change, in percentage points. It reconciles to the adjacent reported operating-margin difference. Do not infer price, mix, cost causes, or normalized earnings; keep this distinct from BAV NOPAT margin.</t>
+      </text>
+    </comment>
+    <comment ref="D112" authorId="0" shapeId="0">
+      <text>
+        <t>Reconstructed operating-margin change = gross-margin change − burden change, in percentage points. It reconciles to the adjacent reported operating-margin difference. Do not infer price, mix, cost causes, or normalized earnings; keep this distinct from BAV NOPAT margin.</t>
+      </text>
+    </comment>
+    <comment ref="E112" authorId="0" shapeId="0">
+      <text>
+        <t>Reconstructed operating-margin change = gross-margin change − burden change, in percentage points. It reconciles to the adjacent reported operating-margin difference. Do not infer price, mix, cost causes, or normalized earnings; keep this distinct from BAV NOPAT margin.</t>
+      </text>
+    </comment>
+    <comment ref="F112" authorId="0" shapeId="0">
+      <text>
+        <t>Reconstructed operating-margin change = gross-margin change − burden change, in percentage points. It reconciles to the adjacent reported operating-margin difference. Do not infer price, mix, cost causes, or normalized earnings; keep this distinct from BAV NOPAT margin.</t>
+      </text>
+    </comment>
+    <comment ref="C116" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="D105" authorId="0" shapeId="0">
+    <comment ref="D116" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="E105" authorId="0" shapeId="0">
+    <comment ref="E116" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="F105" authorId="0" shapeId="0">
+    <comment ref="F116" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="C106" authorId="0" shapeId="0">
+    <comment ref="C117" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="D106" authorId="0" shapeId="0">
+    <comment ref="D117" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="E106" authorId="0" shapeId="0">
+    <comment ref="E117" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="F106" authorId="0" shapeId="0">
+    <comment ref="F117" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="C107" authorId="0" shapeId="0">
+    <comment ref="C118" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="D107" authorId="0" shapeId="0">
+    <comment ref="D118" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="E107" authorId="0" shapeId="0">
+    <comment ref="E118" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="F107" authorId="0" shapeId="0">
+    <comment ref="F118" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="C108" authorId="0" shapeId="0">
+    <comment ref="C119" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D108" authorId="0" shapeId="0">
+    <comment ref="D119" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E108" authorId="0" shapeId="0">
+    <comment ref="E119" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="F108" authorId="0" shapeId="0">
+    <comment ref="F119" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C110" authorId="0" shapeId="0">
+    <comment ref="C121" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D110" authorId="0" shapeId="0">
+    <comment ref="D121" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E110" authorId="0" shapeId="0">
+    <comment ref="E121" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="F110" authorId="0" shapeId="0">
+    <comment ref="F121" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C111" authorId="0" shapeId="0">
+    <comment ref="C122" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D111" authorId="0" shapeId="0">
+    <comment ref="D122" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E111" authorId="0" shapeId="0">
+    <comment ref="E122" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="F111" authorId="0" shapeId="0">
+    <comment ref="F122" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C112" authorId="0" shapeId="0">
+    <comment ref="C123" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D112" authorId="0" shapeId="0">
+    <comment ref="D123" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E112" authorId="0" shapeId="0">
+    <comment ref="E123" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="F112" authorId="0" shapeId="0">
+    <comment ref="F123" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C113" authorId="0" shapeId="0">
+    <comment ref="C124" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D113" authorId="0" shapeId="0">
+    <comment ref="D124" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E113" authorId="0" shapeId="0">
+    <comment ref="E124" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="F113" authorId="0" shapeId="0">
+    <comment ref="F124" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C115" authorId="0" shapeId="0">
+    <comment ref="C126" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="D115" authorId="0" shapeId="0">
+    <comment ref="D126" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="E115" authorId="0" shapeId="0">
+    <comment ref="E126" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="F115" authorId="0" shapeId="0">
+    <comment ref="F126" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="C116" authorId="0" shapeId="0">
+    <comment ref="C127" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="D116" authorId="0" shapeId="0">
+    <comment ref="D127" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="E116" authorId="0" shapeId="0">
+    <comment ref="E127" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="F116" authorId="0" shapeId="0">
+    <comment ref="F127" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="C117" authorId="0" shapeId="0">
+    <comment ref="C128" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="D117" authorId="0" shapeId="0">
+    <comment ref="D128" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="E117" authorId="0" shapeId="0">
+    <comment ref="E128" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="F117" authorId="0" shapeId="0">
+    <comment ref="F128" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="C118" authorId="0" shapeId="0">
+    <comment ref="C129" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="D118" authorId="0" shapeId="0">
+    <comment ref="D129" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="E118" authorId="0" shapeId="0">
+    <comment ref="E129" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="F118" authorId="0" shapeId="0">
+    <comment ref="F129" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="B120" authorId="0" shapeId="0">
+    <comment ref="B131" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="C120" authorId="0" shapeId="0">
+    <comment ref="C131" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="D120" authorId="0" shapeId="0">
+    <comment ref="D131" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="E120" authorId="0" shapeId="0">
+    <comment ref="E131" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="F120" authorId="0" shapeId="0">
+    <comment ref="F131" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="B121" authorId="0" shapeId="0">
+    <comment ref="B132" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="C121" authorId="0" shapeId="0">
+    <comment ref="C132" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="D121" authorId="0" shapeId="0">
+    <comment ref="D132" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="E121" authorId="0" shapeId="0">
+    <comment ref="E132" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="F121" authorId="0" shapeId="0">
+    <comment ref="F132" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
@@ -3151,7 +3286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F125"/>
+  <dimension ref="A1:F131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -5900,7 +6035,7 @@
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>C105:F105</t>
+          <t>C116:F116</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
@@ -5930,7 +6065,7 @@
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>C106:F106</t>
+          <t>C117:F117</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -5960,7 +6095,7 @@
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>C107:F107</t>
+          <t>C118:F118</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
@@ -5990,7 +6125,7 @@
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>C108:F108</t>
+          <t>C119:F119</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
@@ -6020,7 +6155,7 @@
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>C110:F110</t>
+          <t>C121:F121</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
@@ -6050,7 +6185,7 @@
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>C111:F111</t>
+          <t>C122:F122</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
@@ -6080,7 +6215,7 @@
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>C112:F112</t>
+          <t>C123:F123</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
@@ -6110,7 +6245,7 @@
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>C113:F113</t>
+          <t>C124:F124</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -6140,7 +6275,7 @@
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>C115:F115</t>
+          <t>C126:F126</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
@@ -6170,7 +6305,7 @@
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>C116:F116</t>
+          <t>C127:F127</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -6200,7 +6335,7 @@
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>C117:F117</t>
+          <t>C128:F128</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
@@ -6230,7 +6365,7 @@
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>C118:F118</t>
+          <t>C129:F129</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
@@ -6260,7 +6395,7 @@
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>B120:F120</t>
+          <t>B131:F131</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
@@ -6290,7 +6425,7 @@
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>B121:F121</t>
+          <t>B132:F132</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -6836,6 +6971,186 @@
       <c r="F125" s="11" t="inlineStr">
         <is>
           <t>cash_ending_from_flows</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="11" t="n">
+        <v>139</v>
+      </c>
+      <c r="B126" s="11" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="C126" s="11" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D126" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>B107:F107</t>
+        </is>
+      </c>
+      <c r="F126" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="11" t="n">
+        <v>140</v>
+      </c>
+      <c r="B127" s="11" t="inlineStr">
+        <is>
+          <t>Reported operating margin</t>
+        </is>
+      </c>
+      <c r="C127" s="11" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D127" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>B108:F108</t>
+        </is>
+      </c>
+      <c r="F127" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="11" t="n">
+        <v>141</v>
+      </c>
+      <c r="B128" s="11" t="inlineStr">
+        <is>
+          <t>Net operating expense burden</t>
+        </is>
+      </c>
+      <c r="C128" s="11" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D128" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>B109:F109</t>
+        </is>
+      </c>
+      <c r="F128" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="11" t="n">
+        <v>142</v>
+      </c>
+      <c r="B129" s="11" t="inlineStr">
+        <is>
+          <t>Change in gross margin</t>
+        </is>
+      </c>
+      <c r="C129" s="11" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>C110:F110</t>
+        </is>
+      </c>
+      <c r="F129" s="11" t="inlineStr">
+        <is>
+          <t>gross_margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="11" t="n">
+        <v>143</v>
+      </c>
+      <c r="B130" s="11" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden</t>
+        </is>
+      </c>
+      <c r="C130" s="11" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D130" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>C111:F111</t>
+        </is>
+      </c>
+      <c r="F130" s="11" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="11" t="n">
+        <v>144</v>
+      </c>
+      <c r="B131" s="11" t="inlineStr">
+        <is>
+          <t>Reconstructed change in reported operating margin</t>
+        </is>
+      </c>
+      <c r="C131" s="11" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D131" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>C112:F112</t>
+        </is>
+      </c>
+      <c r="F131" s="11" t="inlineStr">
+        <is>
+          <t>gross_margin_change, net_operating_expense_burden_change</t>
         </is>
       </c>
     </row>
@@ -7853,7 +8168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S522"/>
+  <dimension ref="A1:S549"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38164,11 +38479,11 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>C105</t>
+          <t>C116</t>
         </is>
       </c>
       <c r="I382">
-        <f>C104-B104</f>
+        <f>C115-B115</f>
         <v/>
       </c>
       <c r="J382" t="n">
@@ -38240,11 +38555,11 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D116</t>
         </is>
       </c>
       <c r="I383">
-        <f>D104-C104</f>
+        <f>D115-C115</f>
         <v/>
       </c>
       <c r="J383" t="n">
@@ -38316,11 +38631,11 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>E105</t>
+          <t>E116</t>
         </is>
       </c>
       <c r="I384">
-        <f>E104-D104</f>
+        <f>E115-D115</f>
         <v/>
       </c>
       <c r="J384" t="n">
@@ -38392,11 +38707,11 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>F105</t>
+          <t>F116</t>
         </is>
       </c>
       <c r="I385">
-        <f>F104-E104</f>
+        <f>F115-E115</f>
         <v/>
       </c>
       <c r="J385" t="n">
@@ -38468,11 +38783,11 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>C106</t>
+          <t>C117</t>
         </is>
       </c>
       <c r="I386">
-        <f>IF(B104=0,NA(),C104/B104-1)</f>
+        <f>IF(B115=0,NA(),C115/B115-1)</f>
         <v/>
       </c>
       <c r="J386" t="n">
@@ -38549,11 +38864,11 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>D106</t>
+          <t>D117</t>
         </is>
       </c>
       <c r="I387">
-        <f>IF(C104=0,NA(),D104/C104-1)</f>
+        <f>IF(C115=0,NA(),D115/C115-1)</f>
         <v/>
       </c>
       <c r="J387" t="n">
@@ -38630,11 +38945,11 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>E106</t>
+          <t>E117</t>
         </is>
       </c>
       <c r="I388">
-        <f>IF(D104=0,NA(),E104/D104-1)</f>
+        <f>IF(D115=0,NA(),E115/D115-1)</f>
         <v/>
       </c>
       <c r="J388" t="n">
@@ -38711,11 +39026,11 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>F106</t>
+          <t>F117</t>
         </is>
       </c>
       <c r="I389">
-        <f>IF(E104=0,NA(),F104/E104-1)</f>
+        <f>IF(E115=0,NA(),F115/E115-1)</f>
         <v/>
       </c>
       <c r="J389" t="n">
@@ -38792,11 +39107,11 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>C107</t>
+          <t>C118</t>
         </is>
       </c>
       <c r="I390">
-        <f>(B104+C104)/2</f>
+        <f>(B115+C115)/2</f>
         <v/>
       </c>
       <c r="J390" t="n">
@@ -38868,11 +39183,11 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D118</t>
         </is>
       </c>
       <c r="I391">
-        <f>(C104+D104)/2</f>
+        <f>(C115+D115)/2</f>
         <v/>
       </c>
       <c r="J391" t="n">
@@ -38944,11 +39259,11 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>E107</t>
+          <t>E118</t>
         </is>
       </c>
       <c r="I392">
-        <f>(D104+E104)/2</f>
+        <f>(D115+E115)/2</f>
         <v/>
       </c>
       <c r="J392" t="n">
@@ -39020,11 +39335,11 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>F107</t>
+          <t>F118</t>
         </is>
       </c>
       <c r="I393">
-        <f>(E104+F104)/2</f>
+        <f>(E115+F115)/2</f>
         <v/>
       </c>
       <c r="J393" t="n">
@@ -39096,11 +39411,11 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>C108</t>
+          <t>C119</t>
         </is>
       </c>
       <c r="I394">
-        <f>IF('Condensed Financials'!C44=0,NA(),C107/'Condensed Financials'!C44)</f>
+        <f>IF('Condensed Financials'!C44=0,NA(),C118/'Condensed Financials'!C44)</f>
         <v/>
       </c>
       <c r="J394" t="n">
@@ -39177,11 +39492,11 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D119</t>
         </is>
       </c>
       <c r="I395">
-        <f>IF('Condensed Financials'!D44=0,NA(),D107/'Condensed Financials'!D44)</f>
+        <f>IF('Condensed Financials'!D44=0,NA(),D118/'Condensed Financials'!D44)</f>
         <v/>
       </c>
       <c r="J395" t="n">
@@ -39258,11 +39573,11 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>E108</t>
+          <t>E119</t>
         </is>
       </c>
       <c r="I396">
-        <f>IF('Condensed Financials'!E44=0,NA(),E107/'Condensed Financials'!E44)</f>
+        <f>IF('Condensed Financials'!E44=0,NA(),E118/'Condensed Financials'!E44)</f>
         <v/>
       </c>
       <c r="J396" t="n">
@@ -39339,11 +39654,11 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>F108</t>
+          <t>F119</t>
         </is>
       </c>
       <c r="I397">
-        <f>IF('Condensed Financials'!F44=0,NA(),F107/'Condensed Financials'!F44)</f>
+        <f>IF('Condensed Financials'!F44=0,NA(),F118/'Condensed Financials'!F44)</f>
         <v/>
       </c>
       <c r="J397" t="n">
@@ -39420,11 +39735,11 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>C110</t>
+          <t>C121</t>
         </is>
       </c>
       <c r="I398">
-        <f>C109-B109</f>
+        <f>C120-B120</f>
         <v/>
       </c>
       <c r="J398" t="n">
@@ -39496,11 +39811,11 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>D110</t>
+          <t>D121</t>
         </is>
       </c>
       <c r="I399">
-        <f>D109-C109</f>
+        <f>D120-C120</f>
         <v/>
       </c>
       <c r="J399" t="n">
@@ -39572,11 +39887,11 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>E110</t>
+          <t>E121</t>
         </is>
       </c>
       <c r="I400">
-        <f>E109-D109</f>
+        <f>E120-D120</f>
         <v/>
       </c>
       <c r="J400" t="n">
@@ -39648,11 +39963,11 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>F110</t>
+          <t>F121</t>
         </is>
       </c>
       <c r="I401">
-        <f>F109-E109</f>
+        <f>F120-E120</f>
         <v/>
       </c>
       <c r="J401" t="n">
@@ -39724,11 +40039,11 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>C111</t>
+          <t>C122</t>
         </is>
       </c>
       <c r="I402">
-        <f>IF(B109=0,NA(),C109/B109-1)</f>
+        <f>IF(B120=0,NA(),C120/B120-1)</f>
         <v/>
       </c>
       <c r="J402" t="n">
@@ -39805,11 +40120,11 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>D111</t>
+          <t>D122</t>
         </is>
       </c>
       <c r="I403">
-        <f>IF(C109=0,NA(),D109/C109-1)</f>
+        <f>IF(C120=0,NA(),D120/C120-1)</f>
         <v/>
       </c>
       <c r="J403" t="n">
@@ -39886,11 +40201,11 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>E111</t>
+          <t>E122</t>
         </is>
       </c>
       <c r="I404">
-        <f>IF(D109=0,NA(),E109/D109-1)</f>
+        <f>IF(D120=0,NA(),E120/D120-1)</f>
         <v/>
       </c>
       <c r="J404" t="n">
@@ -39967,11 +40282,11 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>F111</t>
+          <t>F122</t>
         </is>
       </c>
       <c r="I405">
-        <f>IF(E109=0,NA(),F109/E109-1)</f>
+        <f>IF(E120=0,NA(),F120/E120-1)</f>
         <v/>
       </c>
       <c r="J405" t="n">
@@ -40048,11 +40363,11 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>C112</t>
+          <t>C123</t>
         </is>
       </c>
       <c r="I406">
-        <f>(B109+C109)/2</f>
+        <f>(B120+C120)/2</f>
         <v/>
       </c>
       <c r="J406" t="n">
@@ -40124,11 +40439,11 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>D112</t>
+          <t>D123</t>
         </is>
       </c>
       <c r="I407">
-        <f>(C109+D109)/2</f>
+        <f>(C120+D120)/2</f>
         <v/>
       </c>
       <c r="J407" t="n">
@@ -40200,11 +40515,11 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>E112</t>
+          <t>E123</t>
         </is>
       </c>
       <c r="I408">
-        <f>(D109+E109)/2</f>
+        <f>(D120+E120)/2</f>
         <v/>
       </c>
       <c r="J408" t="n">
@@ -40276,11 +40591,11 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>F112</t>
+          <t>F123</t>
         </is>
       </c>
       <c r="I409">
-        <f>(E109+F109)/2</f>
+        <f>(E120+F120)/2</f>
         <v/>
       </c>
       <c r="J409" t="n">
@@ -40352,11 +40667,11 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>C113</t>
+          <t>C124</t>
         </is>
       </c>
       <c r="I410">
-        <f>IF('Condensed Financials'!C44=0,NA(),C112/'Condensed Financials'!C44)</f>
+        <f>IF('Condensed Financials'!C44=0,NA(),C123/'Condensed Financials'!C44)</f>
         <v/>
       </c>
       <c r="J410" t="n">
@@ -40433,11 +40748,11 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>D113</t>
+          <t>D124</t>
         </is>
       </c>
       <c r="I411">
-        <f>IF('Condensed Financials'!D44=0,NA(),D112/'Condensed Financials'!D44)</f>
+        <f>IF('Condensed Financials'!D44=0,NA(),D123/'Condensed Financials'!D44)</f>
         <v/>
       </c>
       <c r="J411" t="n">
@@ -40514,11 +40829,11 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>E113</t>
+          <t>E124</t>
         </is>
       </c>
       <c r="I412">
-        <f>IF('Condensed Financials'!E44=0,NA(),E112/'Condensed Financials'!E44)</f>
+        <f>IF('Condensed Financials'!E44=0,NA(),E123/'Condensed Financials'!E44)</f>
         <v/>
       </c>
       <c r="J412" t="n">
@@ -40595,11 +40910,11 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>F113</t>
+          <t>F124</t>
         </is>
       </c>
       <c r="I413">
-        <f>IF('Condensed Financials'!F44=0,NA(),F112/'Condensed Financials'!F44)</f>
+        <f>IF('Condensed Financials'!F44=0,NA(),F123/'Condensed Financials'!F44)</f>
         <v/>
       </c>
       <c r="J413" t="n">
@@ -40676,11 +40991,11 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>C115</t>
+          <t>C126</t>
         </is>
       </c>
       <c r="I414">
-        <f>C114-B114</f>
+        <f>C125-B125</f>
         <v/>
       </c>
       <c r="J414" t="n">
@@ -40752,11 +41067,11 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D126</t>
         </is>
       </c>
       <c r="I415">
-        <f>D114-C114</f>
+        <f>D125-C125</f>
         <v/>
       </c>
       <c r="J415" t="n">
@@ -40828,11 +41143,11 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>E115</t>
+          <t>E126</t>
         </is>
       </c>
       <c r="I416">
-        <f>E114-D114</f>
+        <f>E125-D125</f>
         <v/>
       </c>
       <c r="J416" t="n">
@@ -40904,11 +41219,11 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>F115</t>
+          <t>F126</t>
         </is>
       </c>
       <c r="I417">
-        <f>F114-E114</f>
+        <f>F125-E125</f>
         <v/>
       </c>
       <c r="J417" t="n">
@@ -40980,11 +41295,11 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>C116</t>
+          <t>C127</t>
         </is>
       </c>
       <c r="I418">
-        <f>IF(B114=0,NA(),C114/B114-1)</f>
+        <f>IF(B125=0,NA(),C125/B125-1)</f>
         <v/>
       </c>
       <c r="J418" t="n">
@@ -41061,11 +41376,11 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>D116</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I419">
-        <f>IF(C114=0,NA(),D114/C114-1)</f>
+        <f>IF(C125=0,NA(),D125/C125-1)</f>
         <v/>
       </c>
       <c r="J419" t="n">
@@ -41142,11 +41457,11 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>E116</t>
+          <t>E127</t>
         </is>
       </c>
       <c r="I420">
-        <f>IF(D114=0,NA(),E114/D114-1)</f>
+        <f>IF(D125=0,NA(),E125/D125-1)</f>
         <v/>
       </c>
       <c r="J420" t="n">
@@ -41223,11 +41538,11 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>F116</t>
+          <t>F127</t>
         </is>
       </c>
       <c r="I421">
-        <f>IF(E114=0,NA(),F114/E114-1)</f>
+        <f>IF(E125=0,NA(),F125/E125-1)</f>
         <v/>
       </c>
       <c r="J421" t="n">
@@ -41304,11 +41619,11 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>C117</t>
+          <t>C128</t>
         </is>
       </c>
       <c r="I422">
-        <f>(B114+C114)/2</f>
+        <f>(B125+C125)/2</f>
         <v/>
       </c>
       <c r="J422" t="n">
@@ -41380,11 +41695,11 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>D117</t>
+          <t>D128</t>
         </is>
       </c>
       <c r="I423">
-        <f>(C114+D114)/2</f>
+        <f>(C125+D125)/2</f>
         <v/>
       </c>
       <c r="J423" t="n">
@@ -41456,11 +41771,11 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>E117</t>
+          <t>E128</t>
         </is>
       </c>
       <c r="I424">
-        <f>(D114+E114)/2</f>
+        <f>(D125+E125)/2</f>
         <v/>
       </c>
       <c r="J424" t="n">
@@ -41532,11 +41847,11 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>F117</t>
+          <t>F128</t>
         </is>
       </c>
       <c r="I425">
-        <f>(E114+F114)/2</f>
+        <f>(E125+F125)/2</f>
         <v/>
       </c>
       <c r="J425" t="n">
@@ -41608,11 +41923,11 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>C118</t>
+          <t>C129</t>
         </is>
       </c>
       <c r="I426">
-        <f>IF('Condensed Financials'!C44=0,NA(),C117/'Condensed Financials'!C44)</f>
+        <f>IF('Condensed Financials'!C44=0,NA(),C128/'Condensed Financials'!C44)</f>
         <v/>
       </c>
       <c r="J426" t="n">
@@ -41689,11 +42004,11 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>D118</t>
+          <t>D129</t>
         </is>
       </c>
       <c r="I427">
-        <f>IF('Condensed Financials'!D44=0,NA(),D117/'Condensed Financials'!D44)</f>
+        <f>IF('Condensed Financials'!D44=0,NA(),D128/'Condensed Financials'!D44)</f>
         <v/>
       </c>
       <c r="J427" t="n">
@@ -41770,11 +42085,11 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>E118</t>
+          <t>E129</t>
         </is>
       </c>
       <c r="I428">
-        <f>IF('Condensed Financials'!E44=0,NA(),E117/'Condensed Financials'!E44)</f>
+        <f>IF('Condensed Financials'!E44=0,NA(),E128/'Condensed Financials'!E44)</f>
         <v/>
       </c>
       <c r="J428" t="n">
@@ -41851,11 +42166,11 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>F118</t>
+          <t>F129</t>
         </is>
       </c>
       <c r="I429">
-        <f>IF('Condensed Financials'!F44=0,NA(),F117/'Condensed Financials'!F44)</f>
+        <f>IF('Condensed Financials'!F44=0,NA(),F128/'Condensed Financials'!F44)</f>
         <v/>
       </c>
       <c r="J429" t="n">
@@ -41932,11 +42247,11 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>B120</t>
+          <t>B131</t>
         </is>
       </c>
       <c r="I430">
-        <f>-B119</f>
+        <f>-B130</f>
         <v/>
       </c>
       <c r="J430" t="n">
@@ -42008,11 +42323,11 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>C120</t>
+          <t>C131</t>
         </is>
       </c>
       <c r="I431">
-        <f>-C119</f>
+        <f>-C130</f>
         <v/>
       </c>
       <c r="J431" t="n">
@@ -42084,11 +42399,11 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>D120</t>
+          <t>D131</t>
         </is>
       </c>
       <c r="I432">
-        <f>-D119</f>
+        <f>-D130</f>
         <v/>
       </c>
       <c r="J432" t="n">
@@ -42160,11 +42475,11 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>E120</t>
+          <t>E131</t>
         </is>
       </c>
       <c r="I433">
-        <f>-E119</f>
+        <f>-E130</f>
         <v/>
       </c>
       <c r="J433" t="n">
@@ -42236,11 +42551,11 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>F120</t>
+          <t>F131</t>
         </is>
       </c>
       <c r="I434">
-        <f>-F119</f>
+        <f>-F130</f>
         <v/>
       </c>
       <c r="J434" t="n">
@@ -42312,11 +42627,11 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>B121</t>
+          <t>B132</t>
         </is>
       </c>
       <c r="I435">
-        <f>IF('Condensed Financials'!B44=0,NA(),B120/'Condensed Financials'!B44)</f>
+        <f>IF('Condensed Financials'!B44=0,NA(),B131/'Condensed Financials'!B44)</f>
         <v/>
       </c>
       <c r="J435" t="n">
@@ -42393,11 +42708,11 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>C121</t>
+          <t>C132</t>
         </is>
       </c>
       <c r="I436">
-        <f>IF('Condensed Financials'!C44=0,NA(),C120/'Condensed Financials'!C44)</f>
+        <f>IF('Condensed Financials'!C44=0,NA(),C131/'Condensed Financials'!C44)</f>
         <v/>
       </c>
       <c r="J436" t="n">
@@ -42474,11 +42789,11 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>D121</t>
+          <t>D132</t>
         </is>
       </c>
       <c r="I437">
-        <f>IF('Condensed Financials'!D44=0,NA(),D120/'Condensed Financials'!D44)</f>
+        <f>IF('Condensed Financials'!D44=0,NA(),D131/'Condensed Financials'!D44)</f>
         <v/>
       </c>
       <c r="J437" t="n">
@@ -42555,11 +42870,11 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>E121</t>
+          <t>E132</t>
         </is>
       </c>
       <c r="I438">
-        <f>IF('Condensed Financials'!E44=0,NA(),E120/'Condensed Financials'!E44)</f>
+        <f>IF('Condensed Financials'!E44=0,NA(),E131/'Condensed Financials'!E44)</f>
         <v/>
       </c>
       <c r="J438" t="n">
@@ -42636,11 +42951,11 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>F121</t>
+          <t>F132</t>
         </is>
       </c>
       <c r="I439">
-        <f>IF('Condensed Financials'!F44=0,NA(),F120/'Condensed Financials'!F44)</f>
+        <f>IF('Condensed Financials'!F44=0,NA(),F131/'Condensed Financials'!F44)</f>
         <v/>
       </c>
       <c r="J439" t="n">
@@ -49219,6 +49534,2118 @@
         <v>4</v>
       </c>
       <c r="S522" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>gross_margin__20210831</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>522</v>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Gross margin = reported gross profit / revenue. Zero revenue is undefined (#N/A). Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>reported_margin.gross_margin.2021-08-31</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>B107</t>
+        </is>
+      </c>
+      <c r="I523">
+        <f>IF(B104=0,NA(),B105/B104)</f>
+        <v/>
+      </c>
+      <c r="J523" t="n">
+        <v>0.5034969657645223</v>
+      </c>
+      <c r="K523" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M523" t="inlineStr">
+        <is>
+          <t>Gross margin = reported gross profit / revenue.|Zero revenue yields the undefined-ratio result.|Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="O523" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P523" t="inlineStr">
+        <is>
+          <t>gross_margin</t>
+        </is>
+      </c>
+      <c r="Q523" t="n">
+        <v>139</v>
+      </c>
+      <c r="R523" t="n">
+        <v>0</v>
+      </c>
+      <c r="S523" t="inlineStr">
+        <is>
+          <t>2021-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>gross_margin__20220831</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>523</v>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Gross margin = reported gross profit / revenue. Zero revenue is undefined (#N/A). Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>reported_margin.gross_margin.2022-08-31</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>C107</t>
+        </is>
+      </c>
+      <c r="I524">
+        <f>IF(C104=0,NA(),C105/C104)</f>
+        <v/>
+      </c>
+      <c r="J524" t="n">
+        <v>0.5244654564164786</v>
+      </c>
+      <c r="K524" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M524" t="inlineStr">
+        <is>
+          <t>Gross margin = reported gross profit / revenue.|Zero revenue yields the undefined-ratio result.|Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="O524" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P524" t="inlineStr">
+        <is>
+          <t>gross_margin</t>
+        </is>
+      </c>
+      <c r="Q524" t="n">
+        <v>139</v>
+      </c>
+      <c r="R524" t="n">
+        <v>1</v>
+      </c>
+      <c r="S524" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>gross_margin__20230831</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>524</v>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Gross margin = reported gross profit / revenue. Zero revenue is undefined (#N/A). Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>reported_margin.gross_margin.2023-08-31</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="I525">
+        <f>IF(D104=0,NA(),D105/D104)</f>
+        <v/>
+      </c>
+      <c r="J525" t="n">
+        <v>0.5191868448761403</v>
+      </c>
+      <c r="K525" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M525" t="inlineStr">
+        <is>
+          <t>Gross margin = reported gross profit / revenue.|Zero revenue yields the undefined-ratio result.|Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="O525" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P525" t="inlineStr">
+        <is>
+          <t>gross_margin</t>
+        </is>
+      </c>
+      <c r="Q525" t="n">
+        <v>139</v>
+      </c>
+      <c r="R525" t="n">
+        <v>2</v>
+      </c>
+      <c r="S525" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>gross_margin__20240831</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>525</v>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Gross margin = reported gross profit / revenue. Zero revenue is undefined (#N/A). Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>reported_margin.gross_margin.2024-08-31</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>E107</t>
+        </is>
+      </c>
+      <c r="I526">
+        <f>IF(E104=0,NA(),E105/E104)</f>
+        <v/>
+      </c>
+      <c r="J526" t="n">
+        <v>0.5390333123270689</v>
+      </c>
+      <c r="K526" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M526" t="inlineStr">
+        <is>
+          <t>Gross margin = reported gross profit / revenue.|Zero revenue yields the undefined-ratio result.|Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="O526" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P526" t="inlineStr">
+        <is>
+          <t>gross_margin</t>
+        </is>
+      </c>
+      <c r="Q526" t="n">
+        <v>139</v>
+      </c>
+      <c r="R526" t="n">
+        <v>3</v>
+      </c>
+      <c r="S526" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>gross_margin__20250831</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>526</v>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Gross margin = reported gross profit / revenue. Zero revenue is undefined (#N/A). Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>reported_margin.gross_margin.2025-08-31</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>F107</t>
+        </is>
+      </c>
+      <c r="I527">
+        <f>IF(F104=0,NA(),F105/F104)</f>
+        <v/>
+      </c>
+      <c r="J527" t="n">
+        <v>0.5378141524034866</v>
+      </c>
+      <c r="K527" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M527" t="inlineStr">
+        <is>
+          <t>Gross margin = reported gross profit / revenue.|Zero revenue yields the undefined-ratio result.|Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="O527" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P527" t="inlineStr">
+        <is>
+          <t>gross_margin</t>
+        </is>
+      </c>
+      <c r="Q527" t="n">
+        <v>139</v>
+      </c>
+      <c r="R527" t="n">
+        <v>4</v>
+      </c>
+      <c r="S527" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>reported_operating_margin__20210831</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>527</v>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Reported operating margin</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Reported operating margin = reported operating profit / revenue. Distinct from BAV NOPAT margin; not normalized earnings. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>reported_margin.reported_operating_margin.2021-08-31</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>B108</t>
+        </is>
+      </c>
+      <c r="I528">
+        <f>IF(B104=0,NA(),B106/B104)</f>
+        <v/>
+      </c>
+      <c r="J528" t="n">
+        <v>0.1167425850636102</v>
+      </c>
+      <c r="K528" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M528" t="inlineStr">
+        <is>
+          <t>Reported operating margin = reported operating profit / revenue.|Keep reported operating margin distinct from BAV NOPAT margin.|Do not treat this as normalized earnings.</t>
+        </is>
+      </c>
+      <c r="O528" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P528" t="inlineStr">
+        <is>
+          <t>reported_operating_margin</t>
+        </is>
+      </c>
+      <c r="Q528" t="n">
+        <v>140</v>
+      </c>
+      <c r="R528" t="n">
+        <v>0</v>
+      </c>
+      <c r="S528" t="inlineStr">
+        <is>
+          <t>2021-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>reported_operating_margin__20220831</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>528</v>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Reported operating margin</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Reported operating margin = reported operating profit / revenue. Distinct from BAV NOPAT margin; not normalized earnings. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>reported_margin.reported_operating_margin.2022-08-31</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>C108</t>
+        </is>
+      </c>
+      <c r="I529">
+        <f>IF(C104=0,NA(),C106/C104)</f>
+        <v/>
+      </c>
+      <c r="J529" t="n">
+        <v>0.1292087077521314</v>
+      </c>
+      <c r="K529" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M529" t="inlineStr">
+        <is>
+          <t>Reported operating margin = reported operating profit / revenue.|Keep reported operating margin distinct from BAV NOPAT margin.|Do not treat this as normalized earnings.</t>
+        </is>
+      </c>
+      <c r="O529" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P529" t="inlineStr">
+        <is>
+          <t>reported_operating_margin</t>
+        </is>
+      </c>
+      <c r="Q529" t="n">
+        <v>140</v>
+      </c>
+      <c r="R529" t="n">
+        <v>1</v>
+      </c>
+      <c r="S529" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>reported_operating_margin__20230831</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>529</v>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Reported operating margin</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Reported operating margin = reported operating profit / revenue. Distinct from BAV NOPAT margin; not normalized earnings. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>reported_margin.reported_operating_margin.2023-08-31</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I530">
+        <f>IF(D104=0,NA(),D106/D104)</f>
+        <v/>
+      </c>
+      <c r="J530" t="n">
+        <v>0.1377488336585872</v>
+      </c>
+      <c r="K530" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M530" t="inlineStr">
+        <is>
+          <t>Reported operating margin = reported operating profit / revenue.|Keep reported operating margin distinct from BAV NOPAT margin.|Do not treat this as normalized earnings.</t>
+        </is>
+      </c>
+      <c r="O530" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P530" t="inlineStr">
+        <is>
+          <t>reported_operating_margin</t>
+        </is>
+      </c>
+      <c r="Q530" t="n">
+        <v>140</v>
+      </c>
+      <c r="R530" t="n">
+        <v>2</v>
+      </c>
+      <c r="S530" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>reported_operating_margin__20240831</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>530</v>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Reported operating margin</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Reported operating margin = reported operating profit / revenue. Distinct from BAV NOPAT margin; not normalized earnings. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>reported_margin.reported_operating_margin.2024-08-31</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>E108</t>
+        </is>
+      </c>
+      <c r="I531">
+        <f>IF(E104=0,NA(),E106/E104)</f>
+        <v/>
+      </c>
+      <c r="J531" t="n">
+        <v>0.1613822379790685</v>
+      </c>
+      <c r="K531" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M531" t="inlineStr">
+        <is>
+          <t>Reported operating margin = reported operating profit / revenue.|Keep reported operating margin distinct from BAV NOPAT margin.|Do not treat this as normalized earnings.</t>
+        </is>
+      </c>
+      <c r="O531" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P531" t="inlineStr">
+        <is>
+          <t>reported_operating_margin</t>
+        </is>
+      </c>
+      <c r="Q531" t="n">
+        <v>140</v>
+      </c>
+      <c r="R531" t="n">
+        <v>3</v>
+      </c>
+      <c r="S531" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>reported_operating_margin__20250831</t>
+        </is>
+      </c>
+      <c r="B532" t="n">
+        <v>531</v>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Reported operating margin</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Reported operating margin = reported operating profit / revenue. Distinct from BAV NOPAT margin; not normalized earnings. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>reported_margin.reported_operating_margin.2025-08-31</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>F108</t>
+        </is>
+      </c>
+      <c r="I532">
+        <f>IF(F104=0,NA(),F106/F104)</f>
+        <v/>
+      </c>
+      <c r="J532" t="n">
+        <v>0.1659339887000267</v>
+      </c>
+      <c r="K532" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M532" t="inlineStr">
+        <is>
+          <t>Reported operating margin = reported operating profit / revenue.|Keep reported operating margin distinct from BAV NOPAT margin.|Do not treat this as normalized earnings.</t>
+        </is>
+      </c>
+      <c r="O532" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P532" t="inlineStr">
+        <is>
+          <t>reported_operating_margin</t>
+        </is>
+      </c>
+      <c r="Q532" t="n">
+        <v>140</v>
+      </c>
+      <c r="R532" t="n">
+        <v>4</v>
+      </c>
+      <c r="S532" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden__20210831</t>
+        </is>
+      </c>
+      <c r="B533" t="n">
+        <v>532</v>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Net operating expense burden</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Net operating expense burden = (gross profit − operating profit) / revenue. That difference includes net intervening operating items; it is not necessarily SG&amp;A. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>reported_margin.net_operating_expense_burden.2021-08-31</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>B109</t>
+        </is>
+      </c>
+      <c r="I533">
+        <f>IF(B104=0,NA(),(B105-B106)/B104)</f>
+        <v/>
+      </c>
+      <c r="J533" t="n">
+        <v>0.3867543807009122</v>
+      </c>
+      <c r="K533" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M533" t="inlineStr">
+        <is>
+          <t>Net operating expense burden = (gross profit − operating profit) / revenue.|Gross profit minus operating profit includes net intervening operating items; it is not necessarily SG&amp;A.|Zero revenue yields the undefined-ratio result.</t>
+        </is>
+      </c>
+      <c r="O533" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P533" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden</t>
+        </is>
+      </c>
+      <c r="Q533" t="n">
+        <v>141</v>
+      </c>
+      <c r="R533" t="n">
+        <v>0</v>
+      </c>
+      <c r="S533" t="inlineStr">
+        <is>
+          <t>2021-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden__20220831</t>
+        </is>
+      </c>
+      <c r="B534" t="n">
+        <v>533</v>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Net operating expense burden</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Net operating expense burden = (gross profit − operating profit) / revenue. That difference includes net intervening operating items; it is not necessarily SG&amp;A. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>reported_margin.net_operating_expense_burden.2022-08-31</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>C109</t>
+        </is>
+      </c>
+      <c r="I534">
+        <f>IF(C104=0,NA(),(C105-C106)/C104)</f>
+        <v/>
+      </c>
+      <c r="J534" t="n">
+        <v>0.3952567486643472</v>
+      </c>
+      <c r="K534" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M534" t="inlineStr">
+        <is>
+          <t>Net operating expense burden = (gross profit − operating profit) / revenue.|Gross profit minus operating profit includes net intervening operating items; it is not necessarily SG&amp;A.|Zero revenue yields the undefined-ratio result.</t>
+        </is>
+      </c>
+      <c r="O534" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P534" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden</t>
+        </is>
+      </c>
+      <c r="Q534" t="n">
+        <v>141</v>
+      </c>
+      <c r="R534" t="n">
+        <v>1</v>
+      </c>
+      <c r="S534" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden__20230831</t>
+        </is>
+      </c>
+      <c r="B535" t="n">
+        <v>534</v>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Net operating expense burden</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Net operating expense burden = (gross profit − operating profit) / revenue. That difference includes net intervening operating items; it is not necessarily SG&amp;A. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>reported_margin.net_operating_expense_burden.2023-08-31</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I535">
+        <f>IF(D104=0,NA(),(D105-D106)/D104)</f>
+        <v/>
+      </c>
+      <c r="J535" t="n">
+        <v>0.3814380112175531</v>
+      </c>
+      <c r="K535" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M535" t="inlineStr">
+        <is>
+          <t>Net operating expense burden = (gross profit − operating profit) / revenue.|Gross profit minus operating profit includes net intervening operating items; it is not necessarily SG&amp;A.|Zero revenue yields the undefined-ratio result.</t>
+        </is>
+      </c>
+      <c r="O535" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P535" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden</t>
+        </is>
+      </c>
+      <c r="Q535" t="n">
+        <v>141</v>
+      </c>
+      <c r="R535" t="n">
+        <v>2</v>
+      </c>
+      <c r="S535" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden__20240831</t>
+        </is>
+      </c>
+      <c r="B536" t="n">
+        <v>535</v>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Net operating expense burden</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Net operating expense burden = (gross profit − operating profit) / revenue. That difference includes net intervening operating items; it is not necessarily SG&amp;A. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>reported_margin.net_operating_expense_burden.2024-08-31</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>E109</t>
+        </is>
+      </c>
+      <c r="I536">
+        <f>IF(E104=0,NA(),(E105-E106)/E104)</f>
+        <v/>
+      </c>
+      <c r="J536" t="n">
+        <v>0.3776510743480003</v>
+      </c>
+      <c r="K536" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M536" t="inlineStr">
+        <is>
+          <t>Net operating expense burden = (gross profit − operating profit) / revenue.|Gross profit minus operating profit includes net intervening operating items; it is not necessarily SG&amp;A.|Zero revenue yields the undefined-ratio result.</t>
+        </is>
+      </c>
+      <c r="O536" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P536" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden</t>
+        </is>
+      </c>
+      <c r="Q536" t="n">
+        <v>141</v>
+      </c>
+      <c r="R536" t="n">
+        <v>3</v>
+      </c>
+      <c r="S536" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden__20250831</t>
+        </is>
+      </c>
+      <c r="B537" t="n">
+        <v>536</v>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Net operating expense burden</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Net operating expense burden = (gross profit − operating profit) / revenue. That difference includes net intervening operating items; it is not necessarily SG&amp;A. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>reported_margin.net_operating_expense_burden.2025-08-31</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>F109</t>
+        </is>
+      </c>
+      <c r="I537">
+        <f>IF(F104=0,NA(),(F105-F106)/F104)</f>
+        <v/>
+      </c>
+      <c r="J537" t="n">
+        <v>0.3718801637034599</v>
+      </c>
+      <c r="K537" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M537" t="inlineStr">
+        <is>
+          <t>Net operating expense burden = (gross profit − operating profit) / revenue.|Gross profit minus operating profit includes net intervening operating items; it is not necessarily SG&amp;A.|Zero revenue yields the undefined-ratio result.</t>
+        </is>
+      </c>
+      <c r="O537" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P537" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden</t>
+        </is>
+      </c>
+      <c r="Q537" t="n">
+        <v>141</v>
+      </c>
+      <c r="R537" t="n">
+        <v>4</v>
+      </c>
+      <c r="S537" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>gross_margin_change__20220831</t>
+        </is>
+      </c>
+      <c r="B538" t="n">
+        <v>537</v>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Change in gross margin</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Change in gross margin is a percentage-point movement: current gross margin minus prior gross margin. Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>reported_margin.gross_margin_change.2022-08-31</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>C110</t>
+        </is>
+      </c>
+      <c r="I538">
+        <f>C107-B107</f>
+        <v/>
+      </c>
+      <c r="J538" t="n">
+        <v>0.02096849065195627</v>
+      </c>
+      <c r="K538" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L538" t="inlineStr">
+        <is>
+          <t>gross_margin__20220831,gross_margin__20210831</t>
+        </is>
+      </c>
+      <c r="M538" t="inlineStr">
+        <is>
+          <t>Change in gross margin = current gross margin − prior gross margin.|This is a percentage-point movement, not a causal explanation.|Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="O538" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P538" t="inlineStr">
+        <is>
+          <t>gross_margin_change</t>
+        </is>
+      </c>
+      <c r="Q538" t="n">
+        <v>142</v>
+      </c>
+      <c r="R538" t="n">
+        <v>1</v>
+      </c>
+      <c r="S538" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>gross_margin_change__20230831</t>
+        </is>
+      </c>
+      <c r="B539" t="n">
+        <v>538</v>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Change in gross margin</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Change in gross margin is a percentage-point movement: current gross margin minus prior gross margin. Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>reported_margin.gross_margin_change.2023-08-31</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>D110</t>
+        </is>
+      </c>
+      <c r="I539">
+        <f>D107-C107</f>
+        <v/>
+      </c>
+      <c r="J539" t="n">
+        <v>-0.005278611540338263</v>
+      </c>
+      <c r="K539" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L539" t="inlineStr">
+        <is>
+          <t>gross_margin__20230831,gross_margin__20220831</t>
+        </is>
+      </c>
+      <c r="M539" t="inlineStr">
+        <is>
+          <t>Change in gross margin = current gross margin − prior gross margin.|This is a percentage-point movement, not a causal explanation.|Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="O539" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P539" t="inlineStr">
+        <is>
+          <t>gross_margin_change</t>
+        </is>
+      </c>
+      <c r="Q539" t="n">
+        <v>142</v>
+      </c>
+      <c r="R539" t="n">
+        <v>2</v>
+      </c>
+      <c r="S539" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>gross_margin_change__20240831</t>
+        </is>
+      </c>
+      <c r="B540" t="n">
+        <v>539</v>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Change in gross margin</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Change in gross margin is a percentage-point movement: current gross margin minus prior gross margin. Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>reported_margin.gross_margin_change.2024-08-31</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>E110</t>
+        </is>
+      </c>
+      <c r="I540">
+        <f>E107-D107</f>
+        <v/>
+      </c>
+      <c r="J540" t="n">
+        <v>0.01984646745092855</v>
+      </c>
+      <c r="K540" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L540" t="inlineStr">
+        <is>
+          <t>gross_margin__20240831,gross_margin__20230831</t>
+        </is>
+      </c>
+      <c r="M540" t="inlineStr">
+        <is>
+          <t>Change in gross margin = current gross margin − prior gross margin.|This is a percentage-point movement, not a causal explanation.|Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="O540" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P540" t="inlineStr">
+        <is>
+          <t>gross_margin_change</t>
+        </is>
+      </c>
+      <c r="Q540" t="n">
+        <v>142</v>
+      </c>
+      <c r="R540" t="n">
+        <v>3</v>
+      </c>
+      <c r="S540" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>gross_margin_change__20250831</t>
+        </is>
+      </c>
+      <c r="B541" t="n">
+        <v>540</v>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Change in gross margin</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Change in gross margin is a percentage-point movement: current gross margin minus prior gross margin. Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>reported_margin.gross_margin_change.2025-08-31</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>F110</t>
+        </is>
+      </c>
+      <c r="I541">
+        <f>F107-E107</f>
+        <v/>
+      </c>
+      <c r="J541" t="n">
+        <v>-0.001219159923582236</v>
+      </c>
+      <c r="K541" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L541" t="inlineStr">
+        <is>
+          <t>gross_margin__20250831,gross_margin__20240831</t>
+        </is>
+      </c>
+      <c r="M541" t="inlineStr">
+        <is>
+          <t>Change in gross margin = current gross margin − prior gross margin.|This is a percentage-point movement, not a causal explanation.|Do not infer price, mix, or cost causes.</t>
+        </is>
+      </c>
+      <c r="O541" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P541" t="inlineStr">
+        <is>
+          <t>gross_margin_change</t>
+        </is>
+      </c>
+      <c r="Q541" t="n">
+        <v>142</v>
+      </c>
+      <c r="R541" t="n">
+        <v>4</v>
+      </c>
+      <c r="S541" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden_change__20220831</t>
+        </is>
+      </c>
+      <c r="B542" t="n">
+        <v>541</v>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden is a percentage-point movement: current burden minus prior burden. A positive burden change reduces reported operating margin. Intervening items are not necessarily SG&amp;A.</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>reported_margin.net_operating_expense_burden_change.2022-08-31</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>C111</t>
+        </is>
+      </c>
+      <c r="I542">
+        <f>C109-B109</f>
+        <v/>
+      </c>
+      <c r="J542" t="n">
+        <v>0.008502367963435065</v>
+      </c>
+      <c r="K542" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L542" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden__20220831,net_operating_expense_burden__20210831</t>
+        </is>
+      </c>
+      <c r="M542" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden = current burden − prior burden.|A positive burden change reduces reported operating margin.|Gross profit minus operating profit is not necessarily SG&amp;A.</t>
+        </is>
+      </c>
+      <c r="O542" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P542" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden_change</t>
+        </is>
+      </c>
+      <c r="Q542" t="n">
+        <v>143</v>
+      </c>
+      <c r="R542" t="n">
+        <v>1</v>
+      </c>
+      <c r="S542" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden_change__20230831</t>
+        </is>
+      </c>
+      <c r="B543" t="n">
+        <v>542</v>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden is a percentage-point movement: current burden minus prior burden. A positive burden change reduces reported operating margin. Intervening items are not necessarily SG&amp;A.</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>reported_margin.net_operating_expense_burden_change.2023-08-31</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>D111</t>
+        </is>
+      </c>
+      <c r="I543">
+        <f>D109-C109</f>
+        <v/>
+      </c>
+      <c r="J543" t="n">
+        <v>-0.01381873744679413</v>
+      </c>
+      <c r="K543" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L543" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden__20230831,net_operating_expense_burden__20220831</t>
+        </is>
+      </c>
+      <c r="M543" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden = current burden − prior burden.|A positive burden change reduces reported operating margin.|Gross profit minus operating profit is not necessarily SG&amp;A.</t>
+        </is>
+      </c>
+      <c r="O543" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P543" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden_change</t>
+        </is>
+      </c>
+      <c r="Q543" t="n">
+        <v>143</v>
+      </c>
+      <c r="R543" t="n">
+        <v>2</v>
+      </c>
+      <c r="S543" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden_change__20240831</t>
+        </is>
+      </c>
+      <c r="B544" t="n">
+        <v>543</v>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden is a percentage-point movement: current burden minus prior burden. A positive burden change reduces reported operating margin. Intervening items are not necessarily SG&amp;A.</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>reported_margin.net_operating_expense_burden_change.2024-08-31</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>E111</t>
+        </is>
+      </c>
+      <c r="I544">
+        <f>E109-D109</f>
+        <v/>
+      </c>
+      <c r="J544" t="n">
+        <v>-0.003786936869552782</v>
+      </c>
+      <c r="K544" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L544" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden__20240831,net_operating_expense_burden__20230831</t>
+        </is>
+      </c>
+      <c r="M544" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden = current burden − prior burden.|A positive burden change reduces reported operating margin.|Gross profit minus operating profit is not necessarily SG&amp;A.</t>
+        </is>
+      </c>
+      <c r="O544" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P544" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden_change</t>
+        </is>
+      </c>
+      <c r="Q544" t="n">
+        <v>143</v>
+      </c>
+      <c r="R544" t="n">
+        <v>3</v>
+      </c>
+      <c r="S544" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden_change__20250831</t>
+        </is>
+      </c>
+      <c r="B545" t="n">
+        <v>544</v>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden is a percentage-point movement: current burden minus prior burden. A positive burden change reduces reported operating margin. Intervening items are not necessarily SG&amp;A.</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>reported_margin.net_operating_expense_burden_change.2025-08-31</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>F111</t>
+        </is>
+      </c>
+      <c r="I545">
+        <f>F109-E109</f>
+        <v/>
+      </c>
+      <c r="J545" t="n">
+        <v>-0.005770910644540383</v>
+      </c>
+      <c r="K545" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L545" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden__20250831,net_operating_expense_burden__20240831</t>
+        </is>
+      </c>
+      <c r="M545" t="inlineStr">
+        <is>
+          <t>Change in net operating expense burden = current burden − prior burden.|A positive burden change reduces reported operating margin.|Gross profit minus operating profit is not necessarily SG&amp;A.</t>
+        </is>
+      </c>
+      <c r="O545" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P545" t="inlineStr">
+        <is>
+          <t>net_operating_expense_burden_change</t>
+        </is>
+      </c>
+      <c r="Q545" t="n">
+        <v>143</v>
+      </c>
+      <c r="R545" t="n">
+        <v>4</v>
+      </c>
+      <c r="S545" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>reconstructed_operating_margin_change__20220831</t>
+        </is>
+      </c>
+      <c r="B546" t="n">
+        <v>545</v>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Reconstructed change in reported operating margin</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>Reconstructed operating-margin change = gross-margin change − burden change, in percentage points. It reconciles to the adjacent reported operating-margin difference. Do not infer price, mix, cost causes, or normalized earnings; keep this distinct from BAV NOPAT margin.</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>reported_margin.reconstructed_operating_margin_change.2022-08-31</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>C112</t>
+        </is>
+      </c>
+      <c r="I546">
+        <f>C110-C111</f>
+        <v/>
+      </c>
+      <c r="J546" t="n">
+        <v>0.01246612268852121</v>
+      </c>
+      <c r="K546" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L546" t="inlineStr">
+        <is>
+          <t>gross_margin_change__20220831,net_operating_expense_burden_change__20220831</t>
+        </is>
+      </c>
+      <c r="M546" t="inlineStr">
+        <is>
+          <t>Reconstructed operating-margin change = gross-margin change − burden change.|When defined, this equals the adjacent reported operating-margin difference.|Do not infer price, mix, cost causes, or normalized earnings.</t>
+        </is>
+      </c>
+      <c r="O546" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P546" t="inlineStr">
+        <is>
+          <t>reconstructed_operating_margin_change</t>
+        </is>
+      </c>
+      <c r="Q546" t="n">
+        <v>144</v>
+      </c>
+      <c r="R546" t="n">
+        <v>1</v>
+      </c>
+      <c r="S546" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>reconstructed_operating_margin_change__20230831</t>
+        </is>
+      </c>
+      <c r="B547" t="n">
+        <v>546</v>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Reconstructed change in reported operating margin</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>Reconstructed operating-margin change = gross-margin change − burden change, in percentage points. It reconciles to the adjacent reported operating-margin difference. Do not infer price, mix, cost causes, or normalized earnings; keep this distinct from BAV NOPAT margin.</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>reported_margin.reconstructed_operating_margin_change.2023-08-31</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>D112</t>
+        </is>
+      </c>
+      <c r="I547">
+        <f>D110-D111</f>
+        <v/>
+      </c>
+      <c r="J547" t="n">
+        <v>0.008540125906455864</v>
+      </c>
+      <c r="K547" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L547" t="inlineStr">
+        <is>
+          <t>gross_margin_change__20230831,net_operating_expense_burden_change__20230831</t>
+        </is>
+      </c>
+      <c r="M547" t="inlineStr">
+        <is>
+          <t>Reconstructed operating-margin change = gross-margin change − burden change.|When defined, this equals the adjacent reported operating-margin difference.|Do not infer price, mix, cost causes, or normalized earnings.</t>
+        </is>
+      </c>
+      <c r="O547" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P547" t="inlineStr">
+        <is>
+          <t>reconstructed_operating_margin_change</t>
+        </is>
+      </c>
+      <c r="Q547" t="n">
+        <v>144</v>
+      </c>
+      <c r="R547" t="n">
+        <v>2</v>
+      </c>
+      <c r="S547" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>reconstructed_operating_margin_change__20240831</t>
+        </is>
+      </c>
+      <c r="B548" t="n">
+        <v>547</v>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Reconstructed change in reported operating margin</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Reconstructed operating-margin change = gross-margin change − burden change, in percentage points. It reconciles to the adjacent reported operating-margin difference. Do not infer price, mix, cost causes, or normalized earnings; keep this distinct from BAV NOPAT margin.</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>reported_margin.reconstructed_operating_margin_change.2024-08-31</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>E112</t>
+        </is>
+      </c>
+      <c r="I548">
+        <f>E110-E111</f>
+        <v/>
+      </c>
+      <c r="J548" t="n">
+        <v>0.02363340432048133</v>
+      </c>
+      <c r="K548" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L548" t="inlineStr">
+        <is>
+          <t>gross_margin_change__20240831,net_operating_expense_burden_change__20240831</t>
+        </is>
+      </c>
+      <c r="M548" t="inlineStr">
+        <is>
+          <t>Reconstructed operating-margin change = gross-margin change − burden change.|When defined, this equals the adjacent reported operating-margin difference.|Do not infer price, mix, cost causes, or normalized earnings.</t>
+        </is>
+      </c>
+      <c r="O548" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P548" t="inlineStr">
+        <is>
+          <t>reconstructed_operating_margin_change</t>
+        </is>
+      </c>
+      <c r="Q548" t="n">
+        <v>144</v>
+      </c>
+      <c r="R548" t="n">
+        <v>3</v>
+      </c>
+      <c r="S548" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>reconstructed_operating_margin_change__20250831</t>
+        </is>
+      </c>
+      <c r="B549" t="n">
+        <v>548</v>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Reconstructed change in reported operating margin</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Reconstructed operating-margin change = gross-margin change − burden change, in percentage points. It reconciles to the adjacent reported operating-margin difference. Do not infer price, mix, cost causes, or normalized earnings; keep this distinct from BAV NOPAT margin.</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>reported_margin.reconstructed_operating_margin_change.2025-08-31</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>reported_margin</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>F112</t>
+        </is>
+      </c>
+      <c r="I549">
+        <f>F110-F111</f>
+        <v/>
+      </c>
+      <c r="J549" t="n">
+        <v>0.004551750720958148</v>
+      </c>
+      <c r="K549" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L549" t="inlineStr">
+        <is>
+          <t>gross_margin_change__20250831,net_operating_expense_burden_change__20250831</t>
+        </is>
+      </c>
+      <c r="M549" t="inlineStr">
+        <is>
+          <t>Reconstructed operating-margin change = gross-margin change − burden change.|When defined, this equals the adjacent reported operating-margin difference.|Do not infer price, mix, cost causes, or normalized earnings.</t>
+        </is>
+      </c>
+      <c r="O549" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P549" t="inlineStr">
+        <is>
+          <t>reconstructed_operating_margin_change</t>
+        </is>
+      </c>
+      <c r="Q549" t="n">
+        <v>144</v>
+      </c>
+      <c r="R549" t="n">
+        <v>4</v>
+      </c>
+      <c r="S549" t="inlineStr">
         <is>
           <t>2025-08-31</t>
         </is>
@@ -53609,7 +56036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -55750,445 +58177,684 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+          <t>REPORTED MARGIN BRIDGE CONTEXT</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Revenue (reported)</t>
         </is>
       </c>
       <c r="B104" s="13">
-        <f>'Balance Sheet'!B37</f>
+        <f>'Income Statement'!B21</f>
         <v/>
       </c>
       <c r="C104" s="13">
-        <f>'Balance Sheet'!C37</f>
+        <f>'Income Statement'!C21</f>
         <v/>
       </c>
       <c r="D104" s="13">
-        <f>'Balance Sheet'!D37</f>
+        <f>'Income Statement'!D21</f>
         <v/>
       </c>
       <c r="E104" s="13">
-        <f>'Balance Sheet'!E37</f>
+        <f>'Income Statement'!E21</f>
         <v/>
       </c>
       <c r="F104" s="13">
-        <f>'Balance Sheet'!F37</f>
+        <f>'Income Statement'!F21</f>
         <v/>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>Change in Goodwill</t>
-        </is>
-      </c>
-      <c r="C105" s="16">
-        <f>C104-B104</f>
-        <v/>
-      </c>
-      <c r="D105" s="16">
-        <f>D104-C104</f>
-        <v/>
-      </c>
-      <c r="E105" s="16">
-        <f>E104-D104</f>
-        <v/>
-      </c>
-      <c r="F105" s="16">
-        <f>F104-E104</f>
+          <t>Gross profit (reported)</t>
+        </is>
+      </c>
+      <c r="B105" s="13">
+        <f>'Income Statement'!B12</f>
+        <v/>
+      </c>
+      <c r="C105" s="13">
+        <f>'Income Statement'!C12</f>
+        <v/>
+      </c>
+      <c r="D105" s="13">
+        <f>'Income Statement'!D12</f>
+        <v/>
+      </c>
+      <c r="E105" s="13">
+        <f>'Income Statement'!E12</f>
+        <v/>
+      </c>
+      <c r="F105" s="13">
+        <f>'Income Statement'!F12</f>
         <v/>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
-      </c>
-      <c r="C106" s="15">
-        <f>IF(B104=0,NA(),C104/B104-1)</f>
-        <v/>
-      </c>
-      <c r="D106" s="15">
-        <f>IF(C104=0,NA(),D104/C104-1)</f>
-        <v/>
-      </c>
-      <c r="E106" s="15">
-        <f>IF(D104=0,NA(),E104/D104-1)</f>
-        <v/>
-      </c>
-      <c r="F106" s="15">
-        <f>IF(E104=0,NA(),F104/E104-1)</f>
+          <t>Operating profit (reported)</t>
+        </is>
+      </c>
+      <c r="B106" s="13">
+        <f>'Income Statement'!B15</f>
+        <v/>
+      </c>
+      <c r="C106" s="13">
+        <f>'Income Statement'!C15</f>
+        <v/>
+      </c>
+      <c r="D106" s="13">
+        <f>'Income Statement'!D15</f>
+        <v/>
+      </c>
+      <c r="E106" s="13">
+        <f>'Income Statement'!E15</f>
+        <v/>
+      </c>
+      <c r="F106" s="13">
+        <f>'Income Statement'!F15</f>
         <v/>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill</t>
-        </is>
-      </c>
-      <c r="C107" s="16">
-        <f>(B104+C104)/2</f>
-        <v/>
-      </c>
-      <c r="D107" s="16">
-        <f>(C104+D104)/2</f>
-        <v/>
-      </c>
-      <c r="E107" s="16">
-        <f>(D104+E104)/2</f>
-        <v/>
-      </c>
-      <c r="F107" s="16">
-        <f>(E104+F104)/2</f>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B107" s="15">
+        <f>IF(B104=0,NA(),B105/B104)</f>
+        <v/>
+      </c>
+      <c r="C107" s="15">
+        <f>IF(C104=0,NA(),C105/C104)</f>
+        <v/>
+      </c>
+      <c r="D107" s="15">
+        <f>IF(D104=0,NA(),D105/D104)</f>
+        <v/>
+      </c>
+      <c r="E107" s="15">
+        <f>IF(E104=0,NA(),E105/E104)</f>
+        <v/>
+      </c>
+      <c r="F107" s="15">
+        <f>IF(F104=0,NA(),F105/F104)</f>
         <v/>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
+          <t>Reported operating margin</t>
+        </is>
+      </c>
+      <c r="B108" s="15">
+        <f>IF(B104=0,NA(),B106/B104)</f>
+        <v/>
       </c>
       <c r="C108" s="15">
-        <f>IF('Condensed Financials'!C44=0,NA(),C107/'Condensed Financials'!C44)</f>
+        <f>IF(C104=0,NA(),C106/C104)</f>
         <v/>
       </c>
       <c r="D108" s="15">
-        <f>IF('Condensed Financials'!D44=0,NA(),D107/'Condensed Financials'!D44)</f>
+        <f>IF(D104=0,NA(),D106/D104)</f>
         <v/>
       </c>
       <c r="E108" s="15">
-        <f>IF('Condensed Financials'!E44=0,NA(),E107/'Condensed Financials'!E44)</f>
+        <f>IF(E104=0,NA(),E106/E104)</f>
         <v/>
       </c>
       <c r="F108" s="15">
-        <f>IF('Condensed Financials'!F44=0,NA(),F107/'Condensed Financials'!F44)</f>
+        <f>IF(F104=0,NA(),F106/F104)</f>
         <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
-        </is>
-      </c>
-      <c r="B109" s="13">
-        <f>'Balance Sheet'!B38</f>
-        <v/>
-      </c>
-      <c r="C109" s="13">
-        <f>'Balance Sheet'!C38</f>
-        <v/>
-      </c>
-      <c r="D109" s="13">
-        <f>'Balance Sheet'!D38</f>
-        <v/>
-      </c>
-      <c r="E109" s="13">
-        <f>'Balance Sheet'!E38</f>
-        <v/>
-      </c>
-      <c r="F109" s="13">
-        <f>'Balance Sheet'!F38</f>
+          <t>Net operating expense burden</t>
+        </is>
+      </c>
+      <c r="B109" s="15">
+        <f>IF(B104=0,NA(),(B105-B106)/B104)</f>
+        <v/>
+      </c>
+      <c r="C109" s="15">
+        <f>IF(C104=0,NA(),(C105-C106)/C104)</f>
+        <v/>
+      </c>
+      <c r="D109" s="15">
+        <f>IF(D104=0,NA(),(D105-D106)/D104)</f>
+        <v/>
+      </c>
+      <c r="E109" s="15">
+        <f>IF(E104=0,NA(),(E105-E106)/E104)</f>
+        <v/>
+      </c>
+      <c r="F109" s="15">
+        <f>IF(F104=0,NA(),(F105-F106)/F104)</f>
         <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t>Change in Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C110" s="16">
-        <f>C109-B109</f>
-        <v/>
-      </c>
-      <c r="D110" s="16">
-        <f>D109-C109</f>
-        <v/>
-      </c>
-      <c r="E110" s="16">
-        <f>E109-D109</f>
-        <v/>
-      </c>
-      <c r="F110" s="16">
-        <f>F109-E109</f>
+          <t>Change in gross margin</t>
+        </is>
+      </c>
+      <c r="C110" s="15">
+        <f>C107-B107</f>
+        <v/>
+      </c>
+      <c r="D110" s="15">
+        <f>D107-C107</f>
+        <v/>
+      </c>
+      <c r="E110" s="15">
+        <f>E107-D107</f>
+        <v/>
+      </c>
+      <c r="F110" s="15">
+        <f>F107-E107</f>
         <v/>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>Intangible Assets Growth</t>
+          <t>Change in net operating expense burden</t>
         </is>
       </c>
       <c r="C111" s="15">
-        <f>IF(B109=0,NA(),C109/B109-1)</f>
+        <f>C109-B109</f>
         <v/>
       </c>
       <c r="D111" s="15">
-        <f>IF(C109=0,NA(),D109/C109-1)</f>
+        <f>D109-C109</f>
         <v/>
       </c>
       <c r="E111" s="15">
-        <f>IF(D109=0,NA(),E109/D109-1)</f>
+        <f>E109-D109</f>
         <v/>
       </c>
       <c r="F111" s="15">
-        <f>IF(E109=0,NA(),F109/E109-1)</f>
+        <f>F109-E109</f>
         <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="11" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C112" s="16">
-        <f>(B109+C109)/2</f>
-        <v/>
-      </c>
-      <c r="D112" s="16">
-        <f>(C109+D109)/2</f>
-        <v/>
-      </c>
-      <c r="E112" s="16">
-        <f>(D109+E109)/2</f>
-        <v/>
-      </c>
-      <c r="F112" s="16">
-        <f>(E109+F109)/2</f>
-        <v/>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="11" t="inlineStr">
-        <is>
-          <t>Average Intangible Assets / Revenue</t>
-        </is>
-      </c>
-      <c r="C113" s="15">
-        <f>IF('Condensed Financials'!C44=0,NA(),C112/'Condensed Financials'!C44)</f>
-        <v/>
-      </c>
-      <c r="D113" s="15">
-        <f>IF('Condensed Financials'!D44=0,NA(),D112/'Condensed Financials'!D44)</f>
-        <v/>
-      </c>
-      <c r="E113" s="15">
-        <f>IF('Condensed Financials'!E44=0,NA(),E112/'Condensed Financials'!E44)</f>
-        <v/>
-      </c>
-      <c r="F113" s="15">
-        <f>IF('Condensed Financials'!F44=0,NA(),F112/'Condensed Financials'!F44)</f>
-        <v/>
-      </c>
-    </row>
+          <t>Reconstructed change in reported operating margin</t>
+        </is>
+      </c>
+      <c r="C112" s="15">
+        <f>C110-C111</f>
+        <v/>
+      </c>
+      <c r="D112" s="15">
+        <f>D110-D111</f>
+        <v/>
+      </c>
+      <c r="E112" s="15">
+        <f>E110-E111</f>
+        <v/>
+      </c>
+      <c r="F112" s="15">
+        <f>F110-F111</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113"/>
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="B114" s="13">
-        <f>B104+B109</f>
-        <v/>
-      </c>
-      <c r="C114" s="13">
-        <f>C104+C109</f>
-        <v/>
-      </c>
-      <c r="D114" s="13">
-        <f>D104+D109</f>
-        <v/>
-      </c>
-      <c r="E114" s="13">
-        <f>E104+E109</f>
-        <v/>
-      </c>
-      <c r="F114" s="13">
-        <f>F104+F109</f>
-        <v/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C115" s="16">
-        <f>C114-B114</f>
-        <v/>
-      </c>
-      <c r="D115" s="16">
-        <f>D114-C114</f>
-        <v/>
-      </c>
-      <c r="E115" s="16">
-        <f>E114-D114</f>
-        <v/>
-      </c>
-      <c r="F115" s="16">
-        <f>F114-E114</f>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B115" s="13">
+        <f>'Balance Sheet'!B37</f>
+        <v/>
+      </c>
+      <c r="C115" s="13">
+        <f>'Balance Sheet'!C37</f>
+        <v/>
+      </c>
+      <c r="D115" s="13">
+        <f>'Balance Sheet'!D37</f>
+        <v/>
+      </c>
+      <c r="E115" s="13">
+        <f>'Balance Sheet'!E37</f>
+        <v/>
+      </c>
+      <c r="F115" s="13">
+        <f>'Balance Sheet'!F37</f>
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
-        </is>
-      </c>
-      <c r="C116" s="15">
-        <f>IF(B114=0,NA(),C114/B114-1)</f>
-        <v/>
-      </c>
-      <c r="D116" s="15">
-        <f>IF(C114=0,NA(),D114/C114-1)</f>
-        <v/>
-      </c>
-      <c r="E116" s="15">
-        <f>IF(D114=0,NA(),E114/D114-1)</f>
-        <v/>
-      </c>
-      <c r="F116" s="15">
-        <f>IF(E114=0,NA(),F114/E114-1)</f>
+          <t>Change in Goodwill</t>
+        </is>
+      </c>
+      <c r="C116" s="16">
+        <f>C115-B115</f>
+        <v/>
+      </c>
+      <c r="D116" s="16">
+        <f>D115-C115</f>
+        <v/>
+      </c>
+      <c r="E116" s="16">
+        <f>E115-D115</f>
+        <v/>
+      </c>
+      <c r="F116" s="16">
+        <f>F115-E115</f>
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C117" s="16">
-        <f>(B114+C114)/2</f>
-        <v/>
-      </c>
-      <c r="D117" s="16">
-        <f>(C114+D114)/2</f>
-        <v/>
-      </c>
-      <c r="E117" s="16">
-        <f>(D114+E114)/2</f>
-        <v/>
-      </c>
-      <c r="F117" s="16">
-        <f>(E114+F114)/2</f>
+          <t>Goodwill Growth</t>
+        </is>
+      </c>
+      <c r="C117" s="15">
+        <f>IF(B115=0,NA(),C115/B115-1)</f>
+        <v/>
+      </c>
+      <c r="D117" s="15">
+        <f>IF(C115=0,NA(),D115/C115-1)</f>
+        <v/>
+      </c>
+      <c r="E117" s="15">
+        <f>IF(D115=0,NA(),E115/D115-1)</f>
+        <v/>
+      </c>
+      <c r="F117" s="15">
+        <f>IF(E115=0,NA(),F115/E115-1)</f>
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles / Revenue</t>
-        </is>
-      </c>
-      <c r="C118" s="15">
-        <f>IF('Condensed Financials'!C44=0,NA(),C117/'Condensed Financials'!C44)</f>
-        <v/>
-      </c>
-      <c r="D118" s="15">
-        <f>IF('Condensed Financials'!D44=0,NA(),D117/'Condensed Financials'!D44)</f>
-        <v/>
-      </c>
-      <c r="E118" s="15">
-        <f>IF('Condensed Financials'!E44=0,NA(),E117/'Condensed Financials'!E44)</f>
-        <v/>
-      </c>
-      <c r="F118" s="15">
-        <f>IF('Condensed Financials'!F44=0,NA(),F117/'Condensed Financials'!F44)</f>
+          <t>Average Goodwill</t>
+        </is>
+      </c>
+      <c r="C118" s="16">
+        <f>(B115+C115)/2</f>
+        <v/>
+      </c>
+      <c r="D118" s="16">
+        <f>(C115+D115)/2</f>
+        <v/>
+      </c>
+      <c r="E118" s="16">
+        <f>(D115+E115)/2</f>
+        <v/>
+      </c>
+      <c r="F118" s="16">
+        <f>(E115+F115)/2</f>
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>Payments for Intangible Assets (reported)</t>
-        </is>
-      </c>
-      <c r="B119" s="13">
-        <f>'Cash Flow Statement'!B38</f>
-        <v/>
-      </c>
-      <c r="C119" s="13">
-        <f>'Cash Flow Statement'!C38</f>
-        <v/>
-      </c>
-      <c r="D119" s="13">
-        <f>'Cash Flow Statement'!D38</f>
-        <v/>
-      </c>
-      <c r="E119" s="13">
-        <f>'Cash Flow Statement'!E38</f>
-        <v/>
-      </c>
-      <c r="F119" s="13">
-        <f>'Cash Flow Statement'!F38</f>
+          <t>Average Goodwill / Revenue</t>
+        </is>
+      </c>
+      <c r="C119" s="15">
+        <f>IF('Condensed Financials'!C44=0,NA(),C118/'Condensed Financials'!C44)</f>
+        <v/>
+      </c>
+      <c r="D119" s="15">
+        <f>IF('Condensed Financials'!D44=0,NA(),D118/'Condensed Financials'!D44)</f>
+        <v/>
+      </c>
+      <c r="E119" s="15">
+        <f>IF('Condensed Financials'!E44=0,NA(),E118/'Condensed Financials'!E44)</f>
+        <v/>
+      </c>
+      <c r="F119" s="15">
+        <f>IF('Condensed Financials'!F44=0,NA(),F118/'Condensed Financials'!F44)</f>
         <v/>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>Intangible Payments (−reported)</t>
-        </is>
-      </c>
-      <c r="B120" s="16">
-        <f>-B119</f>
-        <v/>
-      </c>
-      <c r="C120" s="16">
-        <f>-C119</f>
-        <v/>
-      </c>
-      <c r="D120" s="16">
-        <f>-D119</f>
-        <v/>
-      </c>
-      <c r="E120" s="16">
-        <f>-E119</f>
-        <v/>
-      </c>
-      <c r="F120" s="16">
-        <f>-F119</f>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B120" s="13">
+        <f>'Balance Sheet'!B38</f>
+        <v/>
+      </c>
+      <c r="C120" s="13">
+        <f>'Balance Sheet'!C38</f>
+        <v/>
+      </c>
+      <c r="D120" s="13">
+        <f>'Balance Sheet'!D38</f>
+        <v/>
+      </c>
+      <c r="E120" s="13">
+        <f>'Balance Sheet'!E38</f>
+        <v/>
+      </c>
+      <c r="F120" s="13">
+        <f>'Balance Sheet'!F38</f>
         <v/>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
+          <t>Change in Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C121" s="16">
+        <f>C120-B120</f>
+        <v/>
+      </c>
+      <c r="D121" s="16">
+        <f>D120-C120</f>
+        <v/>
+      </c>
+      <c r="E121" s="16">
+        <f>E120-D120</f>
+        <v/>
+      </c>
+      <c r="F121" s="16">
+        <f>F120-E120</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>Intangible Assets Growth</t>
+        </is>
+      </c>
+      <c r="C122" s="15">
+        <f>IF(B120=0,NA(),C120/B120-1)</f>
+        <v/>
+      </c>
+      <c r="D122" s="15">
+        <f>IF(C120=0,NA(),D120/C120-1)</f>
+        <v/>
+      </c>
+      <c r="E122" s="15">
+        <f>IF(D120=0,NA(),E120/D120-1)</f>
+        <v/>
+      </c>
+      <c r="F122" s="15">
+        <f>IF(E120=0,NA(),F120/E120-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="11" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C123" s="16">
+        <f>(B120+C120)/2</f>
+        <v/>
+      </c>
+      <c r="D123" s="16">
+        <f>(C120+D120)/2</f>
+        <v/>
+      </c>
+      <c r="E123" s="16">
+        <f>(D120+E120)/2</f>
+        <v/>
+      </c>
+      <c r="F123" s="16">
+        <f>(E120+F120)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="11" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="C124" s="15">
+        <f>IF('Condensed Financials'!C44=0,NA(),C123/'Condensed Financials'!C44)</f>
+        <v/>
+      </c>
+      <c r="D124" s="15">
+        <f>IF('Condensed Financials'!D44=0,NA(),D123/'Condensed Financials'!D44)</f>
+        <v/>
+      </c>
+      <c r="E124" s="15">
+        <f>IF('Condensed Financials'!E44=0,NA(),E123/'Condensed Financials'!E44)</f>
+        <v/>
+      </c>
+      <c r="F124" s="15">
+        <f>IF('Condensed Financials'!F44=0,NA(),F123/'Condensed Financials'!F44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="11" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B125" s="13">
+        <f>B115+B120</f>
+        <v/>
+      </c>
+      <c r="C125" s="13">
+        <f>C115+C120</f>
+        <v/>
+      </c>
+      <c r="D125" s="13">
+        <f>D115+D120</f>
+        <v/>
+      </c>
+      <c r="E125" s="13">
+        <f>E115+E120</f>
+        <v/>
+      </c>
+      <c r="F125" s="13">
+        <f>F115+F120</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="11" t="inlineStr">
+        <is>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C126" s="16">
+        <f>C125-B125</f>
+        <v/>
+      </c>
+      <c r="D126" s="16">
+        <f>D125-C125</f>
+        <v/>
+      </c>
+      <c r="E126" s="16">
+        <f>E125-D125</f>
+        <v/>
+      </c>
+      <c r="F126" s="16">
+        <f>F125-E125</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C127" s="15">
+        <f>IF(B125=0,NA(),C125/B125-1)</f>
+        <v/>
+      </c>
+      <c r="D127" s="15">
+        <f>IF(C125=0,NA(),D125/C125-1)</f>
+        <v/>
+      </c>
+      <c r="E127" s="15">
+        <f>IF(D125=0,NA(),E125/D125-1)</f>
+        <v/>
+      </c>
+      <c r="F127" s="15">
+        <f>IF(E125=0,NA(),F125/E125-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="11" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C128" s="16">
+        <f>(B125+C125)/2</f>
+        <v/>
+      </c>
+      <c r="D128" s="16">
+        <f>(C125+D125)/2</f>
+        <v/>
+      </c>
+      <c r="E128" s="16">
+        <f>(D125+E125)/2</f>
+        <v/>
+      </c>
+      <c r="F128" s="16">
+        <f>(E125+F125)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="11" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles / Revenue</t>
+        </is>
+      </c>
+      <c r="C129" s="15">
+        <f>IF('Condensed Financials'!C44=0,NA(),C128/'Condensed Financials'!C44)</f>
+        <v/>
+      </c>
+      <c r="D129" s="15">
+        <f>IF('Condensed Financials'!D44=0,NA(),D128/'Condensed Financials'!D44)</f>
+        <v/>
+      </c>
+      <c r="E129" s="15">
+        <f>IF('Condensed Financials'!E44=0,NA(),E128/'Condensed Financials'!E44)</f>
+        <v/>
+      </c>
+      <c r="F129" s="15">
+        <f>IF('Condensed Financials'!F44=0,NA(),F128/'Condensed Financials'!F44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="11" t="inlineStr">
+        <is>
+          <t>Payments for Intangible Assets (reported)</t>
+        </is>
+      </c>
+      <c r="B130" s="13">
+        <f>'Cash Flow Statement'!B38</f>
+        <v/>
+      </c>
+      <c r="C130" s="13">
+        <f>'Cash Flow Statement'!C38</f>
+        <v/>
+      </c>
+      <c r="D130" s="13">
+        <f>'Cash Flow Statement'!D38</f>
+        <v/>
+      </c>
+      <c r="E130" s="13">
+        <f>'Cash Flow Statement'!E38</f>
+        <v/>
+      </c>
+      <c r="F130" s="13">
+        <f>'Cash Flow Statement'!F38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="11" t="inlineStr">
+        <is>
+          <t>Intangible Payments (−reported)</t>
+        </is>
+      </c>
+      <c r="B131" s="16">
+        <f>-B130</f>
+        <v/>
+      </c>
+      <c r="C131" s="16">
+        <f>-C130</f>
+        <v/>
+      </c>
+      <c r="D131" s="16">
+        <f>-D130</f>
+        <v/>
+      </c>
+      <c r="E131" s="16">
+        <f>-E130</f>
+        <v/>
+      </c>
+      <c r="F131" s="16">
+        <f>-F130</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="11" t="inlineStr">
+        <is>
           <t>Intangible Payments / Revenue</t>
         </is>
       </c>
-      <c r="B121" s="15">
-        <f>IF('Condensed Financials'!B44=0,NA(),B120/'Condensed Financials'!B44)</f>
-        <v/>
-      </c>
-      <c r="C121" s="15">
-        <f>IF('Condensed Financials'!C44=0,NA(),C120/'Condensed Financials'!C44)</f>
-        <v/>
-      </c>
-      <c r="D121" s="15">
-        <f>IF('Condensed Financials'!D44=0,NA(),D120/'Condensed Financials'!D44)</f>
-        <v/>
-      </c>
-      <c r="E121" s="15">
-        <f>IF('Condensed Financials'!E44=0,NA(),E120/'Condensed Financials'!E44)</f>
-        <v/>
-      </c>
-      <c r="F121" s="15">
-        <f>IF('Condensed Financials'!F44=0,NA(),F120/'Condensed Financials'!F44)</f>
+      <c r="B132" s="15">
+        <f>IF('Condensed Financials'!B44=0,NA(),B131/'Condensed Financials'!B44)</f>
+        <v/>
+      </c>
+      <c r="C132" s="15">
+        <f>IF('Condensed Financials'!C44=0,NA(),C131/'Condensed Financials'!C44)</f>
+        <v/>
+      </c>
+      <c r="D132" s="15">
+        <f>IF('Condensed Financials'!D44=0,NA(),D131/'Condensed Financials'!D44)</f>
+        <v/>
+      </c>
+      <c r="E132" s="15">
+        <f>IF('Condensed Financials'!E44=0,NA(),E131/'Condensed Financials'!E44)</f>
+        <v/>
+      </c>
+      <c r="F132" s="15">
+        <f>IF('Condensed Financials'!F44=0,NA(),F131/'Condensed Financials'!F44)</f>
         <v/>
       </c>
     </row>

--- a/release/fast_retailing/FastRetailing_Answer_Key.xlsx
+++ b/release/fast_retailing/FastRetailing_Answer_Key.xlsx
@@ -1898,292 +1898,397 @@
         <t>Reconstructed operating-margin change = gross-margin change − burden change, in percentage points. It reconciles to the adjacent reported operating-margin difference. Do not infer price, mix, cost causes, or normalized earnings; keep this distinct from BAV NOPAT margin.</t>
       </text>
     </comment>
-    <comment ref="C116" authorId="0" shapeId="0">
+    <comment ref="B117" authorId="0" shapeId="0">
+      <text>
+        <t>Inventory intensity = ending inventory / annual revenue. This is not inventory days or turnover. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="C117" authorId="0" shapeId="0">
+      <text>
+        <t>Inventory intensity = ending inventory / annual revenue. This is not inventory days or turnover. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="D117" authorId="0" shapeId="0">
+      <text>
+        <t>Inventory intensity = ending inventory / annual revenue. This is not inventory days or turnover. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="E117" authorId="0" shapeId="0">
+      <text>
+        <t>Inventory intensity = ending inventory / annual revenue. This is not inventory days or turnover. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="F117" authorId="0" shapeId="0">
+      <text>
+        <t>Inventory intensity = ending inventory / annual revenue. This is not inventory days or turnover. Zero revenue is undefined (#N/A).</t>
+      </text>
+    </comment>
+    <comment ref="C118" authorId="0" shapeId="0">
+      <text>
+        <t>Change in inventory = current inventory − prior inventory (signed). Opening-period change is not practiced. This is not proof of cash movement, markdowns, or management causes.</t>
+      </text>
+    </comment>
+    <comment ref="D118" authorId="0" shapeId="0">
+      <text>
+        <t>Change in inventory = current inventory − prior inventory (signed). Opening-period change is not practiced. This is not proof of cash movement, markdowns, or management causes.</t>
+      </text>
+    </comment>
+    <comment ref="E118" authorId="0" shapeId="0">
+      <text>
+        <t>Change in inventory = current inventory − prior inventory (signed). Opening-period change is not practiced. This is not proof of cash movement, markdowns, or management causes.</t>
+      </text>
+    </comment>
+    <comment ref="F118" authorId="0" shapeId="0">
+      <text>
+        <t>Change in inventory = current inventory − prior inventory (signed). Opening-period change is not practiced. This is not proof of cash movement, markdowns, or management causes.</t>
+      </text>
+    </comment>
+    <comment ref="C119" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue-scale effect = prior inventory intensity × (current revenue − prior revenue). Uses the prior-intensity / current-revenue attribution convention. Signed; not a cash-movement proof.</t>
+      </text>
+    </comment>
+    <comment ref="D119" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue-scale effect = prior inventory intensity × (current revenue − prior revenue). Uses the prior-intensity / current-revenue attribution convention. Signed; not a cash-movement proof.</t>
+      </text>
+    </comment>
+    <comment ref="E119" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue-scale effect = prior inventory intensity × (current revenue − prior revenue). Uses the prior-intensity / current-revenue attribution convention. Signed; not a cash-movement proof.</t>
+      </text>
+    </comment>
+    <comment ref="F119" authorId="0" shapeId="0">
+      <text>
+        <t>Revenue-scale effect = prior inventory intensity × (current revenue − prior revenue). Uses the prior-intensity / current-revenue attribution convention. Signed; not a cash-movement proof.</t>
+      </text>
+    </comment>
+    <comment ref="C120" authorId="0" shapeId="0">
+      <text>
+        <t>Intensity effect = current revenue × (current inventory intensity − prior inventory intensity). Uses the prior-intensity / current-revenue attribution convention. Signed; not proof of deterioration, seasonality, or markdowns.</t>
+      </text>
+    </comment>
+    <comment ref="D120" authorId="0" shapeId="0">
+      <text>
+        <t>Intensity effect = current revenue × (current inventory intensity − prior inventory intensity). Uses the prior-intensity / current-revenue attribution convention. Signed; not proof of deterioration, seasonality, or markdowns.</t>
+      </text>
+    </comment>
+    <comment ref="E120" authorId="0" shapeId="0">
+      <text>
+        <t>Intensity effect = current revenue × (current inventory intensity − prior inventory intensity). Uses the prior-intensity / current-revenue attribution convention. Signed; not proof of deterioration, seasonality, or markdowns.</t>
+      </text>
+    </comment>
+    <comment ref="F120" authorId="0" shapeId="0">
+      <text>
+        <t>Intensity effect = current revenue × (current inventory intensity − prior inventory intensity). Uses the prior-intensity / current-revenue attribution convention. Signed; not proof of deterioration, seasonality, or markdowns.</t>
+      </text>
+    </comment>
+    <comment ref="C121" authorId="0" shapeId="0">
+      <text>
+        <t>Reconstructed inventory change = revenue-scale effect + intensity effect. Arithmetic decomposition that reconciles to the inventory change when defined. Not inventory days/turnover and not proof of cash movement, deterioration, seasonality, markdowns, or management causes.</t>
+      </text>
+    </comment>
+    <comment ref="D121" authorId="0" shapeId="0">
+      <text>
+        <t>Reconstructed inventory change = revenue-scale effect + intensity effect. Arithmetic decomposition that reconciles to the inventory change when defined. Not inventory days/turnover and not proof of cash movement, deterioration, seasonality, markdowns, or management causes.</t>
+      </text>
+    </comment>
+    <comment ref="E121" authorId="0" shapeId="0">
+      <text>
+        <t>Reconstructed inventory change = revenue-scale effect + intensity effect. Arithmetic decomposition that reconciles to the inventory change when defined. Not inventory days/turnover and not proof of cash movement, deterioration, seasonality, markdowns, or management causes.</t>
+      </text>
+    </comment>
+    <comment ref="F121" authorId="0" shapeId="0">
+      <text>
+        <t>Reconstructed inventory change = revenue-scale effect + intensity effect. Arithmetic decomposition that reconciles to the inventory change when defined. Not inventory days/turnover and not proof of cash movement, deterioration, seasonality, markdowns, or management causes.</t>
+      </text>
+    </comment>
+    <comment ref="C125" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="D116" authorId="0" shapeId="0">
+    <comment ref="D125" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="E116" authorId="0" shapeId="0">
+    <comment ref="E125" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="F116" authorId="0" shapeId="0">
+    <comment ref="F125" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="C117" authorId="0" shapeId="0">
+    <comment ref="C126" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="D117" authorId="0" shapeId="0">
+    <comment ref="D126" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="E117" authorId="0" shapeId="0">
+    <comment ref="E126" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="F117" authorId="0" shapeId="0">
+    <comment ref="F126" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="C118" authorId="0" shapeId="0">
+    <comment ref="C127" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="D118" authorId="0" shapeId="0">
+    <comment ref="D127" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="E118" authorId="0" shapeId="0">
+    <comment ref="E127" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="F118" authorId="0" shapeId="0">
+    <comment ref="F127" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="C119" authorId="0" shapeId="0">
+    <comment ref="C128" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D119" authorId="0" shapeId="0">
+    <comment ref="D128" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E119" authorId="0" shapeId="0">
+    <comment ref="E128" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="F119" authorId="0" shapeId="0">
+    <comment ref="F128" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C121" authorId="0" shapeId="0">
+    <comment ref="C130" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D121" authorId="0" shapeId="0">
+    <comment ref="D130" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E121" authorId="0" shapeId="0">
+    <comment ref="E130" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="F121" authorId="0" shapeId="0">
+    <comment ref="F130" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C122" authorId="0" shapeId="0">
+    <comment ref="C131" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D122" authorId="0" shapeId="0">
+    <comment ref="D131" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E122" authorId="0" shapeId="0">
+    <comment ref="E131" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="F122" authorId="0" shapeId="0">
+    <comment ref="F131" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C123" authorId="0" shapeId="0">
+    <comment ref="C132" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D123" authorId="0" shapeId="0">
+    <comment ref="D132" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E123" authorId="0" shapeId="0">
+    <comment ref="E132" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="F123" authorId="0" shapeId="0">
+    <comment ref="F132" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C124" authorId="0" shapeId="0">
+    <comment ref="C133" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D124" authorId="0" shapeId="0">
+    <comment ref="D133" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E124" authorId="0" shapeId="0">
+    <comment ref="E133" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="F124" authorId="0" shapeId="0">
+    <comment ref="F133" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C126" authorId="0" shapeId="0">
+    <comment ref="C135" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="D126" authorId="0" shapeId="0">
+    <comment ref="D135" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="E126" authorId="0" shapeId="0">
+    <comment ref="E135" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="F126" authorId="0" shapeId="0">
+    <comment ref="F135" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="C127" authorId="0" shapeId="0">
+    <comment ref="C136" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="D127" authorId="0" shapeId="0">
+    <comment ref="D136" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="E127" authorId="0" shapeId="0">
+    <comment ref="E136" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="F127" authorId="0" shapeId="0">
+    <comment ref="F136" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="C128" authorId="0" shapeId="0">
+    <comment ref="C137" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="D128" authorId="0" shapeId="0">
+    <comment ref="D137" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="E128" authorId="0" shapeId="0">
+    <comment ref="E137" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="F128" authorId="0" shapeId="0">
+    <comment ref="F137" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="C129" authorId="0" shapeId="0">
+    <comment ref="C138" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="D129" authorId="0" shapeId="0">
+    <comment ref="D138" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="E129" authorId="0" shapeId="0">
+    <comment ref="E138" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="F129" authorId="0" shapeId="0">
+    <comment ref="F138" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="B131" authorId="0" shapeId="0">
+    <comment ref="B140" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="C131" authorId="0" shapeId="0">
+    <comment ref="C140" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="D131" authorId="0" shapeId="0">
+    <comment ref="D140" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="E131" authorId="0" shapeId="0">
+    <comment ref="E140" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="F131" authorId="0" shapeId="0">
+    <comment ref="F140" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="B132" authorId="0" shapeId="0">
+    <comment ref="B141" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="C132" authorId="0" shapeId="0">
+    <comment ref="C141" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="D132" authorId="0" shapeId="0">
+    <comment ref="D141" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="E132" authorId="0" shapeId="0">
+    <comment ref="E141" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="F132" authorId="0" shapeId="0">
+    <comment ref="F141" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
@@ -3286,7 +3391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F131"/>
+  <dimension ref="A1:F136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6035,7 +6140,7 @@
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>C116:F116</t>
+          <t>C125:F125</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
@@ -6065,7 +6170,7 @@
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>C117:F117</t>
+          <t>C126:F126</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -6095,7 +6200,7 @@
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>C118:F118</t>
+          <t>C127:F127</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
@@ -6125,7 +6230,7 @@
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>C119:F119</t>
+          <t>C128:F128</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
@@ -6155,7 +6260,7 @@
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>C121:F121</t>
+          <t>C130:F130</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
@@ -6185,7 +6290,7 @@
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>C122:F122</t>
+          <t>C131:F131</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
@@ -6215,7 +6320,7 @@
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>C123:F123</t>
+          <t>C132:F132</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
@@ -6245,7 +6350,7 @@
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>C124:F124</t>
+          <t>C133:F133</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -6275,7 +6380,7 @@
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>C126:F126</t>
+          <t>C135:F135</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
@@ -6305,7 +6410,7 @@
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>C127:F127</t>
+          <t>C136:F136</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -6335,7 +6440,7 @@
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>C128:F128</t>
+          <t>C137:F137</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
@@ -6365,7 +6470,7 @@
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>C129:F129</t>
+          <t>C138:F138</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
@@ -6395,7 +6500,7 @@
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>B131:F131</t>
+          <t>B140:F140</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
@@ -6425,7 +6530,7 @@
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>B132:F132</t>
+          <t>B141:F141</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -7151,6 +7256,156 @@
       <c r="F131" s="11" t="inlineStr">
         <is>
           <t>gross_margin_change, net_operating_expense_burden_change</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="11" t="n">
+        <v>145</v>
+      </c>
+      <c r="B132" s="11" t="inlineStr">
+        <is>
+          <t>Inventory intensity</t>
+        </is>
+      </c>
+      <c r="C132" s="11" t="inlineStr">
+        <is>
+          <t>2021–2025 (5 cells)</t>
+        </is>
+      </c>
+      <c r="D132" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>B117:F117</t>
+        </is>
+      </c>
+      <c r="F132" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="11" t="n">
+        <v>146</v>
+      </c>
+      <c r="B133" s="11" t="inlineStr">
+        <is>
+          <t>Change in inventory</t>
+        </is>
+      </c>
+      <c r="C133" s="11" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D133" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>C118:F118</t>
+        </is>
+      </c>
+      <c r="F133" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="11" t="n">
+        <v>147</v>
+      </c>
+      <c r="B134" s="11" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect on inventory</t>
+        </is>
+      </c>
+      <c r="C134" s="11" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D134" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>C119:F119</t>
+        </is>
+      </c>
+      <c r="F134" s="11" t="inlineStr">
+        <is>
+          <t>inventory_intensity</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="11" t="n">
+        <v>148</v>
+      </c>
+      <c r="B135" s="11" t="inlineStr">
+        <is>
+          <t>Intensity effect on inventory</t>
+        </is>
+      </c>
+      <c r="C135" s="11" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D135" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>C120:F120</t>
+        </is>
+      </c>
+      <c r="F135" s="11" t="inlineStr">
+        <is>
+          <t>inventory_intensity</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="11" t="n">
+        <v>149</v>
+      </c>
+      <c r="B136" s="11" t="inlineStr">
+        <is>
+          <t>Reconstructed change in inventory</t>
+        </is>
+      </c>
+      <c r="C136" s="11" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D136" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="inlineStr">
+        <is>
+          <t>C121:F121</t>
+        </is>
+      </c>
+      <c r="F136" s="11" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect, inventory_intensity_effect</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S549"/>
+  <dimension ref="A1:S570"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38479,11 +38734,11 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>C116</t>
+          <t>C125</t>
         </is>
       </c>
       <c r="I382">
-        <f>C115-B115</f>
+        <f>C124-B124</f>
         <v/>
       </c>
       <c r="J382" t="n">
@@ -38555,11 +38810,11 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>D116</t>
+          <t>D125</t>
         </is>
       </c>
       <c r="I383">
-        <f>D115-C115</f>
+        <f>D124-C124</f>
         <v/>
       </c>
       <c r="J383" t="n">
@@ -38631,11 +38886,11 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>E116</t>
+          <t>E125</t>
         </is>
       </c>
       <c r="I384">
-        <f>E115-D115</f>
+        <f>E124-D124</f>
         <v/>
       </c>
       <c r="J384" t="n">
@@ -38707,11 +38962,11 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>F116</t>
+          <t>F125</t>
         </is>
       </c>
       <c r="I385">
-        <f>F115-E115</f>
+        <f>F124-E124</f>
         <v/>
       </c>
       <c r="J385" t="n">
@@ -38783,11 +39038,11 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>C117</t>
+          <t>C126</t>
         </is>
       </c>
       <c r="I386">
-        <f>IF(B115=0,NA(),C115/B115-1)</f>
+        <f>IF(B124=0,NA(),C124/B124-1)</f>
         <v/>
       </c>
       <c r="J386" t="n">
@@ -38864,11 +39119,11 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>D117</t>
+          <t>D126</t>
         </is>
       </c>
       <c r="I387">
-        <f>IF(C115=0,NA(),D115/C115-1)</f>
+        <f>IF(C124=0,NA(),D124/C124-1)</f>
         <v/>
       </c>
       <c r="J387" t="n">
@@ -38945,11 +39200,11 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>E117</t>
+          <t>E126</t>
         </is>
       </c>
       <c r="I388">
-        <f>IF(D115=0,NA(),E115/D115-1)</f>
+        <f>IF(D124=0,NA(),E124/D124-1)</f>
         <v/>
       </c>
       <c r="J388" t="n">
@@ -39026,11 +39281,11 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>F117</t>
+          <t>F126</t>
         </is>
       </c>
       <c r="I389">
-        <f>IF(E115=0,NA(),F115/E115-1)</f>
+        <f>IF(E124=0,NA(),F124/E124-1)</f>
         <v/>
       </c>
       <c r="J389" t="n">
@@ -39107,11 +39362,11 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>C118</t>
+          <t>C127</t>
         </is>
       </c>
       <c r="I390">
-        <f>(B115+C115)/2</f>
+        <f>(B124+C124)/2</f>
         <v/>
       </c>
       <c r="J390" t="n">
@@ -39183,11 +39438,11 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>D118</t>
+          <t>D127</t>
         </is>
       </c>
       <c r="I391">
-        <f>(C115+D115)/2</f>
+        <f>(C124+D124)/2</f>
         <v/>
       </c>
       <c r="J391" t="n">
@@ -39259,11 +39514,11 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>E118</t>
+          <t>E127</t>
         </is>
       </c>
       <c r="I392">
-        <f>(D115+E115)/2</f>
+        <f>(D124+E124)/2</f>
         <v/>
       </c>
       <c r="J392" t="n">
@@ -39335,11 +39590,11 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>F118</t>
+          <t>F127</t>
         </is>
       </c>
       <c r="I393">
-        <f>(E115+F115)/2</f>
+        <f>(E124+F124)/2</f>
         <v/>
       </c>
       <c r="J393" t="n">
@@ -39411,11 +39666,11 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>C119</t>
+          <t>C128</t>
         </is>
       </c>
       <c r="I394">
-        <f>IF('Condensed Financials'!C44=0,NA(),C118/'Condensed Financials'!C44)</f>
+        <f>IF('Condensed Financials'!C44=0,NA(),C127/'Condensed Financials'!C44)</f>
         <v/>
       </c>
       <c r="J394" t="n">
@@ -39492,11 +39747,11 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>D119</t>
+          <t>D128</t>
         </is>
       </c>
       <c r="I395">
-        <f>IF('Condensed Financials'!D44=0,NA(),D118/'Condensed Financials'!D44)</f>
+        <f>IF('Condensed Financials'!D44=0,NA(),D127/'Condensed Financials'!D44)</f>
         <v/>
       </c>
       <c r="J395" t="n">
@@ -39573,11 +39828,11 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>E119</t>
+          <t>E128</t>
         </is>
       </c>
       <c r="I396">
-        <f>IF('Condensed Financials'!E44=0,NA(),E118/'Condensed Financials'!E44)</f>
+        <f>IF('Condensed Financials'!E44=0,NA(),E127/'Condensed Financials'!E44)</f>
         <v/>
       </c>
       <c r="J396" t="n">
@@ -39654,11 +39909,11 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>F119</t>
+          <t>F128</t>
         </is>
       </c>
       <c r="I397">
-        <f>IF('Condensed Financials'!F44=0,NA(),F118/'Condensed Financials'!F44)</f>
+        <f>IF('Condensed Financials'!F44=0,NA(),F127/'Condensed Financials'!F44)</f>
         <v/>
       </c>
       <c r="J397" t="n">
@@ -39735,11 +39990,11 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>C121</t>
+          <t>C130</t>
         </is>
       </c>
       <c r="I398">
-        <f>C120-B120</f>
+        <f>C129-B129</f>
         <v/>
       </c>
       <c r="J398" t="n">
@@ -39811,11 +40066,11 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>D121</t>
+          <t>D130</t>
         </is>
       </c>
       <c r="I399">
-        <f>D120-C120</f>
+        <f>D129-C129</f>
         <v/>
       </c>
       <c r="J399" t="n">
@@ -39887,11 +40142,11 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>E121</t>
+          <t>E130</t>
         </is>
       </c>
       <c r="I400">
-        <f>E120-D120</f>
+        <f>E129-D129</f>
         <v/>
       </c>
       <c r="J400" t="n">
@@ -39963,11 +40218,11 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>F121</t>
+          <t>F130</t>
         </is>
       </c>
       <c r="I401">
-        <f>F120-E120</f>
+        <f>F129-E129</f>
         <v/>
       </c>
       <c r="J401" t="n">
@@ -40039,11 +40294,11 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>C122</t>
+          <t>C131</t>
         </is>
       </c>
       <c r="I402">
-        <f>IF(B120=0,NA(),C120/B120-1)</f>
+        <f>IF(B129=0,NA(),C129/B129-1)</f>
         <v/>
       </c>
       <c r="J402" t="n">
@@ -40120,11 +40375,11 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>D122</t>
+          <t>D131</t>
         </is>
       </c>
       <c r="I403">
-        <f>IF(C120=0,NA(),D120/C120-1)</f>
+        <f>IF(C129=0,NA(),D129/C129-1)</f>
         <v/>
       </c>
       <c r="J403" t="n">
@@ -40201,11 +40456,11 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>E122</t>
+          <t>E131</t>
         </is>
       </c>
       <c r="I404">
-        <f>IF(D120=0,NA(),E120/D120-1)</f>
+        <f>IF(D129=0,NA(),E129/D129-1)</f>
         <v/>
       </c>
       <c r="J404" t="n">
@@ -40282,11 +40537,11 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>F122</t>
+          <t>F131</t>
         </is>
       </c>
       <c r="I405">
-        <f>IF(E120=0,NA(),F120/E120-1)</f>
+        <f>IF(E129=0,NA(),F129/E129-1)</f>
         <v/>
       </c>
       <c r="J405" t="n">
@@ -40363,11 +40618,11 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>C123</t>
+          <t>C132</t>
         </is>
       </c>
       <c r="I406">
-        <f>(B120+C120)/2</f>
+        <f>(B129+C129)/2</f>
         <v/>
       </c>
       <c r="J406" t="n">
@@ -40439,11 +40694,11 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>D123</t>
+          <t>D132</t>
         </is>
       </c>
       <c r="I407">
-        <f>(C120+D120)/2</f>
+        <f>(C129+D129)/2</f>
         <v/>
       </c>
       <c r="J407" t="n">
@@ -40515,11 +40770,11 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>E123</t>
+          <t>E132</t>
         </is>
       </c>
       <c r="I408">
-        <f>(D120+E120)/2</f>
+        <f>(D129+E129)/2</f>
         <v/>
       </c>
       <c r="J408" t="n">
@@ -40591,11 +40846,11 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>F123</t>
+          <t>F132</t>
         </is>
       </c>
       <c r="I409">
-        <f>(E120+F120)/2</f>
+        <f>(E129+F129)/2</f>
         <v/>
       </c>
       <c r="J409" t="n">
@@ -40667,11 +40922,11 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>C124</t>
+          <t>C133</t>
         </is>
       </c>
       <c r="I410">
-        <f>IF('Condensed Financials'!C44=0,NA(),C123/'Condensed Financials'!C44)</f>
+        <f>IF('Condensed Financials'!C44=0,NA(),C132/'Condensed Financials'!C44)</f>
         <v/>
       </c>
       <c r="J410" t="n">
@@ -40748,11 +41003,11 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>D124</t>
+          <t>D133</t>
         </is>
       </c>
       <c r="I411">
-        <f>IF('Condensed Financials'!D44=0,NA(),D123/'Condensed Financials'!D44)</f>
+        <f>IF('Condensed Financials'!D44=0,NA(),D132/'Condensed Financials'!D44)</f>
         <v/>
       </c>
       <c r="J411" t="n">
@@ -40829,11 +41084,11 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>E124</t>
+          <t>E133</t>
         </is>
       </c>
       <c r="I412">
-        <f>IF('Condensed Financials'!E44=0,NA(),E123/'Condensed Financials'!E44)</f>
+        <f>IF('Condensed Financials'!E44=0,NA(),E132/'Condensed Financials'!E44)</f>
         <v/>
       </c>
       <c r="J412" t="n">
@@ -40910,11 +41165,11 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>F124</t>
+          <t>F133</t>
         </is>
       </c>
       <c r="I413">
-        <f>IF('Condensed Financials'!F44=0,NA(),F123/'Condensed Financials'!F44)</f>
+        <f>IF('Condensed Financials'!F44=0,NA(),F132/'Condensed Financials'!F44)</f>
         <v/>
       </c>
       <c r="J413" t="n">
@@ -40991,11 +41246,11 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>C126</t>
+          <t>C135</t>
         </is>
       </c>
       <c r="I414">
-        <f>C125-B125</f>
+        <f>C134-B134</f>
         <v/>
       </c>
       <c r="J414" t="n">
@@ -41067,11 +41322,11 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>D126</t>
+          <t>D135</t>
         </is>
       </c>
       <c r="I415">
-        <f>D125-C125</f>
+        <f>D134-C134</f>
         <v/>
       </c>
       <c r="J415" t="n">
@@ -41143,11 +41398,11 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>E126</t>
+          <t>E135</t>
         </is>
       </c>
       <c r="I416">
-        <f>E125-D125</f>
+        <f>E134-D134</f>
         <v/>
       </c>
       <c r="J416" t="n">
@@ -41219,11 +41474,11 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>F126</t>
+          <t>F135</t>
         </is>
       </c>
       <c r="I417">
-        <f>F125-E125</f>
+        <f>F134-E134</f>
         <v/>
       </c>
       <c r="J417" t="n">
@@ -41295,11 +41550,11 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>C127</t>
+          <t>C136</t>
         </is>
       </c>
       <c r="I418">
-        <f>IF(B125=0,NA(),C125/B125-1)</f>
+        <f>IF(B134=0,NA(),C134/B134-1)</f>
         <v/>
       </c>
       <c r="J418" t="n">
@@ -41376,11 +41631,11 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>D127</t>
+          <t>D136</t>
         </is>
       </c>
       <c r="I419">
-        <f>IF(C125=0,NA(),D125/C125-1)</f>
+        <f>IF(C134=0,NA(),D134/C134-1)</f>
         <v/>
       </c>
       <c r="J419" t="n">
@@ -41457,11 +41712,11 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>E127</t>
+          <t>E136</t>
         </is>
       </c>
       <c r="I420">
-        <f>IF(D125=0,NA(),E125/D125-1)</f>
+        <f>IF(D134=0,NA(),E134/D134-1)</f>
         <v/>
       </c>
       <c r="J420" t="n">
@@ -41538,11 +41793,11 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>F127</t>
+          <t>F136</t>
         </is>
       </c>
       <c r="I421">
-        <f>IF(E125=0,NA(),F125/E125-1)</f>
+        <f>IF(E134=0,NA(),F134/E134-1)</f>
         <v/>
       </c>
       <c r="J421" t="n">
@@ -41619,11 +41874,11 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>C128</t>
+          <t>C137</t>
         </is>
       </c>
       <c r="I422">
-        <f>(B125+C125)/2</f>
+        <f>(B134+C134)/2</f>
         <v/>
       </c>
       <c r="J422" t="n">
@@ -41695,11 +41950,11 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>D128</t>
+          <t>D137</t>
         </is>
       </c>
       <c r="I423">
-        <f>(C125+D125)/2</f>
+        <f>(C134+D134)/2</f>
         <v/>
       </c>
       <c r="J423" t="n">
@@ -41771,11 +42026,11 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>E128</t>
+          <t>E137</t>
         </is>
       </c>
       <c r="I424">
-        <f>(D125+E125)/2</f>
+        <f>(D134+E134)/2</f>
         <v/>
       </c>
       <c r="J424" t="n">
@@ -41847,11 +42102,11 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>F128</t>
+          <t>F137</t>
         </is>
       </c>
       <c r="I425">
-        <f>(E125+F125)/2</f>
+        <f>(E134+F134)/2</f>
         <v/>
       </c>
       <c r="J425" t="n">
@@ -41923,11 +42178,11 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>C129</t>
+          <t>C138</t>
         </is>
       </c>
       <c r="I426">
-        <f>IF('Condensed Financials'!C44=0,NA(),C128/'Condensed Financials'!C44)</f>
+        <f>IF('Condensed Financials'!C44=0,NA(),C137/'Condensed Financials'!C44)</f>
         <v/>
       </c>
       <c r="J426" t="n">
@@ -42004,11 +42259,11 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>D129</t>
+          <t>D138</t>
         </is>
       </c>
       <c r="I427">
-        <f>IF('Condensed Financials'!D44=0,NA(),D128/'Condensed Financials'!D44)</f>
+        <f>IF('Condensed Financials'!D44=0,NA(),D137/'Condensed Financials'!D44)</f>
         <v/>
       </c>
       <c r="J427" t="n">
@@ -42085,11 +42340,11 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>E129</t>
+          <t>E138</t>
         </is>
       </c>
       <c r="I428">
-        <f>IF('Condensed Financials'!E44=0,NA(),E128/'Condensed Financials'!E44)</f>
+        <f>IF('Condensed Financials'!E44=0,NA(),E137/'Condensed Financials'!E44)</f>
         <v/>
       </c>
       <c r="J428" t="n">
@@ -42166,11 +42421,11 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>F129</t>
+          <t>F138</t>
         </is>
       </c>
       <c r="I429">
-        <f>IF('Condensed Financials'!F44=0,NA(),F128/'Condensed Financials'!F44)</f>
+        <f>IF('Condensed Financials'!F44=0,NA(),F137/'Condensed Financials'!F44)</f>
         <v/>
       </c>
       <c r="J429" t="n">
@@ -42247,11 +42502,11 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>B131</t>
+          <t>B140</t>
         </is>
       </c>
       <c r="I430">
-        <f>-B130</f>
+        <f>-B139</f>
         <v/>
       </c>
       <c r="J430" t="n">
@@ -42323,11 +42578,11 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>C131</t>
+          <t>C140</t>
         </is>
       </c>
       <c r="I431">
-        <f>-C130</f>
+        <f>-C139</f>
         <v/>
       </c>
       <c r="J431" t="n">
@@ -42399,11 +42654,11 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>D131</t>
+          <t>D140</t>
         </is>
       </c>
       <c r="I432">
-        <f>-D130</f>
+        <f>-D139</f>
         <v/>
       </c>
       <c r="J432" t="n">
@@ -42475,11 +42730,11 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>E131</t>
+          <t>E140</t>
         </is>
       </c>
       <c r="I433">
-        <f>-E130</f>
+        <f>-E139</f>
         <v/>
       </c>
       <c r="J433" t="n">
@@ -42551,11 +42806,11 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>F131</t>
+          <t>F140</t>
         </is>
       </c>
       <c r="I434">
-        <f>-F130</f>
+        <f>-F139</f>
         <v/>
       </c>
       <c r="J434" t="n">
@@ -42627,11 +42882,11 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>B132</t>
+          <t>B141</t>
         </is>
       </c>
       <c r="I435">
-        <f>IF('Condensed Financials'!B44=0,NA(),B131/'Condensed Financials'!B44)</f>
+        <f>IF('Condensed Financials'!B44=0,NA(),B140/'Condensed Financials'!B44)</f>
         <v/>
       </c>
       <c r="J435" t="n">
@@ -42708,11 +42963,11 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>C132</t>
+          <t>C141</t>
         </is>
       </c>
       <c r="I436">
-        <f>IF('Condensed Financials'!C44=0,NA(),C131/'Condensed Financials'!C44)</f>
+        <f>IF('Condensed Financials'!C44=0,NA(),C140/'Condensed Financials'!C44)</f>
         <v/>
       </c>
       <c r="J436" t="n">
@@ -42789,11 +43044,11 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>D132</t>
+          <t>D141</t>
         </is>
       </c>
       <c r="I437">
-        <f>IF('Condensed Financials'!D44=0,NA(),D131/'Condensed Financials'!D44)</f>
+        <f>IF('Condensed Financials'!D44=0,NA(),D140/'Condensed Financials'!D44)</f>
         <v/>
       </c>
       <c r="J437" t="n">
@@ -42870,11 +43125,11 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>E132</t>
+          <t>E141</t>
         </is>
       </c>
       <c r="I438">
-        <f>IF('Condensed Financials'!E44=0,NA(),E131/'Condensed Financials'!E44)</f>
+        <f>IF('Condensed Financials'!E44=0,NA(),E140/'Condensed Financials'!E44)</f>
         <v/>
       </c>
       <c r="J438" t="n">
@@ -42951,11 +43206,11 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>F132</t>
+          <t>F141</t>
         </is>
       </c>
       <c r="I439">
-        <f>IF('Condensed Financials'!F44=0,NA(),F131/'Condensed Financials'!F44)</f>
+        <f>IF('Condensed Financials'!F44=0,NA(),F140/'Condensed Financials'!F44)</f>
         <v/>
       </c>
       <c r="J439" t="n">
@@ -51646,6 +51901,1662 @@
         <v>4</v>
       </c>
       <c r="S549" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>inventory_intensity__20210831</t>
+        </is>
+      </c>
+      <c r="B550" t="n">
+        <v>549</v>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Inventory intensity</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Inventory intensity = ending inventory / annual revenue. This is not inventory days or turnover. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_intensity.2021-08-31</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>B117</t>
+        </is>
+      </c>
+      <c r="I550">
+        <f>IF(B116=0,NA(),B115/B116)</f>
+        <v/>
+      </c>
+      <c r="J550" t="n">
+        <v>0.1851239948391743</v>
+      </c>
+      <c r="K550" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M550" t="inlineStr">
+        <is>
+          <t>Inventory intensity = ending inventory / annual revenue.|This is not inventory days or turnover.|Zero revenue yields the undefined-ratio result.</t>
+        </is>
+      </c>
+      <c r="O550" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P550" t="inlineStr">
+        <is>
+          <t>inventory_intensity</t>
+        </is>
+      </c>
+      <c r="Q550" t="n">
+        <v>145</v>
+      </c>
+      <c r="R550" t="n">
+        <v>0</v>
+      </c>
+      <c r="S550" t="inlineStr">
+        <is>
+          <t>2021-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>inventory_intensity__20220831</t>
+        </is>
+      </c>
+      <c r="B551" t="n">
+        <v>550</v>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Inventory intensity</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Inventory intensity = ending inventory / annual revenue. This is not inventory days or turnover. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_intensity.2022-08-31</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>C117</t>
+        </is>
+      </c>
+      <c r="I551">
+        <f>IF(C116=0,NA(),C115/C116)</f>
+        <v/>
+      </c>
+      <c r="J551" t="n">
+        <v>0.2111700292292195</v>
+      </c>
+      <c r="K551" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M551" t="inlineStr">
+        <is>
+          <t>Inventory intensity = ending inventory / annual revenue.|This is not inventory days or turnover.|Zero revenue yields the undefined-ratio result.</t>
+        </is>
+      </c>
+      <c r="O551" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P551" t="inlineStr">
+        <is>
+          <t>inventory_intensity</t>
+        </is>
+      </c>
+      <c r="Q551" t="n">
+        <v>145</v>
+      </c>
+      <c r="R551" t="n">
+        <v>1</v>
+      </c>
+      <c r="S551" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>inventory_intensity__20230831</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>551</v>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Inventory intensity</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Inventory intensity = ending inventory / annual revenue. This is not inventory days or turnover. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_intensity.2023-08-31</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>D117</t>
+        </is>
+      </c>
+      <c r="I552">
+        <f>IF(D116=0,NA(),D115/D116)</f>
+        <v/>
+      </c>
+      <c r="J552" t="n">
+        <v>0.1623874006572068</v>
+      </c>
+      <c r="K552" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M552" t="inlineStr">
+        <is>
+          <t>Inventory intensity = ending inventory / annual revenue.|This is not inventory days or turnover.|Zero revenue yields the undefined-ratio result.</t>
+        </is>
+      </c>
+      <c r="O552" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P552" t="inlineStr">
+        <is>
+          <t>inventory_intensity</t>
+        </is>
+      </c>
+      <c r="Q552" t="n">
+        <v>145</v>
+      </c>
+      <c r="R552" t="n">
+        <v>2</v>
+      </c>
+      <c r="S552" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>inventory_intensity__20240831</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>552</v>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Inventory intensity</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Inventory intensity = ending inventory / annual revenue. This is not inventory days or turnover. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_intensity.2024-08-31</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>E117</t>
+        </is>
+      </c>
+      <c r="I553">
+        <f>IF(E116=0,NA(),E115/E116)</f>
+        <v/>
+      </c>
+      <c r="J553" t="n">
+        <v>0.1528624579391437</v>
+      </c>
+      <c r="K553" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M553" t="inlineStr">
+        <is>
+          <t>Inventory intensity = ending inventory / annual revenue.|This is not inventory days or turnover.|Zero revenue yields the undefined-ratio result.</t>
+        </is>
+      </c>
+      <c r="O553" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P553" t="inlineStr">
+        <is>
+          <t>inventory_intensity</t>
+        </is>
+      </c>
+      <c r="Q553" t="n">
+        <v>145</v>
+      </c>
+      <c r="R553" t="n">
+        <v>3</v>
+      </c>
+      <c r="S553" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>inventory_intensity__20250831</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>553</v>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Inventory intensity</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Inventory intensity = ending inventory / annual revenue. This is not inventory days or turnover. Zero revenue is undefined (#N/A).</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_intensity.2025-08-31</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>F117</t>
+        </is>
+      </c>
+      <c r="I554">
+        <f>IF(F116=0,NA(),F115/F116)</f>
+        <v/>
+      </c>
+      <c r="J554" t="n">
+        <v>0.1502579444023433</v>
+      </c>
+      <c r="K554" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M554" t="inlineStr">
+        <is>
+          <t>Inventory intensity = ending inventory / annual revenue.|This is not inventory days or turnover.|Zero revenue yields the undefined-ratio result.</t>
+        </is>
+      </c>
+      <c r="O554" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P554" t="inlineStr">
+        <is>
+          <t>inventory_intensity</t>
+        </is>
+      </c>
+      <c r="Q554" t="n">
+        <v>145</v>
+      </c>
+      <c r="R554" t="n">
+        <v>4</v>
+      </c>
+      <c r="S554" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>inventory_change__20220831</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>554</v>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Change in inventory</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Change in inventory = current inventory − prior inventory (signed). Opening-period change is not practiced. This is not proof of cash movement, markdowns, or management causes.</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_change.2022-08-31</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>C118</t>
+        </is>
+      </c>
+      <c r="I555">
+        <f>C115-B115</f>
+        <v/>
+      </c>
+      <c r="J555" t="n">
+        <v>91060</v>
+      </c>
+      <c r="K555" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>Change in inventory = current inventory − prior inventory.|The movement is signed; it is not proof of cash movement.|Do not infer markdowns or management causes.</t>
+        </is>
+      </c>
+      <c r="O555" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P555" t="inlineStr">
+        <is>
+          <t>inventory_change</t>
+        </is>
+      </c>
+      <c r="Q555" t="n">
+        <v>146</v>
+      </c>
+      <c r="R555" t="n">
+        <v>1</v>
+      </c>
+      <c r="S555" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>inventory_change__20230831</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>555</v>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Change in inventory</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Change in inventory = current inventory − prior inventory (signed). Opening-period change is not practiced. This is not proof of cash movement, markdowns, or management causes.</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_change.2023-08-31</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>D118</t>
+        </is>
+      </c>
+      <c r="I556">
+        <f>D115-C115</f>
+        <v/>
+      </c>
+      <c r="J556" t="n">
+        <v>-36674</v>
+      </c>
+      <c r="K556" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>Change in inventory = current inventory − prior inventory.|The movement is signed; it is not proof of cash movement.|Do not infer markdowns or management causes.</t>
+        </is>
+      </c>
+      <c r="O556" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P556" t="inlineStr">
+        <is>
+          <t>inventory_change</t>
+        </is>
+      </c>
+      <c r="Q556" t="n">
+        <v>146</v>
+      </c>
+      <c r="R556" t="n">
+        <v>2</v>
+      </c>
+      <c r="S556" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>inventory_change__20240831</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>556</v>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Change in inventory</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Change in inventory = current inventory − prior inventory (signed). Opening-period change is not practiced. This is not proof of cash movement, markdowns, or management causes.</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_change.2024-08-31</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>E118</t>
+        </is>
+      </c>
+      <c r="I557">
+        <f>E115-D115</f>
+        <v/>
+      </c>
+      <c r="J557" t="n">
+        <v>25206</v>
+      </c>
+      <c r="K557" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>Change in inventory = current inventory − prior inventory.|The movement is signed; it is not proof of cash movement.|Do not infer markdowns or management causes.</t>
+        </is>
+      </c>
+      <c r="O557" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P557" t="inlineStr">
+        <is>
+          <t>inventory_change</t>
+        </is>
+      </c>
+      <c r="Q557" t="n">
+        <v>146</v>
+      </c>
+      <c r="R557" t="n">
+        <v>3</v>
+      </c>
+      <c r="S557" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>inventory_change__20250831</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>557</v>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Change in inventory</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Change in inventory = current inventory − prior inventory (signed). Opening-period change is not practiced. This is not proof of cash movement, markdowns, or management causes.</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_change.2025-08-31</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>F118</t>
+        </is>
+      </c>
+      <c r="I558">
+        <f>F115-E115</f>
+        <v/>
+      </c>
+      <c r="J558" t="n">
+        <v>36498</v>
+      </c>
+      <c r="K558" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>Change in inventory = current inventory − prior inventory.|The movement is signed; it is not proof of cash movement.|Do not infer markdowns or management causes.</t>
+        </is>
+      </c>
+      <c r="O558" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P558" t="inlineStr">
+        <is>
+          <t>inventory_change</t>
+        </is>
+      </c>
+      <c r="Q558" t="n">
+        <v>146</v>
+      </c>
+      <c r="R558" t="n">
+        <v>4</v>
+      </c>
+      <c r="S558" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect__20220831</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>558</v>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect on inventory</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect = prior inventory intensity × (current revenue − prior revenue). Uses the prior-intensity / current-revenue attribution convention. Signed; not a cash-movement proof.</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_revenue_scale_effect.2022-08-31</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>C119</t>
+        </is>
+      </c>
+      <c r="I559">
+        <f>B117*(C116-B116)</f>
+        <v/>
+      </c>
+      <c r="J559" t="n">
+        <v>31124.89725231037</v>
+      </c>
+      <c r="K559" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>inventory_intensity__20210831</t>
+        </is>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect = prior inventory intensity × (current revenue − prior revenue).|This uses the prior-intensity / current-revenue convention.|Signed arithmetic only; not proof of cash movement.</t>
+        </is>
+      </c>
+      <c r="O559" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P559" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect</t>
+        </is>
+      </c>
+      <c r="Q559" t="n">
+        <v>147</v>
+      </c>
+      <c r="R559" t="n">
+        <v>1</v>
+      </c>
+      <c r="S559" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect__20230831</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>559</v>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect on inventory</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect = prior inventory intensity × (current revenue − prior revenue). Uses the prior-intensity / current-revenue attribution convention. Signed; not a cash-movement proof.</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_revenue_scale_effect.2023-08-31</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>D119</t>
+        </is>
+      </c>
+      <c r="I560">
+        <f>C117*(D116-C116)</f>
+        <v/>
+      </c>
+      <c r="J560" t="n">
+        <v>98285.92255430177</v>
+      </c>
+      <c r="K560" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>inventory_intensity__20220831</t>
+        </is>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect = prior inventory intensity × (current revenue − prior revenue).|This uses the prior-intensity / current-revenue convention.|Signed arithmetic only; not proof of cash movement.</t>
+        </is>
+      </c>
+      <c r="O560" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P560" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect</t>
+        </is>
+      </c>
+      <c r="Q560" t="n">
+        <v>147</v>
+      </c>
+      <c r="R560" t="n">
+        <v>2</v>
+      </c>
+      <c r="S560" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect__20240831</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>560</v>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect on inventory</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect = prior inventory intensity × (current revenue − prior revenue). Uses the prior-intensity / current-revenue attribution convention. Signed; not a cash-movement proof.</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_revenue_scale_effect.2024-08-31</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>E119</t>
+        </is>
+      </c>
+      <c r="I561">
+        <f>D117*(E116-D116)</f>
+        <v/>
+      </c>
+      <c r="J561" t="n">
+        <v>54769.86010626204</v>
+      </c>
+      <c r="K561" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>inventory_intensity__20230831</t>
+        </is>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect = prior inventory intensity × (current revenue − prior revenue).|This uses the prior-intensity / current-revenue convention.|Signed arithmetic only; not proof of cash movement.</t>
+        </is>
+      </c>
+      <c r="O561" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P561" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect</t>
+        </is>
+      </c>
+      <c r="Q561" t="n">
+        <v>147</v>
+      </c>
+      <c r="R561" t="n">
+        <v>3</v>
+      </c>
+      <c r="S561" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect__20250831</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>561</v>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect on inventory</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect = prior inventory intensity × (current revenue − prior revenue). Uses the prior-intensity / current-revenue attribution convention. Signed; not a cash-movement proof.</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_revenue_scale_effect.2025-08-31</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>F119</t>
+        </is>
+      </c>
+      <c r="I562">
+        <f>E117*(F116-E116)</f>
+        <v/>
+      </c>
+      <c r="J562" t="n">
+        <v>45354.74985791775</v>
+      </c>
+      <c r="K562" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>inventory_intensity__20240831</t>
+        </is>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>Revenue-scale effect = prior inventory intensity × (current revenue − prior revenue).|This uses the prior-intensity / current-revenue convention.|Signed arithmetic only; not proof of cash movement.</t>
+        </is>
+      </c>
+      <c r="O562" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P562" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect</t>
+        </is>
+      </c>
+      <c r="Q562" t="n">
+        <v>147</v>
+      </c>
+      <c r="R562" t="n">
+        <v>4</v>
+      </c>
+      <c r="S562" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>inventory_intensity_effect__20220831</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>562</v>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Intensity effect on inventory</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Intensity effect = current revenue × (current inventory intensity − prior inventory intensity). Uses the prior-intensity / current-revenue attribution convention. Signed; not proof of deterioration, seasonality, or markdowns.</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_intensity_effect.2022-08-31</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>C120</t>
+        </is>
+      </c>
+      <c r="I563">
+        <f>C116*(C117-B117)</f>
+        <v/>
+      </c>
+      <c r="J563" t="n">
+        <v>59935.10274768962</v>
+      </c>
+      <c r="K563" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>inventory_intensity__20220831,inventory_intensity__20210831</t>
+        </is>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>Intensity effect = current revenue × (current intensity − prior intensity).|This uses the prior-intensity / current-revenue convention.|Signed arithmetic only; not proof of deterioration, seasonality, or markdowns.</t>
+        </is>
+      </c>
+      <c r="O563" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P563" t="inlineStr">
+        <is>
+          <t>inventory_intensity_effect</t>
+        </is>
+      </c>
+      <c r="Q563" t="n">
+        <v>148</v>
+      </c>
+      <c r="R563" t="n">
+        <v>1</v>
+      </c>
+      <c r="S563" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>inventory_intensity_effect__20230831</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>563</v>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Intensity effect on inventory</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Intensity effect = current revenue × (current inventory intensity − prior inventory intensity). Uses the prior-intensity / current-revenue attribution convention. Signed; not proof of deterioration, seasonality, or markdowns.</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_intensity_effect.2023-08-31</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>D120</t>
+        </is>
+      </c>
+      <c r="I564">
+        <f>D116*(D117-C117)</f>
+        <v/>
+      </c>
+      <c r="J564" t="n">
+        <v>-134959.9225543018</v>
+      </c>
+      <c r="K564" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>inventory_intensity__20230831,inventory_intensity__20220831</t>
+        </is>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>Intensity effect = current revenue × (current intensity − prior intensity).|This uses the prior-intensity / current-revenue convention.|Signed arithmetic only; not proof of deterioration, seasonality, or markdowns.</t>
+        </is>
+      </c>
+      <c r="O564" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P564" t="inlineStr">
+        <is>
+          <t>inventory_intensity_effect</t>
+        </is>
+      </c>
+      <c r="Q564" t="n">
+        <v>148</v>
+      </c>
+      <c r="R564" t="n">
+        <v>2</v>
+      </c>
+      <c r="S564" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>inventory_intensity_effect__20240831</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>564</v>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Intensity effect on inventory</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Intensity effect = current revenue × (current inventory intensity − prior inventory intensity). Uses the prior-intensity / current-revenue attribution convention. Signed; not proof of deterioration, seasonality, or markdowns.</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_intensity_effect.2024-08-31</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>E120</t>
+        </is>
+      </c>
+      <c r="I565">
+        <f>E116*(E117-D117)</f>
+        <v/>
+      </c>
+      <c r="J565" t="n">
+        <v>-29563.86010626207</v>
+      </c>
+      <c r="K565" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>inventory_intensity__20240831,inventory_intensity__20230831</t>
+        </is>
+      </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>Intensity effect = current revenue × (current intensity − prior intensity).|This uses the prior-intensity / current-revenue convention.|Signed arithmetic only; not proof of deterioration, seasonality, or markdowns.</t>
+        </is>
+      </c>
+      <c r="O565" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P565" t="inlineStr">
+        <is>
+          <t>inventory_intensity_effect</t>
+        </is>
+      </c>
+      <c r="Q565" t="n">
+        <v>148</v>
+      </c>
+      <c r="R565" t="n">
+        <v>3</v>
+      </c>
+      <c r="S565" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>inventory_intensity_effect__20250831</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>565</v>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Intensity effect on inventory</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Intensity effect = current revenue × (current inventory intensity − prior inventory intensity). Uses the prior-intensity / current-revenue attribution convention. Signed; not proof of deterioration, seasonality, or markdowns.</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_intensity_effect.2025-08-31</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>F120</t>
+        </is>
+      </c>
+      <c r="I566">
+        <f>F116*(F117-E117)</f>
+        <v/>
+      </c>
+      <c r="J566" t="n">
+        <v>-8856.749857917737</v>
+      </c>
+      <c r="K566" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>inventory_intensity__20250831,inventory_intensity__20240831</t>
+        </is>
+      </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>Intensity effect = current revenue × (current intensity − prior intensity).|This uses the prior-intensity / current-revenue convention.|Signed arithmetic only; not proof of deterioration, seasonality, or markdowns.</t>
+        </is>
+      </c>
+      <c r="O566" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P566" t="inlineStr">
+        <is>
+          <t>inventory_intensity_effect</t>
+        </is>
+      </c>
+      <c r="Q566" t="n">
+        <v>148</v>
+      </c>
+      <c r="R566" t="n">
+        <v>4</v>
+      </c>
+      <c r="S566" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>reconstructed_inventory_change__20220831</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>566</v>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Reconstructed change in inventory</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Reconstructed inventory change = revenue-scale effect + intensity effect. Arithmetic decomposition that reconciles to the inventory change when defined. Not inventory days/turnover and not proof of cash movement, deterioration, seasonality, markdowns, or management causes.</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>inventory_analysis.reconstructed_inventory_change.2022-08-31</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>C121</t>
+        </is>
+      </c>
+      <c r="I567">
+        <f>C119+C120</f>
+        <v/>
+      </c>
+      <c r="J567" t="n">
+        <v>91059.99999999999</v>
+      </c>
+      <c r="K567" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect__20220831,inventory_intensity_effect__20220831</t>
+        </is>
+      </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>Reconstructed inventory change = revenue-scale effect + intensity effect.|When defined, this reconciles to the adjacent inventory change.|Arithmetic decomposition only; not cash movement, deterioration, seasonality, markdowns, or management causes.</t>
+        </is>
+      </c>
+      <c r="O567" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P567" t="inlineStr">
+        <is>
+          <t>reconstructed_inventory_change</t>
+        </is>
+      </c>
+      <c r="Q567" t="n">
+        <v>149</v>
+      </c>
+      <c r="R567" t="n">
+        <v>1</v>
+      </c>
+      <c r="S567" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>reconstructed_inventory_change__20230831</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>567</v>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Reconstructed change in inventory</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Reconstructed inventory change = revenue-scale effect + intensity effect. Arithmetic decomposition that reconciles to the inventory change when defined. Not inventory days/turnover and not proof of cash movement, deterioration, seasonality, markdowns, or management causes.</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>inventory_analysis.reconstructed_inventory_change.2023-08-31</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>D121</t>
+        </is>
+      </c>
+      <c r="I568">
+        <f>D119+D120</f>
+        <v/>
+      </c>
+      <c r="J568" t="n">
+        <v>-36674</v>
+      </c>
+      <c r="K568" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect__20230831,inventory_intensity_effect__20230831</t>
+        </is>
+      </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>Reconstructed inventory change = revenue-scale effect + intensity effect.|When defined, this reconciles to the adjacent inventory change.|Arithmetic decomposition only; not cash movement, deterioration, seasonality, markdowns, or management causes.</t>
+        </is>
+      </c>
+      <c r="O568" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P568" t="inlineStr">
+        <is>
+          <t>reconstructed_inventory_change</t>
+        </is>
+      </c>
+      <c r="Q568" t="n">
+        <v>149</v>
+      </c>
+      <c r="R568" t="n">
+        <v>2</v>
+      </c>
+      <c r="S568" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>reconstructed_inventory_change__20240831</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>568</v>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Reconstructed change in inventory</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Reconstructed inventory change = revenue-scale effect + intensity effect. Arithmetic decomposition that reconciles to the inventory change when defined. Not inventory days/turnover and not proof of cash movement, deterioration, seasonality, markdowns, or management causes.</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>inventory_analysis.reconstructed_inventory_change.2024-08-31</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>E121</t>
+        </is>
+      </c>
+      <c r="I569">
+        <f>E119+E120</f>
+        <v/>
+      </c>
+      <c r="J569" t="n">
+        <v>25205.99999999997</v>
+      </c>
+      <c r="K569" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect__20240831,inventory_intensity_effect__20240831</t>
+        </is>
+      </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>Reconstructed inventory change = revenue-scale effect + intensity effect.|When defined, this reconciles to the adjacent inventory change.|Arithmetic decomposition only; not cash movement, deterioration, seasonality, markdowns, or management causes.</t>
+        </is>
+      </c>
+      <c r="O569" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P569" t="inlineStr">
+        <is>
+          <t>reconstructed_inventory_change</t>
+        </is>
+      </c>
+      <c r="Q569" t="n">
+        <v>149</v>
+      </c>
+      <c r="R569" t="n">
+        <v>3</v>
+      </c>
+      <c r="S569" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>reconstructed_inventory_change__20250831</t>
+        </is>
+      </c>
+      <c r="B570" t="n">
+        <v>569</v>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Reconstructed change in inventory</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Reconstructed inventory change = revenue-scale effect + intensity effect. Arithmetic decomposition that reconciles to the inventory change when defined. Not inventory days/turnover and not proof of cash movement, deterioration, seasonality, markdowns, or management causes.</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>inventory_analysis.reconstructed_inventory_change.2025-08-31</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>F121</t>
+        </is>
+      </c>
+      <c r="I570">
+        <f>F119+F120</f>
+        <v/>
+      </c>
+      <c r="J570" t="n">
+        <v>36498.00000000001</v>
+      </c>
+      <c r="K570" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>inventory_revenue_scale_effect__20250831,inventory_intensity_effect__20250831</t>
+        </is>
+      </c>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>Reconstructed inventory change = revenue-scale effect + intensity effect.|When defined, this reconciles to the adjacent inventory change.|Arithmetic decomposition only; not cash movement, deterioration, seasonality, markdowns, or management causes.</t>
+        </is>
+      </c>
+      <c r="O570" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P570" t="inlineStr">
+        <is>
+          <t>reconstructed_inventory_change</t>
+        </is>
+      </c>
+      <c r="Q570" t="n">
+        <v>149</v>
+      </c>
+      <c r="R570" t="n">
+        <v>4</v>
+      </c>
+      <c r="S570" t="inlineStr">
         <is>
           <t>2025-08-31</t>
         </is>
@@ -56036,7 +57947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -58416,445 +60327,626 @@
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+          <t>INVENTORY GROWTH AND INTENSITY CONTEXT</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>Goodwill</t>
+          <t>Inventory (reported)</t>
         </is>
       </c>
       <c r="B115" s="13">
-        <f>'Balance Sheet'!B37</f>
+        <f>'Balance Sheet'!B11</f>
         <v/>
       </c>
       <c r="C115" s="13">
-        <f>'Balance Sheet'!C37</f>
+        <f>'Balance Sheet'!C11</f>
         <v/>
       </c>
       <c r="D115" s="13">
-        <f>'Balance Sheet'!D37</f>
+        <f>'Balance Sheet'!D11</f>
         <v/>
       </c>
       <c r="E115" s="13">
-        <f>'Balance Sheet'!E37</f>
+        <f>'Balance Sheet'!E11</f>
         <v/>
       </c>
       <c r="F115" s="13">
-        <f>'Balance Sheet'!F37</f>
+        <f>'Balance Sheet'!F11</f>
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t>Change in Goodwill</t>
-        </is>
-      </c>
-      <c r="C116" s="16">
-        <f>C115-B115</f>
-        <v/>
-      </c>
-      <c r="D116" s="16">
-        <f>D115-C115</f>
-        <v/>
-      </c>
-      <c r="E116" s="16">
-        <f>E115-D115</f>
-        <v/>
-      </c>
-      <c r="F116" s="16">
-        <f>F115-E115</f>
+          <t>Revenue (reported)</t>
+        </is>
+      </c>
+      <c r="B116" s="13">
+        <f>'Income Statement'!B21</f>
+        <v/>
+      </c>
+      <c r="C116" s="13">
+        <f>'Income Statement'!C21</f>
+        <v/>
+      </c>
+      <c r="D116" s="13">
+        <f>'Income Statement'!D21</f>
+        <v/>
+      </c>
+      <c r="E116" s="13">
+        <f>'Income Statement'!E21</f>
+        <v/>
+      </c>
+      <c r="F116" s="13">
+        <f>'Income Statement'!F21</f>
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
+          <t>Inventory intensity</t>
+        </is>
+      </c>
+      <c r="B117" s="15">
+        <f>IF(B116=0,NA(),B115/B116)</f>
+        <v/>
       </c>
       <c r="C117" s="15">
-        <f>IF(B115=0,NA(),C115/B115-1)</f>
+        <f>IF(C116=0,NA(),C115/C116)</f>
         <v/>
       </c>
       <c r="D117" s="15">
-        <f>IF(C115=0,NA(),D115/C115-1)</f>
+        <f>IF(D116=0,NA(),D115/D116)</f>
         <v/>
       </c>
       <c r="E117" s="15">
-        <f>IF(D115=0,NA(),E115/D115-1)</f>
+        <f>IF(E116=0,NA(),E115/E116)</f>
         <v/>
       </c>
       <c r="F117" s="15">
-        <f>IF(E115=0,NA(),F115/E115-1)</f>
+        <f>IF(F116=0,NA(),F115/F116)</f>
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill</t>
+          <t>Change in inventory</t>
         </is>
       </c>
       <c r="C118" s="16">
-        <f>(B115+C115)/2</f>
+        <f>C115-B115</f>
         <v/>
       </c>
       <c r="D118" s="16">
-        <f>(C115+D115)/2</f>
+        <f>D115-C115</f>
         <v/>
       </c>
       <c r="E118" s="16">
-        <f>(D115+E115)/2</f>
+        <f>E115-D115</f>
         <v/>
       </c>
       <c r="F118" s="16">
-        <f>(E115+F115)/2</f>
+        <f>F115-E115</f>
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
-      <c r="C119" s="15">
-        <f>IF('Condensed Financials'!C44=0,NA(),C118/'Condensed Financials'!C44)</f>
-        <v/>
-      </c>
-      <c r="D119" s="15">
-        <f>IF('Condensed Financials'!D44=0,NA(),D118/'Condensed Financials'!D44)</f>
-        <v/>
-      </c>
-      <c r="E119" s="15">
-        <f>IF('Condensed Financials'!E44=0,NA(),E118/'Condensed Financials'!E44)</f>
-        <v/>
-      </c>
-      <c r="F119" s="15">
-        <f>IF('Condensed Financials'!F44=0,NA(),F118/'Condensed Financials'!F44)</f>
+          <t>Revenue-scale effect on inventory</t>
+        </is>
+      </c>
+      <c r="C119" s="16">
+        <f>B117*(C116-B116)</f>
+        <v/>
+      </c>
+      <c r="D119" s="16">
+        <f>C117*(D116-C116)</f>
+        <v/>
+      </c>
+      <c r="E119" s="16">
+        <f>D117*(E116-D116)</f>
+        <v/>
+      </c>
+      <c r="F119" s="16">
+        <f>E117*(F116-E116)</f>
         <v/>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
-        </is>
-      </c>
-      <c r="B120" s="13">
-        <f>'Balance Sheet'!B38</f>
-        <v/>
-      </c>
-      <c r="C120" s="13">
-        <f>'Balance Sheet'!C38</f>
-        <v/>
-      </c>
-      <c r="D120" s="13">
-        <f>'Balance Sheet'!D38</f>
-        <v/>
-      </c>
-      <c r="E120" s="13">
-        <f>'Balance Sheet'!E38</f>
-        <v/>
-      </c>
-      <c r="F120" s="13">
-        <f>'Balance Sheet'!F38</f>
+          <t>Intensity effect on inventory</t>
+        </is>
+      </c>
+      <c r="C120" s="16">
+        <f>C116*(C117-B117)</f>
+        <v/>
+      </c>
+      <c r="D120" s="16">
+        <f>D116*(D117-C117)</f>
+        <v/>
+      </c>
+      <c r="E120" s="16">
+        <f>E116*(E117-D117)</f>
+        <v/>
+      </c>
+      <c r="F120" s="16">
+        <f>F116*(F117-E117)</f>
         <v/>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>Change in Intangible Assets</t>
+          <t>Reconstructed change in inventory</t>
         </is>
       </c>
       <c r="C121" s="16">
-        <f>C120-B120</f>
+        <f>C119+C120</f>
         <v/>
       </c>
       <c r="D121" s="16">
-        <f>D120-C120</f>
+        <f>D119+D120</f>
         <v/>
       </c>
       <c r="E121" s="16">
-        <f>E120-D120</f>
+        <f>E119+E120</f>
         <v/>
       </c>
       <c r="F121" s="16">
-        <f>F120-E120</f>
-        <v/>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="11" t="inlineStr">
-        <is>
-          <t>Intangible Assets Growth</t>
-        </is>
-      </c>
-      <c r="C122" s="15">
-        <f>IF(B120=0,NA(),C120/B120-1)</f>
-        <v/>
-      </c>
-      <c r="D122" s="15">
-        <f>IF(C120=0,NA(),D120/C120-1)</f>
-        <v/>
-      </c>
-      <c r="E122" s="15">
-        <f>IF(D120=0,NA(),E120/D120-1)</f>
-        <v/>
-      </c>
-      <c r="F122" s="15">
-        <f>IF(E120=0,NA(),F120/E120-1)</f>
-        <v/>
-      </c>
-    </row>
+        <f>F119+F120</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122"/>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C123" s="16">
-        <f>(B120+C120)/2</f>
-        <v/>
-      </c>
-      <c r="D123" s="16">
-        <f>(C120+D120)/2</f>
-        <v/>
-      </c>
-      <c r="E123" s="16">
-        <f>(D120+E120)/2</f>
-        <v/>
-      </c>
-      <c r="F123" s="16">
-        <f>(E120+F120)/2</f>
-        <v/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>Average Intangible Assets / Revenue</t>
-        </is>
-      </c>
-      <c r="C124" s="15">
-        <f>IF('Condensed Financials'!C44=0,NA(),C123/'Condensed Financials'!C44)</f>
-        <v/>
-      </c>
-      <c r="D124" s="15">
-        <f>IF('Condensed Financials'!D44=0,NA(),D123/'Condensed Financials'!D44)</f>
-        <v/>
-      </c>
-      <c r="E124" s="15">
-        <f>IF('Condensed Financials'!E44=0,NA(),E123/'Condensed Financials'!E44)</f>
-        <v/>
-      </c>
-      <c r="F124" s="15">
-        <f>IF('Condensed Financials'!F44=0,NA(),F123/'Condensed Financials'!F44)</f>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B124" s="13">
+        <f>'Balance Sheet'!B37</f>
+        <v/>
+      </c>
+      <c r="C124" s="13">
+        <f>'Balance Sheet'!C37</f>
+        <v/>
+      </c>
+      <c r="D124" s="13">
+        <f>'Balance Sheet'!D37</f>
+        <v/>
+      </c>
+      <c r="E124" s="13">
+        <f>'Balance Sheet'!E37</f>
+        <v/>
+      </c>
+      <c r="F124" s="13">
+        <f>'Balance Sheet'!F37</f>
         <v/>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="B125" s="13">
-        <f>B115+B120</f>
-        <v/>
-      </c>
-      <c r="C125" s="13">
-        <f>C115+C120</f>
-        <v/>
-      </c>
-      <c r="D125" s="13">
-        <f>D115+D120</f>
-        <v/>
-      </c>
-      <c r="E125" s="13">
-        <f>E115+E120</f>
-        <v/>
-      </c>
-      <c r="F125" s="13">
-        <f>F115+F120</f>
+          <t>Change in Goodwill</t>
+        </is>
+      </c>
+      <c r="C125" s="16">
+        <f>C124-B124</f>
+        <v/>
+      </c>
+      <c r="D125" s="16">
+        <f>D124-C124</f>
+        <v/>
+      </c>
+      <c r="E125" s="16">
+        <f>E124-D124</f>
+        <v/>
+      </c>
+      <c r="F125" s="16">
+        <f>F124-E124</f>
         <v/>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C126" s="16">
-        <f>C125-B125</f>
-        <v/>
-      </c>
-      <c r="D126" s="16">
-        <f>D125-C125</f>
-        <v/>
-      </c>
-      <c r="E126" s="16">
-        <f>E125-D125</f>
-        <v/>
-      </c>
-      <c r="F126" s="16">
-        <f>F125-E125</f>
+          <t>Goodwill Growth</t>
+        </is>
+      </c>
+      <c r="C126" s="15">
+        <f>IF(B124=0,NA(),C124/B124-1)</f>
+        <v/>
+      </c>
+      <c r="D126" s="15">
+        <f>IF(C124=0,NA(),D124/C124-1)</f>
+        <v/>
+      </c>
+      <c r="E126" s="15">
+        <f>IF(D124=0,NA(),E124/D124-1)</f>
+        <v/>
+      </c>
+      <c r="F126" s="15">
+        <f>IF(E124=0,NA(),F124/E124-1)</f>
         <v/>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
-        </is>
-      </c>
-      <c r="C127" s="15">
-        <f>IF(B125=0,NA(),C125/B125-1)</f>
-        <v/>
-      </c>
-      <c r="D127" s="15">
-        <f>IF(C125=0,NA(),D125/C125-1)</f>
-        <v/>
-      </c>
-      <c r="E127" s="15">
-        <f>IF(D125=0,NA(),E125/D125-1)</f>
-        <v/>
-      </c>
-      <c r="F127" s="15">
-        <f>IF(E125=0,NA(),F125/E125-1)</f>
+          <t>Average Goodwill</t>
+        </is>
+      </c>
+      <c r="C127" s="16">
+        <f>(B124+C124)/2</f>
+        <v/>
+      </c>
+      <c r="D127" s="16">
+        <f>(C124+D124)/2</f>
+        <v/>
+      </c>
+      <c r="E127" s="16">
+        <f>(D124+E124)/2</f>
+        <v/>
+      </c>
+      <c r="F127" s="16">
+        <f>(E124+F124)/2</f>
         <v/>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C128" s="16">
-        <f>(B125+C125)/2</f>
-        <v/>
-      </c>
-      <c r="D128" s="16">
-        <f>(C125+D125)/2</f>
-        <v/>
-      </c>
-      <c r="E128" s="16">
-        <f>(D125+E125)/2</f>
-        <v/>
-      </c>
-      <c r="F128" s="16">
-        <f>(E125+F125)/2</f>
+          <t>Average Goodwill / Revenue</t>
+        </is>
+      </c>
+      <c r="C128" s="15">
+        <f>IF('Condensed Financials'!C44=0,NA(),C127/'Condensed Financials'!C44)</f>
+        <v/>
+      </c>
+      <c r="D128" s="15">
+        <f>IF('Condensed Financials'!D44=0,NA(),D127/'Condensed Financials'!D44)</f>
+        <v/>
+      </c>
+      <c r="E128" s="15">
+        <f>IF('Condensed Financials'!E44=0,NA(),E127/'Condensed Financials'!E44)</f>
+        <v/>
+      </c>
+      <c r="F128" s="15">
+        <f>IF('Condensed Financials'!F44=0,NA(),F127/'Condensed Financials'!F44)</f>
         <v/>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles / Revenue</t>
-        </is>
-      </c>
-      <c r="C129" s="15">
-        <f>IF('Condensed Financials'!C44=0,NA(),C128/'Condensed Financials'!C44)</f>
-        <v/>
-      </c>
-      <c r="D129" s="15">
-        <f>IF('Condensed Financials'!D44=0,NA(),D128/'Condensed Financials'!D44)</f>
-        <v/>
-      </c>
-      <c r="E129" s="15">
-        <f>IF('Condensed Financials'!E44=0,NA(),E128/'Condensed Financials'!E44)</f>
-        <v/>
-      </c>
-      <c r="F129" s="15">
-        <f>IF('Condensed Financials'!F44=0,NA(),F128/'Condensed Financials'!F44)</f>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B129" s="13">
+        <f>'Balance Sheet'!B38</f>
+        <v/>
+      </c>
+      <c r="C129" s="13">
+        <f>'Balance Sheet'!C38</f>
+        <v/>
+      </c>
+      <c r="D129" s="13">
+        <f>'Balance Sheet'!D38</f>
+        <v/>
+      </c>
+      <c r="E129" s="13">
+        <f>'Balance Sheet'!E38</f>
+        <v/>
+      </c>
+      <c r="F129" s="13">
+        <f>'Balance Sheet'!F38</f>
         <v/>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>Payments for Intangible Assets (reported)</t>
-        </is>
-      </c>
-      <c r="B130" s="13">
-        <f>'Cash Flow Statement'!B38</f>
-        <v/>
-      </c>
-      <c r="C130" s="13">
-        <f>'Cash Flow Statement'!C38</f>
-        <v/>
-      </c>
-      <c r="D130" s="13">
-        <f>'Cash Flow Statement'!D38</f>
-        <v/>
-      </c>
-      <c r="E130" s="13">
-        <f>'Cash Flow Statement'!E38</f>
-        <v/>
-      </c>
-      <c r="F130" s="13">
-        <f>'Cash Flow Statement'!F38</f>
+          <t>Change in Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C130" s="16">
+        <f>C129-B129</f>
+        <v/>
+      </c>
+      <c r="D130" s="16">
+        <f>D129-C129</f>
+        <v/>
+      </c>
+      <c r="E130" s="16">
+        <f>E129-D129</f>
+        <v/>
+      </c>
+      <c r="F130" s="16">
+        <f>F129-E129</f>
         <v/>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>Intangible Payments (−reported)</t>
-        </is>
-      </c>
-      <c r="B131" s="16">
-        <f>-B130</f>
-        <v/>
-      </c>
-      <c r="C131" s="16">
-        <f>-C130</f>
-        <v/>
-      </c>
-      <c r="D131" s="16">
-        <f>-D130</f>
-        <v/>
-      </c>
-      <c r="E131" s="16">
-        <f>-E130</f>
-        <v/>
-      </c>
-      <c r="F131" s="16">
-        <f>-F130</f>
+          <t>Intangible Assets Growth</t>
+        </is>
+      </c>
+      <c r="C131" s="15">
+        <f>IF(B129=0,NA(),C129/B129-1)</f>
+        <v/>
+      </c>
+      <c r="D131" s="15">
+        <f>IF(C129=0,NA(),D129/C129-1)</f>
+        <v/>
+      </c>
+      <c r="E131" s="15">
+        <f>IF(D129=0,NA(),E129/D129-1)</f>
+        <v/>
+      </c>
+      <c r="F131" s="15">
+        <f>IF(E129=0,NA(),F129/E129-1)</f>
         <v/>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
         <is>
+          <t>Average Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C132" s="16">
+        <f>(B129+C129)/2</f>
+        <v/>
+      </c>
+      <c r="D132" s="16">
+        <f>(C129+D129)/2</f>
+        <v/>
+      </c>
+      <c r="E132" s="16">
+        <f>(D129+E129)/2</f>
+        <v/>
+      </c>
+      <c r="F132" s="16">
+        <f>(E129+F129)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="11" t="inlineStr">
+        <is>
+          <t>Average Intangible Assets / Revenue</t>
+        </is>
+      </c>
+      <c r="C133" s="15">
+        <f>IF('Condensed Financials'!C44=0,NA(),C132/'Condensed Financials'!C44)</f>
+        <v/>
+      </c>
+      <c r="D133" s="15">
+        <f>IF('Condensed Financials'!D44=0,NA(),D132/'Condensed Financials'!D44)</f>
+        <v/>
+      </c>
+      <c r="E133" s="15">
+        <f>IF('Condensed Financials'!E44=0,NA(),E132/'Condensed Financials'!E44)</f>
+        <v/>
+      </c>
+      <c r="F133" s="15">
+        <f>IF('Condensed Financials'!F44=0,NA(),F132/'Condensed Financials'!F44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="11" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B134" s="13">
+        <f>B124+B129</f>
+        <v/>
+      </c>
+      <c r="C134" s="13">
+        <f>C124+C129</f>
+        <v/>
+      </c>
+      <c r="D134" s="13">
+        <f>D124+D129</f>
+        <v/>
+      </c>
+      <c r="E134" s="13">
+        <f>E124+E129</f>
+        <v/>
+      </c>
+      <c r="F134" s="13">
+        <f>F124+F129</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="11" t="inlineStr">
+        <is>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C135" s="16">
+        <f>C134-B134</f>
+        <v/>
+      </c>
+      <c r="D135" s="16">
+        <f>D134-C134</f>
+        <v/>
+      </c>
+      <c r="E135" s="16">
+        <f>E134-D134</f>
+        <v/>
+      </c>
+      <c r="F135" s="16">
+        <f>F134-E134</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C136" s="15">
+        <f>IF(B134=0,NA(),C134/B134-1)</f>
+        <v/>
+      </c>
+      <c r="D136" s="15">
+        <f>IF(C134=0,NA(),D134/C134-1)</f>
+        <v/>
+      </c>
+      <c r="E136" s="15">
+        <f>IF(D134=0,NA(),E134/D134-1)</f>
+        <v/>
+      </c>
+      <c r="F136" s="15">
+        <f>IF(E134=0,NA(),F134/E134-1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="11" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C137" s="16">
+        <f>(B134+C134)/2</f>
+        <v/>
+      </c>
+      <c r="D137" s="16">
+        <f>(C134+D134)/2</f>
+        <v/>
+      </c>
+      <c r="E137" s="16">
+        <f>(D134+E134)/2</f>
+        <v/>
+      </c>
+      <c r="F137" s="16">
+        <f>(E134+F134)/2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="11" t="inlineStr">
+        <is>
+          <t>Average Goodwill &amp; Intangibles / Revenue</t>
+        </is>
+      </c>
+      <c r="C138" s="15">
+        <f>IF('Condensed Financials'!C44=0,NA(),C137/'Condensed Financials'!C44)</f>
+        <v/>
+      </c>
+      <c r="D138" s="15">
+        <f>IF('Condensed Financials'!D44=0,NA(),D137/'Condensed Financials'!D44)</f>
+        <v/>
+      </c>
+      <c r="E138" s="15">
+        <f>IF('Condensed Financials'!E44=0,NA(),E137/'Condensed Financials'!E44)</f>
+        <v/>
+      </c>
+      <c r="F138" s="15">
+        <f>IF('Condensed Financials'!F44=0,NA(),F137/'Condensed Financials'!F44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="11" t="inlineStr">
+        <is>
+          <t>Payments for Intangible Assets (reported)</t>
+        </is>
+      </c>
+      <c r="B139" s="13">
+        <f>'Cash Flow Statement'!B38</f>
+        <v/>
+      </c>
+      <c r="C139" s="13">
+        <f>'Cash Flow Statement'!C38</f>
+        <v/>
+      </c>
+      <c r="D139" s="13">
+        <f>'Cash Flow Statement'!D38</f>
+        <v/>
+      </c>
+      <c r="E139" s="13">
+        <f>'Cash Flow Statement'!E38</f>
+        <v/>
+      </c>
+      <c r="F139" s="13">
+        <f>'Cash Flow Statement'!F38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="11" t="inlineStr">
+        <is>
+          <t>Intangible Payments (−reported)</t>
+        </is>
+      </c>
+      <c r="B140" s="16">
+        <f>-B139</f>
+        <v/>
+      </c>
+      <c r="C140" s="16">
+        <f>-C139</f>
+        <v/>
+      </c>
+      <c r="D140" s="16">
+        <f>-D139</f>
+        <v/>
+      </c>
+      <c r="E140" s="16">
+        <f>-E139</f>
+        <v/>
+      </c>
+      <c r="F140" s="16">
+        <f>-F139</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="11" t="inlineStr">
+        <is>
           <t>Intangible Payments / Revenue</t>
         </is>
       </c>
-      <c r="B132" s="15">
-        <f>IF('Condensed Financials'!B44=0,NA(),B131/'Condensed Financials'!B44)</f>
-        <v/>
-      </c>
-      <c r="C132" s="15">
-        <f>IF('Condensed Financials'!C44=0,NA(),C131/'Condensed Financials'!C44)</f>
-        <v/>
-      </c>
-      <c r="D132" s="15">
-        <f>IF('Condensed Financials'!D44=0,NA(),D131/'Condensed Financials'!D44)</f>
-        <v/>
-      </c>
-      <c r="E132" s="15">
-        <f>IF('Condensed Financials'!E44=0,NA(),E131/'Condensed Financials'!E44)</f>
-        <v/>
-      </c>
-      <c r="F132" s="15">
-        <f>IF('Condensed Financials'!F44=0,NA(),F131/'Condensed Financials'!F44)</f>
+      <c r="B141" s="15">
+        <f>IF('Condensed Financials'!B44=0,NA(),B140/'Condensed Financials'!B44)</f>
+        <v/>
+      </c>
+      <c r="C141" s="15">
+        <f>IF('Condensed Financials'!C44=0,NA(),C140/'Condensed Financials'!C44)</f>
+        <v/>
+      </c>
+      <c r="D141" s="15">
+        <f>IF('Condensed Financials'!D44=0,NA(),D140/'Condensed Financials'!D44)</f>
+        <v/>
+      </c>
+      <c r="E141" s="15">
+        <f>IF('Condensed Financials'!E44=0,NA(),E140/'Condensed Financials'!E44)</f>
+        <v/>
+      </c>
+      <c r="F141" s="15">
+        <f>IF('Condensed Financials'!F44=0,NA(),F140/'Condensed Financials'!F44)</f>
         <v/>
       </c>
     </row>

--- a/release/fast_retailing/FastRetailing_Answer_Key.xlsx
+++ b/release/fast_retailing/FastRetailing_Answer_Key.xlsx
@@ -2003,292 +2003,332 @@
         <t>Reconstructed inventory change = revenue-scale effect + intensity effect. Arithmetic decomposition that reconciles to the inventory change when defined. Not inventory days/turnover and not proof of cash movement, deterioration, seasonality, markdowns, or management causes.</t>
       </text>
     </comment>
-    <comment ref="C125" authorId="0" shapeId="0">
+    <comment ref="C123" authorId="0" shapeId="0">
+      <text>
+        <t>Balance-implied inventory CF adjustment = −(current inventory − prior inventory), the negative of the inventory balance movement. This is not the reported operating cash-flow reconciliation adjustment. Opening-period comparison is not practiced.</t>
+      </text>
+    </comment>
+    <comment ref="D123" authorId="0" shapeId="0">
+      <text>
+        <t>Balance-implied inventory CF adjustment = −(current inventory − prior inventory), the negative of the inventory balance movement. This is not the reported operating cash-flow reconciliation adjustment. Opening-period comparison is not practiced.</t>
+      </text>
+    </comment>
+    <comment ref="E123" authorId="0" shapeId="0">
+      <text>
+        <t>Balance-implied inventory CF adjustment = −(current inventory − prior inventory), the negative of the inventory balance movement. This is not the reported operating cash-flow reconciliation adjustment. Opening-period comparison is not practiced.</t>
+      </text>
+    </comment>
+    <comment ref="F123" authorId="0" shapeId="0">
+      <text>
+        <t>Balance-implied inventory CF adjustment = −(current inventory − prior inventory), the negative of the inventory balance movement. This is not the reported operating cash-flow reconciliation adjustment. Opening-period comparison is not practiced.</t>
+      </text>
+    </comment>
+    <comment ref="C124" authorId="0" shapeId="0">
+      <text>
+        <t>Unexplained inventory CF difference = reported operating CF inventory adjustment − balance-implied adjustment. A nonzero difference needs further evidence; it does not establish an error, cash paid for inventory, FX, acquisitions, write-downs, or another specific cause. Do not insert a balancing plug.</t>
+      </text>
+    </comment>
+    <comment ref="D124" authorId="0" shapeId="0">
+      <text>
+        <t>Unexplained inventory CF difference = reported operating CF inventory adjustment − balance-implied adjustment. A nonzero difference needs further evidence; it does not establish an error, cash paid for inventory, FX, acquisitions, write-downs, or another specific cause. Do not insert a balancing plug.</t>
+      </text>
+    </comment>
+    <comment ref="E124" authorId="0" shapeId="0">
+      <text>
+        <t>Unexplained inventory CF difference = reported operating CF inventory adjustment − balance-implied adjustment. A nonzero difference needs further evidence; it does not establish an error, cash paid for inventory, FX, acquisitions, write-downs, or another specific cause. Do not insert a balancing plug.</t>
+      </text>
+    </comment>
+    <comment ref="F124" authorId="0" shapeId="0">
+      <text>
+        <t>Unexplained inventory CF difference = reported operating CF inventory adjustment − balance-implied adjustment. A nonzero difference needs further evidence; it does not establish an error, cash paid for inventory, FX, acquisitions, write-downs, or another specific cause. Do not insert a balancing plug.</t>
+      </text>
+    </comment>
+    <comment ref="C128" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="D125" authorId="0" shapeId="0">
+    <comment ref="D128" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="E125" authorId="0" shapeId="0">
+    <comment ref="E128" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="F125" authorId="0" shapeId="0">
+    <comment ref="F128" authorId="0" shapeId="0">
       <text>
         <t>Current goodwill − prior goodwill. Flat goodwill does not establish absence of impairment disclosed elsewhere.</t>
       </text>
     </comment>
-    <comment ref="C126" authorId="0" shapeId="0">
+    <comment ref="C129" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="D126" authorId="0" shapeId="0">
+    <comment ref="D129" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="E126" authorId="0" shapeId="0">
+    <comment ref="E129" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="F126" authorId="0" shapeId="0">
+    <comment ref="F129" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported goodwill.</t>
       </text>
     </comment>
-    <comment ref="C127" authorId="0" shapeId="0">
+    <comment ref="C130" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="D127" authorId="0" shapeId="0">
+    <comment ref="D130" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="E127" authorId="0" shapeId="0">
+    <comment ref="E130" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="F127" authorId="0" shapeId="0">
+    <comment ref="F130" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending goodwill.</t>
       </text>
     </comment>
-    <comment ref="C128" authorId="0" shapeId="0">
+    <comment ref="C131" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D128" authorId="0" shapeId="0">
+    <comment ref="D131" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E128" authorId="0" shapeId="0">
+    <comment ref="E131" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="F128" authorId="0" shapeId="0">
+    <comment ref="F131" authorId="0" shapeId="0">
       <text>
         <t>Average goodwill divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C130" authorId="0" shapeId="0">
+    <comment ref="C133" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D130" authorId="0" shapeId="0">
+    <comment ref="D133" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E130" authorId="0" shapeId="0">
+    <comment ref="E133" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="F130" authorId="0" shapeId="0">
+    <comment ref="F133" authorId="0" shapeId="0">
       <text>
         <t>Current intangible assets − prior intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C131" authorId="0" shapeId="0">
+    <comment ref="C134" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D131" authorId="0" shapeId="0">
+    <comment ref="D134" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E131" authorId="0" shapeId="0">
+    <comment ref="E134" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="F131" authorId="0" shapeId="0">
+    <comment ref="F134" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in reported intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C132" authorId="0" shapeId="0">
+    <comment ref="C135" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="D132" authorId="0" shapeId="0">
+    <comment ref="D135" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="E132" authorId="0" shapeId="0">
+    <comment ref="E135" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="F132" authorId="0" shapeId="0">
+    <comment ref="F135" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending intangible assets.</t>
       </text>
     </comment>
-    <comment ref="C133" authorId="0" shapeId="0">
+    <comment ref="C136" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="D133" authorId="0" shapeId="0">
+    <comment ref="D136" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="E133" authorId="0" shapeId="0">
+    <comment ref="E136" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="F133" authorId="0" shapeId="0">
+    <comment ref="F136" authorId="0" shapeId="0">
       <text>
         <t>Average intangible assets divided by Revenue (average-balance intensity).</t>
       </text>
     </comment>
-    <comment ref="C135" authorId="0" shapeId="0">
+    <comment ref="C138" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="D135" authorId="0" shapeId="0">
+    <comment ref="D138" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="E135" authorId="0" shapeId="0">
+    <comment ref="E138" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="F135" authorId="0" shapeId="0">
+    <comment ref="F138" authorId="0" shapeId="0">
       <text>
         <t>Current combined total − prior combined total.</t>
       </text>
     </comment>
-    <comment ref="C136" authorId="0" shapeId="0">
+    <comment ref="C139" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="D136" authorId="0" shapeId="0">
+    <comment ref="D139" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="E136" authorId="0" shapeId="0">
+    <comment ref="E139" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="F136" authorId="0" shapeId="0">
+    <comment ref="F139" authorId="0" shapeId="0">
       <text>
         <t>Percentage change in the combined goodwill and intangibles total.</t>
       </text>
     </comment>
-    <comment ref="C137" authorId="0" shapeId="0">
+    <comment ref="C140" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="D137" authorId="0" shapeId="0">
+    <comment ref="D140" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="E137" authorId="0" shapeId="0">
+    <comment ref="E140" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="F137" authorId="0" shapeId="0">
+    <comment ref="F140" authorId="0" shapeId="0">
       <text>
         <t>Average beginning and ending combined goodwill and intangibles.</t>
       </text>
     </comment>
-    <comment ref="C138" authorId="0" shapeId="0">
+    <comment ref="C141" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="D138" authorId="0" shapeId="0">
+    <comment ref="D141" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="E138" authorId="0" shapeId="0">
+    <comment ref="E141" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="F138" authorId="0" shapeId="0">
+    <comment ref="F141" authorId="0" shapeId="0">
       <text>
         <t>Average combined goodwill and intangibles divided by Revenue.</t>
       </text>
     </comment>
-    <comment ref="B140" authorId="0" shapeId="0">
+    <comment ref="B143" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="C140" authorId="0" shapeId="0">
+    <comment ref="C143" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="D140" authorId="0" shapeId="0">
+    <comment ref="D143" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="E140" authorId="0" shapeId="0">
+    <comment ref="E143" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="F140" authorId="0" shapeId="0">
+    <comment ref="F143" authorId="0" shapeId="0">
       <text>
         <t>Presented as −reported payments for intangible assets. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="B141" authorId="0" shapeId="0">
+    <comment ref="B144" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="C141" authorId="0" shapeId="0">
+    <comment ref="C144" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="D141" authorId="0" shapeId="0">
+    <comment ref="D144" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="E141" authorId="0" shapeId="0">
+    <comment ref="E144" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
     </comment>
-    <comment ref="F141" authorId="0" shapeId="0">
+    <comment ref="F144" authorId="0" shapeId="0">
       <text>
         <t>Presented intangible payments divided by Revenue. Intangible payments are not business acquisitions.</t>
       </text>
@@ -3391,7 +3431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F136"/>
+  <dimension ref="A1:F138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6140,7 +6180,7 @@
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>C125:F125</t>
+          <t>C128:F128</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr">
@@ -6170,7 +6210,7 @@
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>C126:F126</t>
+          <t>C129:F129</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr">
@@ -6200,7 +6240,7 @@
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>C127:F127</t>
+          <t>C130:F130</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr">
@@ -6230,7 +6270,7 @@
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>C128:F128</t>
+          <t>C131:F131</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr">
@@ -6260,7 +6300,7 @@
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>C130:F130</t>
+          <t>C133:F133</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr">
@@ -6290,7 +6330,7 @@
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>C131:F131</t>
+          <t>C134:F134</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr">
@@ -6320,7 +6360,7 @@
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>C132:F132</t>
+          <t>C135:F135</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr">
@@ -6350,7 +6390,7 @@
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>C133:F133</t>
+          <t>C136:F136</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr">
@@ -6380,7 +6420,7 @@
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>C135:F135</t>
+          <t>C138:F138</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr">
@@ -6410,7 +6450,7 @@
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>C136:F136</t>
+          <t>C139:F139</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr">
@@ -6440,7 +6480,7 @@
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>C137:F137</t>
+          <t>C140:F140</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr">
@@ -6470,7 +6510,7 @@
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>C138:F138</t>
+          <t>C141:F141</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr">
@@ -6500,7 +6540,7 @@
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>B140:F140</t>
+          <t>B143:F143</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr">
@@ -6530,7 +6570,7 @@
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>B141:F141</t>
+          <t>B144:F144</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr">
@@ -7406,6 +7446,66 @@
       <c r="F136" s="11" t="inlineStr">
         <is>
           <t>inventory_revenue_scale_effect, inventory_intensity_effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="11" t="n">
+        <v>150</v>
+      </c>
+      <c r="B137" s="11" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment</t>
+        </is>
+      </c>
+      <c r="C137" s="11" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D137" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E137" s="11" t="inlineStr">
+        <is>
+          <t>C123:F123</t>
+        </is>
+      </c>
+      <c r="F137" s="11" t="inlineStr">
+        <is>
+          <t>inventory_change</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="11" t="n">
+        <v>151</v>
+      </c>
+      <c r="B138" s="11" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference</t>
+        </is>
+      </c>
+      <c r="C138" s="11" t="inlineStr">
+        <is>
+          <t>2022–2025 (4 cells)</t>
+        </is>
+      </c>
+      <c r="D138" s="11" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="E138" s="11" t="inlineStr">
+        <is>
+          <t>C124:F124</t>
+        </is>
+      </c>
+      <c r="F138" s="11" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment</t>
         </is>
       </c>
     </row>
@@ -8423,7 +8523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S570"/>
+  <dimension ref="A1:S578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38734,11 +38834,11 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>C125</t>
+          <t>C128</t>
         </is>
       </c>
       <c r="I382">
-        <f>C124-B124</f>
+        <f>C127-B127</f>
         <v/>
       </c>
       <c r="J382" t="n">
@@ -38810,11 +38910,11 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>D125</t>
+          <t>D128</t>
         </is>
       </c>
       <c r="I383">
-        <f>D124-C124</f>
+        <f>D127-C127</f>
         <v/>
       </c>
       <c r="J383" t="n">
@@ -38886,11 +38986,11 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>E125</t>
+          <t>E128</t>
         </is>
       </c>
       <c r="I384">
-        <f>E124-D124</f>
+        <f>E127-D127</f>
         <v/>
       </c>
       <c r="J384" t="n">
@@ -38962,11 +39062,11 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>F125</t>
+          <t>F128</t>
         </is>
       </c>
       <c r="I385">
-        <f>F124-E124</f>
+        <f>F127-E127</f>
         <v/>
       </c>
       <c r="J385" t="n">
@@ -39038,11 +39138,11 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>C126</t>
+          <t>C129</t>
         </is>
       </c>
       <c r="I386">
-        <f>IF(B124=0,NA(),C124/B124-1)</f>
+        <f>IF(B127=0,NA(),C127/B127-1)</f>
         <v/>
       </c>
       <c r="J386" t="n">
@@ -39119,11 +39219,11 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>D126</t>
+          <t>D129</t>
         </is>
       </c>
       <c r="I387">
-        <f>IF(C124=0,NA(),D124/C124-1)</f>
+        <f>IF(C127=0,NA(),D127/C127-1)</f>
         <v/>
       </c>
       <c r="J387" t="n">
@@ -39200,11 +39300,11 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>E126</t>
+          <t>E129</t>
         </is>
       </c>
       <c r="I388">
-        <f>IF(D124=0,NA(),E124/D124-1)</f>
+        <f>IF(D127=0,NA(),E127/D127-1)</f>
         <v/>
       </c>
       <c r="J388" t="n">
@@ -39281,11 +39381,11 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>F126</t>
+          <t>F129</t>
         </is>
       </c>
       <c r="I389">
-        <f>IF(E124=0,NA(),F124/E124-1)</f>
+        <f>IF(E127=0,NA(),F127/E127-1)</f>
         <v/>
       </c>
       <c r="J389" t="n">
@@ -39362,11 +39462,11 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>C127</t>
+          <t>C130</t>
         </is>
       </c>
       <c r="I390">
-        <f>(B124+C124)/2</f>
+        <f>(B127+C127)/2</f>
         <v/>
       </c>
       <c r="J390" t="n">
@@ -39438,11 +39538,11 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>D127</t>
+          <t>D130</t>
         </is>
       </c>
       <c r="I391">
-        <f>(C124+D124)/2</f>
+        <f>(C127+D127)/2</f>
         <v/>
       </c>
       <c r="J391" t="n">
@@ -39514,11 +39614,11 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>E127</t>
+          <t>E130</t>
         </is>
       </c>
       <c r="I392">
-        <f>(D124+E124)/2</f>
+        <f>(D127+E127)/2</f>
         <v/>
       </c>
       <c r="J392" t="n">
@@ -39590,11 +39690,11 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t>F127</t>
+          <t>F130</t>
         </is>
       </c>
       <c r="I393">
-        <f>(E124+F124)/2</f>
+        <f>(E127+F127)/2</f>
         <v/>
       </c>
       <c r="J393" t="n">
@@ -39666,11 +39766,11 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>C128</t>
+          <t>C131</t>
         </is>
       </c>
       <c r="I394">
-        <f>IF('Condensed Financials'!C44=0,NA(),C127/'Condensed Financials'!C44)</f>
+        <f>IF('Condensed Financials'!C44=0,NA(),C130/'Condensed Financials'!C44)</f>
         <v/>
       </c>
       <c r="J394" t="n">
@@ -39747,11 +39847,11 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t>D128</t>
+          <t>D131</t>
         </is>
       </c>
       <c r="I395">
-        <f>IF('Condensed Financials'!D44=0,NA(),D127/'Condensed Financials'!D44)</f>
+        <f>IF('Condensed Financials'!D44=0,NA(),D130/'Condensed Financials'!D44)</f>
         <v/>
       </c>
       <c r="J395" t="n">
@@ -39828,11 +39928,11 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>E128</t>
+          <t>E131</t>
         </is>
       </c>
       <c r="I396">
-        <f>IF('Condensed Financials'!E44=0,NA(),E127/'Condensed Financials'!E44)</f>
+        <f>IF('Condensed Financials'!E44=0,NA(),E130/'Condensed Financials'!E44)</f>
         <v/>
       </c>
       <c r="J396" t="n">
@@ -39909,11 +40009,11 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>F128</t>
+          <t>F131</t>
         </is>
       </c>
       <c r="I397">
-        <f>IF('Condensed Financials'!F44=0,NA(),F127/'Condensed Financials'!F44)</f>
+        <f>IF('Condensed Financials'!F44=0,NA(),F130/'Condensed Financials'!F44)</f>
         <v/>
       </c>
       <c r="J397" t="n">
@@ -39990,11 +40090,11 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>C130</t>
+          <t>C133</t>
         </is>
       </c>
       <c r="I398">
-        <f>C129-B129</f>
+        <f>C132-B132</f>
         <v/>
       </c>
       <c r="J398" t="n">
@@ -40066,11 +40166,11 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t>D130</t>
+          <t>D133</t>
         </is>
       </c>
       <c r="I399">
-        <f>D129-C129</f>
+        <f>D132-C132</f>
         <v/>
       </c>
       <c r="J399" t="n">
@@ -40142,11 +40242,11 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t>E130</t>
+          <t>E133</t>
         </is>
       </c>
       <c r="I400">
-        <f>E129-D129</f>
+        <f>E132-D132</f>
         <v/>
       </c>
       <c r="J400" t="n">
@@ -40218,11 +40318,11 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t>F130</t>
+          <t>F133</t>
         </is>
       </c>
       <c r="I401">
-        <f>F129-E129</f>
+        <f>F132-E132</f>
         <v/>
       </c>
       <c r="J401" t="n">
@@ -40294,11 +40394,11 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t>C131</t>
+          <t>C134</t>
         </is>
       </c>
       <c r="I402">
-        <f>IF(B129=0,NA(),C129/B129-1)</f>
+        <f>IF(B132=0,NA(),C132/B132-1)</f>
         <v/>
       </c>
       <c r="J402" t="n">
@@ -40375,11 +40475,11 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>D131</t>
+          <t>D134</t>
         </is>
       </c>
       <c r="I403">
-        <f>IF(C129=0,NA(),D129/C129-1)</f>
+        <f>IF(C132=0,NA(),D132/C132-1)</f>
         <v/>
       </c>
       <c r="J403" t="n">
@@ -40456,11 +40556,11 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>E131</t>
+          <t>E134</t>
         </is>
       </c>
       <c r="I404">
-        <f>IF(D129=0,NA(),E129/D129-1)</f>
+        <f>IF(D132=0,NA(),E132/D132-1)</f>
         <v/>
       </c>
       <c r="J404" t="n">
@@ -40537,11 +40637,11 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>F131</t>
+          <t>F134</t>
         </is>
       </c>
       <c r="I405">
-        <f>IF(E129=0,NA(),F129/E129-1)</f>
+        <f>IF(E132=0,NA(),F132/E132-1)</f>
         <v/>
       </c>
       <c r="J405" t="n">
@@ -40618,11 +40718,11 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>C132</t>
+          <t>C135</t>
         </is>
       </c>
       <c r="I406">
-        <f>(B129+C129)/2</f>
+        <f>(B132+C132)/2</f>
         <v/>
       </c>
       <c r="J406" t="n">
@@ -40694,11 +40794,11 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t>D132</t>
+          <t>D135</t>
         </is>
       </c>
       <c r="I407">
-        <f>(C129+D129)/2</f>
+        <f>(C132+D132)/2</f>
         <v/>
       </c>
       <c r="J407" t="n">
@@ -40770,11 +40870,11 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>E132</t>
+          <t>E135</t>
         </is>
       </c>
       <c r="I408">
-        <f>(D129+E129)/2</f>
+        <f>(D132+E132)/2</f>
         <v/>
       </c>
       <c r="J408" t="n">
@@ -40846,11 +40946,11 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>F132</t>
+          <t>F135</t>
         </is>
       </c>
       <c r="I409">
-        <f>(E129+F129)/2</f>
+        <f>(E132+F132)/2</f>
         <v/>
       </c>
       <c r="J409" t="n">
@@ -40922,11 +41022,11 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t>C133</t>
+          <t>C136</t>
         </is>
       </c>
       <c r="I410">
-        <f>IF('Condensed Financials'!C44=0,NA(),C132/'Condensed Financials'!C44)</f>
+        <f>IF('Condensed Financials'!C44=0,NA(),C135/'Condensed Financials'!C44)</f>
         <v/>
       </c>
       <c r="J410" t="n">
@@ -41003,11 +41103,11 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>D133</t>
+          <t>D136</t>
         </is>
       </c>
       <c r="I411">
-        <f>IF('Condensed Financials'!D44=0,NA(),D132/'Condensed Financials'!D44)</f>
+        <f>IF('Condensed Financials'!D44=0,NA(),D135/'Condensed Financials'!D44)</f>
         <v/>
       </c>
       <c r="J411" t="n">
@@ -41084,11 +41184,11 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t>E133</t>
+          <t>E136</t>
         </is>
       </c>
       <c r="I412">
-        <f>IF('Condensed Financials'!E44=0,NA(),E132/'Condensed Financials'!E44)</f>
+        <f>IF('Condensed Financials'!E44=0,NA(),E135/'Condensed Financials'!E44)</f>
         <v/>
       </c>
       <c r="J412" t="n">
@@ -41165,11 +41265,11 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>F133</t>
+          <t>F136</t>
         </is>
       </c>
       <c r="I413">
-        <f>IF('Condensed Financials'!F44=0,NA(),F132/'Condensed Financials'!F44)</f>
+        <f>IF('Condensed Financials'!F44=0,NA(),F135/'Condensed Financials'!F44)</f>
         <v/>
       </c>
       <c r="J413" t="n">
@@ -41246,11 +41346,11 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>C135</t>
+          <t>C138</t>
         </is>
       </c>
       <c r="I414">
-        <f>C134-B134</f>
+        <f>C137-B137</f>
         <v/>
       </c>
       <c r="J414" t="n">
@@ -41322,11 +41422,11 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>D135</t>
+          <t>D138</t>
         </is>
       </c>
       <c r="I415">
-        <f>D134-C134</f>
+        <f>D137-C137</f>
         <v/>
       </c>
       <c r="J415" t="n">
@@ -41398,11 +41498,11 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>E135</t>
+          <t>E138</t>
         </is>
       </c>
       <c r="I416">
-        <f>E134-D134</f>
+        <f>E137-D137</f>
         <v/>
       </c>
       <c r="J416" t="n">
@@ -41474,11 +41574,11 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>F135</t>
+          <t>F138</t>
         </is>
       </c>
       <c r="I417">
-        <f>F134-E134</f>
+        <f>F137-E137</f>
         <v/>
       </c>
       <c r="J417" t="n">
@@ -41550,11 +41650,11 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>C136</t>
+          <t>C139</t>
         </is>
       </c>
       <c r="I418">
-        <f>IF(B134=0,NA(),C134/B134-1)</f>
+        <f>IF(B137=0,NA(),C137/B137-1)</f>
         <v/>
       </c>
       <c r="J418" t="n">
@@ -41631,11 +41731,11 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>D136</t>
+          <t>D139</t>
         </is>
       </c>
       <c r="I419">
-        <f>IF(C134=0,NA(),D134/C134-1)</f>
+        <f>IF(C137=0,NA(),D137/C137-1)</f>
         <v/>
       </c>
       <c r="J419" t="n">
@@ -41712,11 +41812,11 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>E136</t>
+          <t>E139</t>
         </is>
       </c>
       <c r="I420">
-        <f>IF(D134=0,NA(),E134/D134-1)</f>
+        <f>IF(D137=0,NA(),E137/D137-1)</f>
         <v/>
       </c>
       <c r="J420" t="n">
@@ -41793,11 +41893,11 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>F136</t>
+          <t>F139</t>
         </is>
       </c>
       <c r="I421">
-        <f>IF(E134=0,NA(),F134/E134-1)</f>
+        <f>IF(E137=0,NA(),F137/E137-1)</f>
         <v/>
       </c>
       <c r="J421" t="n">
@@ -41874,11 +41974,11 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>C137</t>
+          <t>C140</t>
         </is>
       </c>
       <c r="I422">
-        <f>(B134+C134)/2</f>
+        <f>(B137+C137)/2</f>
         <v/>
       </c>
       <c r="J422" t="n">
@@ -41950,11 +42050,11 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>D137</t>
+          <t>D140</t>
         </is>
       </c>
       <c r="I423">
-        <f>(C134+D134)/2</f>
+        <f>(C137+D137)/2</f>
         <v/>
       </c>
       <c r="J423" t="n">
@@ -42026,11 +42126,11 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>E137</t>
+          <t>E140</t>
         </is>
       </c>
       <c r="I424">
-        <f>(D134+E134)/2</f>
+        <f>(D137+E137)/2</f>
         <v/>
       </c>
       <c r="J424" t="n">
@@ -42102,11 +42202,11 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>F137</t>
+          <t>F140</t>
         </is>
       </c>
       <c r="I425">
-        <f>(E134+F134)/2</f>
+        <f>(E137+F137)/2</f>
         <v/>
       </c>
       <c r="J425" t="n">
@@ -42178,11 +42278,11 @@
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>C138</t>
+          <t>C141</t>
         </is>
       </c>
       <c r="I426">
-        <f>IF('Condensed Financials'!C44=0,NA(),C137/'Condensed Financials'!C44)</f>
+        <f>IF('Condensed Financials'!C44=0,NA(),C140/'Condensed Financials'!C44)</f>
         <v/>
       </c>
       <c r="J426" t="n">
@@ -42259,11 +42359,11 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>D138</t>
+          <t>D141</t>
         </is>
       </c>
       <c r="I427">
-        <f>IF('Condensed Financials'!D44=0,NA(),D137/'Condensed Financials'!D44)</f>
+        <f>IF('Condensed Financials'!D44=0,NA(),D140/'Condensed Financials'!D44)</f>
         <v/>
       </c>
       <c r="J427" t="n">
@@ -42340,11 +42440,11 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>E138</t>
+          <t>E141</t>
         </is>
       </c>
       <c r="I428">
-        <f>IF('Condensed Financials'!E44=0,NA(),E137/'Condensed Financials'!E44)</f>
+        <f>IF('Condensed Financials'!E44=0,NA(),E140/'Condensed Financials'!E44)</f>
         <v/>
       </c>
       <c r="J428" t="n">
@@ -42421,11 +42521,11 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>F138</t>
+          <t>F141</t>
         </is>
       </c>
       <c r="I429">
-        <f>IF('Condensed Financials'!F44=0,NA(),F137/'Condensed Financials'!F44)</f>
+        <f>IF('Condensed Financials'!F44=0,NA(),F140/'Condensed Financials'!F44)</f>
         <v/>
       </c>
       <c r="J429" t="n">
@@ -42502,11 +42602,11 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>B140</t>
+          <t>B143</t>
         </is>
       </c>
       <c r="I430">
-        <f>-B139</f>
+        <f>-B142</f>
         <v/>
       </c>
       <c r="J430" t="n">
@@ -42578,11 +42678,11 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>C140</t>
+          <t>C143</t>
         </is>
       </c>
       <c r="I431">
-        <f>-C139</f>
+        <f>-C142</f>
         <v/>
       </c>
       <c r="J431" t="n">
@@ -42654,11 +42754,11 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>D140</t>
+          <t>D143</t>
         </is>
       </c>
       <c r="I432">
-        <f>-D139</f>
+        <f>-D142</f>
         <v/>
       </c>
       <c r="J432" t="n">
@@ -42730,11 +42830,11 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>E140</t>
+          <t>E143</t>
         </is>
       </c>
       <c r="I433">
-        <f>-E139</f>
+        <f>-E142</f>
         <v/>
       </c>
       <c r="J433" t="n">
@@ -42806,11 +42906,11 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>F140</t>
+          <t>F143</t>
         </is>
       </c>
       <c r="I434">
-        <f>-F139</f>
+        <f>-F142</f>
         <v/>
       </c>
       <c r="J434" t="n">
@@ -42882,11 +42982,11 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>B141</t>
+          <t>B144</t>
         </is>
       </c>
       <c r="I435">
-        <f>IF('Condensed Financials'!B44=0,NA(),B140/'Condensed Financials'!B44)</f>
+        <f>IF('Condensed Financials'!B44=0,NA(),B143/'Condensed Financials'!B44)</f>
         <v/>
       </c>
       <c r="J435" t="n">
@@ -42963,11 +43063,11 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>C141</t>
+          <t>C144</t>
         </is>
       </c>
       <c r="I436">
-        <f>IF('Condensed Financials'!C44=0,NA(),C140/'Condensed Financials'!C44)</f>
+        <f>IF('Condensed Financials'!C44=0,NA(),C143/'Condensed Financials'!C44)</f>
         <v/>
       </c>
       <c r="J436" t="n">
@@ -43044,11 +43144,11 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>D141</t>
+          <t>D144</t>
         </is>
       </c>
       <c r="I437">
-        <f>IF('Condensed Financials'!D44=0,NA(),D140/'Condensed Financials'!D44)</f>
+        <f>IF('Condensed Financials'!D44=0,NA(),D143/'Condensed Financials'!D44)</f>
         <v/>
       </c>
       <c r="J437" t="n">
@@ -43125,11 +43225,11 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>E141</t>
+          <t>E144</t>
         </is>
       </c>
       <c r="I438">
-        <f>IF('Condensed Financials'!E44=0,NA(),E140/'Condensed Financials'!E44)</f>
+        <f>IF('Condensed Financials'!E44=0,NA(),E143/'Condensed Financials'!E44)</f>
         <v/>
       </c>
       <c r="J438" t="n">
@@ -43206,11 +43306,11 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>F141</t>
+          <t>F144</t>
         </is>
       </c>
       <c r="I439">
-        <f>IF('Condensed Financials'!F44=0,NA(),F140/'Condensed Financials'!F44)</f>
+        <f>IF('Condensed Financials'!F44=0,NA(),F143/'Condensed Financials'!F44)</f>
         <v/>
       </c>
       <c r="J439" t="n">
@@ -53557,6 +53657,654 @@
         <v>4</v>
       </c>
       <c r="S570" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment__20220831</t>
+        </is>
+      </c>
+      <c r="B571" t="n">
+        <v>570</v>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment = −(current inventory − prior inventory), the negative of the inventory balance movement. This is not the reported operating cash-flow reconciliation adjustment. Opening-period comparison is not practiced.</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_balance_implied_cf_adjustment.2022-08-31</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>C123</t>
+        </is>
+      </c>
+      <c r="I571">
+        <f>-C118</f>
+        <v/>
+      </c>
+      <c r="J571" t="n">
+        <v>-91060</v>
+      </c>
+      <c r="K571" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>inventory_change__20220831</t>
+        </is>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment = −(current inventory − prior inventory).|This is the negative of the inventory balance movement, not the reported operating cash-flow reconciliation adjustment.|Do not treat this as cash paid for inventory.</t>
+        </is>
+      </c>
+      <c r="O571" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P571" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment</t>
+        </is>
+      </c>
+      <c r="Q571" t="n">
+        <v>150</v>
+      </c>
+      <c r="R571" t="n">
+        <v>1</v>
+      </c>
+      <c r="S571" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment__20230831</t>
+        </is>
+      </c>
+      <c r="B572" t="n">
+        <v>571</v>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment = −(current inventory − prior inventory), the negative of the inventory balance movement. This is not the reported operating cash-flow reconciliation adjustment. Opening-period comparison is not practiced.</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_balance_implied_cf_adjustment.2023-08-31</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I572">
+        <f>-D118</f>
+        <v/>
+      </c>
+      <c r="J572" t="n">
+        <v>36674</v>
+      </c>
+      <c r="K572" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>inventory_change__20230831</t>
+        </is>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment = −(current inventory − prior inventory).|This is the negative of the inventory balance movement, not the reported operating cash-flow reconciliation adjustment.|Do not treat this as cash paid for inventory.</t>
+        </is>
+      </c>
+      <c r="O572" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P572" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment</t>
+        </is>
+      </c>
+      <c r="Q572" t="n">
+        <v>150</v>
+      </c>
+      <c r="R572" t="n">
+        <v>2</v>
+      </c>
+      <c r="S572" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment__20240831</t>
+        </is>
+      </c>
+      <c r="B573" t="n">
+        <v>572</v>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment = −(current inventory − prior inventory), the negative of the inventory balance movement. This is not the reported operating cash-flow reconciliation adjustment. Opening-period comparison is not practiced.</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_balance_implied_cf_adjustment.2024-08-31</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>E123</t>
+        </is>
+      </c>
+      <c r="I573">
+        <f>-E118</f>
+        <v/>
+      </c>
+      <c r="J573" t="n">
+        <v>-25206</v>
+      </c>
+      <c r="K573" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>inventory_change__20240831</t>
+        </is>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment = −(current inventory − prior inventory).|This is the negative of the inventory balance movement, not the reported operating cash-flow reconciliation adjustment.|Do not treat this as cash paid for inventory.</t>
+        </is>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment</t>
+        </is>
+      </c>
+      <c r="Q573" t="n">
+        <v>150</v>
+      </c>
+      <c r="R573" t="n">
+        <v>3</v>
+      </c>
+      <c r="S573" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment__20250831</t>
+        </is>
+      </c>
+      <c r="B574" t="n">
+        <v>573</v>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment = −(current inventory − prior inventory), the negative of the inventory balance movement. This is not the reported operating cash-flow reconciliation adjustment. Opening-period comparison is not practiced.</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_balance_implied_cf_adjustment.2025-08-31</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>F123</t>
+        </is>
+      </c>
+      <c r="I574">
+        <f>-F118</f>
+        <v/>
+      </c>
+      <c r="J574" t="n">
+        <v>-36498</v>
+      </c>
+      <c r="K574" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>inventory_change__20250831</t>
+        </is>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>Balance-implied inventory CF adjustment = −(current inventory − prior inventory).|This is the negative of the inventory balance movement, not the reported operating cash-flow reconciliation adjustment.|Do not treat this as cash paid for inventory.</t>
+        </is>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment</t>
+        </is>
+      </c>
+      <c r="Q574" t="n">
+        <v>150</v>
+      </c>
+      <c r="R574" t="n">
+        <v>4</v>
+      </c>
+      <c r="S574" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>inventory_cf_adjustment_difference__20220831</t>
+        </is>
+      </c>
+      <c r="B575" t="n">
+        <v>574</v>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference = reported operating CF inventory adjustment − balance-implied adjustment. A nonzero difference needs further evidence; it does not establish an error, cash paid for inventory, FX, acquisitions, write-downs, or another specific cause. Do not insert a balancing plug.</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_cf_adjustment_difference.2022-08-31</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>C124</t>
+        </is>
+      </c>
+      <c r="I575">
+        <f>C122-C123</f>
+        <v/>
+      </c>
+      <c r="J575" t="n">
+        <v>40164</v>
+      </c>
+      <c r="K575" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L575" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment__20220831</t>
+        </is>
+      </c>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference = reported operating CF inventory adjustment − balance-implied adjustment.|A nonzero difference needs further evidence; it does not establish an error, cash paid for inventory, FX, acquisitions, write-downs, or another specific cause.|Do not insert a balancing plug.</t>
+        </is>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>inventory_cf_adjustment_difference</t>
+        </is>
+      </c>
+      <c r="Q575" t="n">
+        <v>151</v>
+      </c>
+      <c r="R575" t="n">
+        <v>1</v>
+      </c>
+      <c r="S575" t="inlineStr">
+        <is>
+          <t>2022-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>inventory_cf_adjustment_difference__20230831</t>
+        </is>
+      </c>
+      <c r="B576" t="n">
+        <v>575</v>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference = reported operating CF inventory adjustment − balance-implied adjustment. A nonzero difference needs further evidence; it does not establish an error, cash paid for inventory, FX, acquisitions, write-downs, or another specific cause. Do not insert a balancing plug.</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_cf_adjustment_difference.2023-08-31</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>D124</t>
+        </is>
+      </c>
+      <c r="I576">
+        <f>D122-D123</f>
+        <v/>
+      </c>
+      <c r="J576" t="n">
+        <v>10234</v>
+      </c>
+      <c r="K576" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L576" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment__20230831</t>
+        </is>
+      </c>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference = reported operating CF inventory adjustment − balance-implied adjustment.|A nonzero difference needs further evidence; it does not establish an error, cash paid for inventory, FX, acquisitions, write-downs, or another specific cause.|Do not insert a balancing plug.</t>
+        </is>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P576" t="inlineStr">
+        <is>
+          <t>inventory_cf_adjustment_difference</t>
+        </is>
+      </c>
+      <c r="Q576" t="n">
+        <v>151</v>
+      </c>
+      <c r="R576" t="n">
+        <v>2</v>
+      </c>
+      <c r="S576" t="inlineStr">
+        <is>
+          <t>2023-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>inventory_cf_adjustment_difference__20240831</t>
+        </is>
+      </c>
+      <c r="B577" t="n">
+        <v>576</v>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference = reported operating CF inventory adjustment − balance-implied adjustment. A nonzero difference needs further evidence; it does not establish an error, cash paid for inventory, FX, acquisitions, write-downs, or another specific cause. Do not insert a balancing plug.</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_cf_adjustment_difference.2024-08-31</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>E124</t>
+        </is>
+      </c>
+      <c r="I577">
+        <f>E122-E123</f>
+        <v/>
+      </c>
+      <c r="J577" t="n">
+        <v>1666</v>
+      </c>
+      <c r="K577" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L577" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment__20240831</t>
+        </is>
+      </c>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference = reported operating CF inventory adjustment − balance-implied adjustment.|A nonzero difference needs further evidence; it does not establish an error, cash paid for inventory, FX, acquisitions, write-downs, or another specific cause.|Do not insert a balancing plug.</t>
+        </is>
+      </c>
+      <c r="O577" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P577" t="inlineStr">
+        <is>
+          <t>inventory_cf_adjustment_difference</t>
+        </is>
+      </c>
+      <c r="Q577" t="n">
+        <v>151</v>
+      </c>
+      <c r="R577" t="n">
+        <v>3</v>
+      </c>
+      <c r="S577" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>inventory_cf_adjustment_difference__20250831</t>
+        </is>
+      </c>
+      <c r="B578" t="n">
+        <v>577</v>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference = reported operating CF inventory adjustment − balance-implied adjustment. A nonzero difference needs further evidence; it does not establish an error, cash paid for inventory, FX, acquisitions, write-downs, or another specific cause. Do not insert a balancing plug.</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>inventory_analysis.inventory_cf_adjustment_difference.2025-08-31</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>inventory_analysis</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>ALT DuPont</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>F124</t>
+        </is>
+      </c>
+      <c r="I578">
+        <f>F122-F123</f>
+        <v/>
+      </c>
+      <c r="J578" t="n">
+        <v>6643</v>
+      </c>
+      <c r="K578" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L578" t="inlineStr">
+        <is>
+          <t>inventory_balance_implied_cf_adjustment__20250831</t>
+        </is>
+      </c>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>Unexplained inventory CF difference = reported operating CF inventory adjustment − balance-implied adjustment.|A nonzero difference needs further evidence; it does not establish an error, cash paid for inventory, FX, acquisitions, write-downs, or another specific cause.|Do not insert a balancing plug.</t>
+        </is>
+      </c>
+      <c r="O578" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P578" t="inlineStr">
+        <is>
+          <t>inventory_cf_adjustment_difference</t>
+        </is>
+      </c>
+      <c r="Q578" t="n">
+        <v>151</v>
+      </c>
+      <c r="R578" t="n">
+        <v>4</v>
+      </c>
+      <c r="S578" t="inlineStr">
         <is>
           <t>2025-08-31</t>
         </is>
@@ -57947,7 +58695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F141"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -60504,434 +61252,426 @@
         <v/>
       </c>
     </row>
-    <row r="122"/>
+    <row r="122">
+      <c r="A122" s="11" t="inlineStr">
+        <is>
+          <t>Inventory CF adjustment (reported)</t>
+        </is>
+      </c>
+      <c r="B122" s="13">
+        <f>'Cash Flow Statement'!B7</f>
+        <v/>
+      </c>
+      <c r="C122" s="13">
+        <f>'Cash Flow Statement'!C7</f>
+        <v/>
+      </c>
+      <c r="D122" s="13">
+        <f>'Cash Flow Statement'!D7</f>
+        <v/>
+      </c>
+      <c r="E122" s="13">
+        <f>'Cash Flow Statement'!E7</f>
+        <v/>
+      </c>
+      <c r="F122" s="13">
+        <f>'Cash Flow Statement'!F7</f>
+        <v/>
+      </c>
+    </row>
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
-        </is>
+          <t>Balance-implied inventory CF adjustment</t>
+        </is>
+      </c>
+      <c r="C123" s="16">
+        <f>-C118</f>
+        <v/>
+      </c>
+      <c r="D123" s="16">
+        <f>-D118</f>
+        <v/>
+      </c>
+      <c r="E123" s="16">
+        <f>-E118</f>
+        <v/>
+      </c>
+      <c r="F123" s="16">
+        <f>-F118</f>
+        <v/>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t>Goodwill</t>
-        </is>
-      </c>
-      <c r="B124" s="13">
-        <f>'Balance Sheet'!B37</f>
-        <v/>
-      </c>
-      <c r="C124" s="13">
-        <f>'Balance Sheet'!C37</f>
-        <v/>
-      </c>
-      <c r="D124" s="13">
-        <f>'Balance Sheet'!D37</f>
-        <v/>
-      </c>
-      <c r="E124" s="13">
-        <f>'Balance Sheet'!E37</f>
-        <v/>
-      </c>
-      <c r="F124" s="13">
-        <f>'Balance Sheet'!F37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="11" t="inlineStr">
-        <is>
-          <t>Change in Goodwill</t>
-        </is>
-      </c>
-      <c r="C125" s="16">
-        <f>C124-B124</f>
-        <v/>
-      </c>
-      <c r="D125" s="16">
-        <f>D124-C124</f>
-        <v/>
-      </c>
-      <c r="E125" s="16">
-        <f>E124-D124</f>
-        <v/>
-      </c>
-      <c r="F125" s="16">
-        <f>F124-E124</f>
-        <v/>
-      </c>
-    </row>
+          <t>Unexplained inventory CF difference</t>
+        </is>
+      </c>
+      <c r="C124" s="16">
+        <f>C122-C123</f>
+        <v/>
+      </c>
+      <c r="D124" s="16">
+        <f>D122-D123</f>
+        <v/>
+      </c>
+      <c r="E124" s="16">
+        <f>E122-E123</f>
+        <v/>
+      </c>
+      <c r="F124" s="16">
+        <f>F122-F123</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125"/>
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t>Goodwill Growth</t>
-        </is>
-      </c>
-      <c r="C126" s="15">
-        <f>IF(B124=0,NA(),C124/B124-1)</f>
-        <v/>
-      </c>
-      <c r="D126" s="15">
-        <f>IF(C124=0,NA(),D124/C124-1)</f>
-        <v/>
-      </c>
-      <c r="E126" s="15">
-        <f>IF(D124=0,NA(),E124/D124-1)</f>
-        <v/>
-      </c>
-      <c r="F126" s="15">
-        <f>IF(E124=0,NA(),F124/E124-1)</f>
-        <v/>
+          <t>GOODWILL &amp; INTANGIBLES CONTEXT</t>
+        </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill</t>
-        </is>
-      </c>
-      <c r="C127" s="16">
-        <f>(B124+C124)/2</f>
-        <v/>
-      </c>
-      <c r="D127" s="16">
-        <f>(C124+D124)/2</f>
-        <v/>
-      </c>
-      <c r="E127" s="16">
-        <f>(D124+E124)/2</f>
-        <v/>
-      </c>
-      <c r="F127" s="16">
-        <f>(E124+F124)/2</f>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B127" s="13">
+        <f>'Balance Sheet'!B37</f>
+        <v/>
+      </c>
+      <c r="C127" s="13">
+        <f>'Balance Sheet'!C37</f>
+        <v/>
+      </c>
+      <c r="D127" s="13">
+        <f>'Balance Sheet'!D37</f>
+        <v/>
+      </c>
+      <c r="E127" s="13">
+        <f>'Balance Sheet'!E37</f>
+        <v/>
+      </c>
+      <c r="F127" s="13">
+        <f>'Balance Sheet'!F37</f>
         <v/>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill / Revenue</t>
-        </is>
-      </c>
-      <c r="C128" s="15">
-        <f>IF('Condensed Financials'!C44=0,NA(),C127/'Condensed Financials'!C44)</f>
-        <v/>
-      </c>
-      <c r="D128" s="15">
-        <f>IF('Condensed Financials'!D44=0,NA(),D127/'Condensed Financials'!D44)</f>
-        <v/>
-      </c>
-      <c r="E128" s="15">
-        <f>IF('Condensed Financials'!E44=0,NA(),E127/'Condensed Financials'!E44)</f>
-        <v/>
-      </c>
-      <c r="F128" s="15">
-        <f>IF('Condensed Financials'!F44=0,NA(),F127/'Condensed Financials'!F44)</f>
+          <t>Change in Goodwill</t>
+        </is>
+      </c>
+      <c r="C128" s="16">
+        <f>C127-B127</f>
+        <v/>
+      </c>
+      <c r="D128" s="16">
+        <f>D127-C127</f>
+        <v/>
+      </c>
+      <c r="E128" s="16">
+        <f>E127-D127</f>
+        <v/>
+      </c>
+      <c r="F128" s="16">
+        <f>F127-E127</f>
         <v/>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>Intangible Assets</t>
-        </is>
-      </c>
-      <c r="B129" s="13">
-        <f>'Balance Sheet'!B38</f>
-        <v/>
-      </c>
-      <c r="C129" s="13">
-        <f>'Balance Sheet'!C38</f>
-        <v/>
-      </c>
-      <c r="D129" s="13">
-        <f>'Balance Sheet'!D38</f>
-        <v/>
-      </c>
-      <c r="E129" s="13">
-        <f>'Balance Sheet'!E38</f>
-        <v/>
-      </c>
-      <c r="F129" s="13">
-        <f>'Balance Sheet'!F38</f>
+          <t>Goodwill Growth</t>
+        </is>
+      </c>
+      <c r="C129" s="15">
+        <f>IF(B127=0,NA(),C127/B127-1)</f>
+        <v/>
+      </c>
+      <c r="D129" s="15">
+        <f>IF(C127=0,NA(),D127/C127-1)</f>
+        <v/>
+      </c>
+      <c r="E129" s="15">
+        <f>IF(D127=0,NA(),E127/D127-1)</f>
+        <v/>
+      </c>
+      <c r="F129" s="15">
+        <f>IF(E127=0,NA(),F127/E127-1)</f>
         <v/>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="11" t="inlineStr">
         <is>
-          <t>Change in Intangible Assets</t>
+          <t>Average Goodwill</t>
         </is>
       </c>
       <c r="C130" s="16">
-        <f>C129-B129</f>
+        <f>(B127+C127)/2</f>
         <v/>
       </c>
       <c r="D130" s="16">
-        <f>D129-C129</f>
+        <f>(C127+D127)/2</f>
         <v/>
       </c>
       <c r="E130" s="16">
-        <f>E129-D129</f>
+        <f>(D127+E127)/2</f>
         <v/>
       </c>
       <c r="F130" s="16">
-        <f>F129-E129</f>
+        <f>(E127+F127)/2</f>
         <v/>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>Intangible Assets Growth</t>
+          <t>Average Goodwill / Revenue</t>
         </is>
       </c>
       <c r="C131" s="15">
-        <f>IF(B129=0,NA(),C129/B129-1)</f>
+        <f>IF('Condensed Financials'!C44=0,NA(),C130/'Condensed Financials'!C44)</f>
         <v/>
       </c>
       <c r="D131" s="15">
-        <f>IF(C129=0,NA(),D129/C129-1)</f>
+        <f>IF('Condensed Financials'!D44=0,NA(),D130/'Condensed Financials'!D44)</f>
         <v/>
       </c>
       <c r="E131" s="15">
-        <f>IF(D129=0,NA(),E129/D129-1)</f>
+        <f>IF('Condensed Financials'!E44=0,NA(),E130/'Condensed Financials'!E44)</f>
         <v/>
       </c>
       <c r="F131" s="15">
-        <f>IF(E129=0,NA(),F129/E129-1)</f>
+        <f>IF('Condensed Financials'!F44=0,NA(),F130/'Condensed Financials'!F44)</f>
         <v/>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t>Average Intangible Assets</t>
-        </is>
-      </c>
-      <c r="C132" s="16">
-        <f>(B129+C129)/2</f>
-        <v/>
-      </c>
-      <c r="D132" s="16">
-        <f>(C129+D129)/2</f>
-        <v/>
-      </c>
-      <c r="E132" s="16">
-        <f>(D129+E129)/2</f>
-        <v/>
-      </c>
-      <c r="F132" s="16">
-        <f>(E129+F129)/2</f>
+          <t>Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B132" s="13">
+        <f>'Balance Sheet'!B38</f>
+        <v/>
+      </c>
+      <c r="C132" s="13">
+        <f>'Balance Sheet'!C38</f>
+        <v/>
+      </c>
+      <c r="D132" s="13">
+        <f>'Balance Sheet'!D38</f>
+        <v/>
+      </c>
+      <c r="E132" s="13">
+        <f>'Balance Sheet'!E38</f>
+        <v/>
+      </c>
+      <c r="F132" s="13">
+        <f>'Balance Sheet'!F38</f>
         <v/>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>Average Intangible Assets / Revenue</t>
-        </is>
-      </c>
-      <c r="C133" s="15">
-        <f>IF('Condensed Financials'!C44=0,NA(),C132/'Condensed Financials'!C44)</f>
-        <v/>
-      </c>
-      <c r="D133" s="15">
-        <f>IF('Condensed Financials'!D44=0,NA(),D132/'Condensed Financials'!D44)</f>
-        <v/>
-      </c>
-      <c r="E133" s="15">
-        <f>IF('Condensed Financials'!E44=0,NA(),E132/'Condensed Financials'!E44)</f>
-        <v/>
-      </c>
-      <c r="F133" s="15">
-        <f>IF('Condensed Financials'!F44=0,NA(),F132/'Condensed Financials'!F44)</f>
+          <t>Change in Intangible Assets</t>
+        </is>
+      </c>
+      <c r="C133" s="16">
+        <f>C132-B132</f>
+        <v/>
+      </c>
+      <c r="D133" s="16">
+        <f>D132-C132</f>
+        <v/>
+      </c>
+      <c r="E133" s="16">
+        <f>E132-D132</f>
+        <v/>
+      </c>
+      <c r="F133" s="16">
+        <f>F132-E132</f>
         <v/>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="B134" s="13">
-        <f>B124+B129</f>
-        <v/>
-      </c>
-      <c r="C134" s="13">
-        <f>C124+C129</f>
-        <v/>
-      </c>
-      <c r="D134" s="13">
-        <f>D124+D129</f>
-        <v/>
-      </c>
-      <c r="E134" s="13">
-        <f>E124+E129</f>
-        <v/>
-      </c>
-      <c r="F134" s="13">
-        <f>F124+F129</f>
+          <t>Intangible Assets Growth</t>
+        </is>
+      </c>
+      <c r="C134" s="15">
+        <f>IF(B132=0,NA(),C132/B132-1)</f>
+        <v/>
+      </c>
+      <c r="D134" s="15">
+        <f>IF(C132=0,NA(),D132/C132-1)</f>
+        <v/>
+      </c>
+      <c r="E134" s="15">
+        <f>IF(D132=0,NA(),E132/D132-1)</f>
+        <v/>
+      </c>
+      <c r="F134" s="15">
+        <f>IF(E132=0,NA(),F132/E132-1)</f>
         <v/>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>Change in Goodwill &amp; Intangibles</t>
+          <t>Average Intangible Assets</t>
         </is>
       </c>
       <c r="C135" s="16">
-        <f>C134-B134</f>
+        <f>(B132+C132)/2</f>
         <v/>
       </c>
       <c r="D135" s="16">
-        <f>D134-C134</f>
+        <f>(C132+D132)/2</f>
         <v/>
       </c>
       <c r="E135" s="16">
-        <f>E134-D134</f>
+        <f>(D132+E132)/2</f>
         <v/>
       </c>
       <c r="F135" s="16">
-        <f>F134-E134</f>
+        <f>(E132+F132)/2</f>
         <v/>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="11" t="inlineStr">
         <is>
-          <t>Goodwill &amp; Intangibles Growth</t>
+          <t>Average Intangible Assets / Revenue</t>
         </is>
       </c>
       <c r="C136" s="15">
-        <f>IF(B134=0,NA(),C134/B134-1)</f>
+        <f>IF('Condensed Financials'!C44=0,NA(),C135/'Condensed Financials'!C44)</f>
         <v/>
       </c>
       <c r="D136" s="15">
-        <f>IF(C134=0,NA(),D134/C134-1)</f>
+        <f>IF('Condensed Financials'!D44=0,NA(),D135/'Condensed Financials'!D44)</f>
         <v/>
       </c>
       <c r="E136" s="15">
-        <f>IF(D134=0,NA(),E134/D134-1)</f>
+        <f>IF('Condensed Financials'!E44=0,NA(),E135/'Condensed Financials'!E44)</f>
         <v/>
       </c>
       <c r="F136" s="15">
-        <f>IF(E134=0,NA(),F134/E134-1)</f>
+        <f>IF('Condensed Financials'!F44=0,NA(),F135/'Condensed Financials'!F44)</f>
         <v/>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles</t>
-        </is>
-      </c>
-      <c r="C137" s="16">
-        <f>(B134+C134)/2</f>
-        <v/>
-      </c>
-      <c r="D137" s="16">
-        <f>(C134+D134)/2</f>
-        <v/>
-      </c>
-      <c r="E137" s="16">
-        <f>(D134+E134)/2</f>
-        <v/>
-      </c>
-      <c r="F137" s="16">
-        <f>(E134+F134)/2</f>
+          <t>Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="B137" s="13">
+        <f>B127+B132</f>
+        <v/>
+      </c>
+      <c r="C137" s="13">
+        <f>C127+C132</f>
+        <v/>
+      </c>
+      <c r="D137" s="13">
+        <f>D127+D132</f>
+        <v/>
+      </c>
+      <c r="E137" s="13">
+        <f>E127+E132</f>
+        <v/>
+      </c>
+      <c r="F137" s="13">
+        <f>F127+F132</f>
         <v/>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t>Average Goodwill &amp; Intangibles / Revenue</t>
-        </is>
-      </c>
-      <c r="C138" s="15">
-        <f>IF('Condensed Financials'!C44=0,NA(),C137/'Condensed Financials'!C44)</f>
-        <v/>
-      </c>
-      <c r="D138" s="15">
-        <f>IF('Condensed Financials'!D44=0,NA(),D137/'Condensed Financials'!D44)</f>
-        <v/>
-      </c>
-      <c r="E138" s="15">
-        <f>IF('Condensed Financials'!E44=0,NA(),E137/'Condensed Financials'!E44)</f>
-        <v/>
-      </c>
-      <c r="F138" s="15">
-        <f>IF('Condensed Financials'!F44=0,NA(),F137/'Condensed Financials'!F44)</f>
+          <t>Change in Goodwill &amp; Intangibles</t>
+        </is>
+      </c>
+      <c r="C138" s="16">
+        <f>C137-B137</f>
+        <v/>
+      </c>
+      <c r="D138" s="16">
+        <f>D137-C137</f>
+        <v/>
+      </c>
+      <c r="E138" s="16">
+        <f>E137-D137</f>
+        <v/>
+      </c>
+      <c r="F138" s="16">
+        <f>F137-E137</f>
         <v/>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>Payments for Intangible Assets (reported)</t>
-        </is>
-      </c>
-      <c r="B139" s="13">
-        <f>'Cash Flow Statement'!B38</f>
-        <v/>
-      </c>
-      <c r="C139" s="13">
-        <f>'Cash Flow Statement'!C38</f>
-        <v/>
-      </c>
-      <c r="D139" s="13">
-        <f>'Cash Flow Statement'!D38</f>
-        <v/>
-      </c>
-      <c r="E139" s="13">
-        <f>'Cash Flow Statement'!E38</f>
-        <v/>
-      </c>
-      <c r="F139" s="13">
-        <f>'Cash Flow Statement'!F38</f>
+          <t>Goodwill &amp; Intangibles Growth</t>
+        </is>
+      </c>
+      <c r="C139" s="15">
+        <f>IF(B137=0,NA(),C137/B137-1)</f>
+        <v/>
+      </c>
+      <c r="D139" s="15">
+        <f>IF(C137=0,NA(),D137/C137-1)</f>
+        <v/>
+      </c>
+      <c r="E139" s="15">
+        <f>IF(D137=0,NA(),E137/D137-1)</f>
+        <v/>
+      </c>
+      <c r="F139" s="15">
+        <f>IF(E137=0,NA(),F137/E137-1)</f>
         <v/>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t>Intangible Payments (−reported)</t>
-        </is>
-      </c>
-      <c r="B140" s="16">
-        <f>-B139</f>
-        <v/>
+          <t>Average Goodwill &amp; Intangibles</t>
+        </is>
       </c>
       <c r="C140" s="16">
-        <f>-C139</f>
+        <f>(B137+C137)/2</f>
         <v/>
       </c>
       <c r="D140" s="16">
-        <f>-D139</f>
+        <f>(C137+D137)/2</f>
         <v/>
       </c>
       <c r="E140" s="16">
-        <f>-E139</f>
+        <f>(D137+E137)/2</f>
         <v/>
       </c>
       <c r="F140" s="16">
-        <f>-F139</f>
+        <f>(E137+F137)/2</f>
         <v/>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>Intangible Payments / Revenue</t>
-        </is>
-      </c>
-      <c r="B141" s="15">
-        <f>IF('Condensed Financials'!B44=0,NA(),B140/'Condensed Financials'!B44)</f>
-        <v/>
+          <t>Average Goodwill &amp; Intangibles / Revenue</t>
+        </is>
       </c>
       <c r="C141" s="15">
         <f>IF('Condensed Financials'!C44=0,NA(),C140/'Condensed Financials'!C44)</f>
@@ -60947,6 +61687,87 @@
       </c>
       <c r="F141" s="15">
         <f>IF('Condensed Financials'!F44=0,NA(),F140/'Condensed Financials'!F44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="11" t="inlineStr">
+        <is>
+          <t>Payments for Intangible Assets (reported)</t>
+        </is>
+      </c>
+      <c r="B142" s="13">
+        <f>'Cash Flow Statement'!B38</f>
+        <v/>
+      </c>
+      <c r="C142" s="13">
+        <f>'Cash Flow Statement'!C38</f>
+        <v/>
+      </c>
+      <c r="D142" s="13">
+        <f>'Cash Flow Statement'!D38</f>
+        <v/>
+      </c>
+      <c r="E142" s="13">
+        <f>'Cash Flow Statement'!E38</f>
+        <v/>
+      </c>
+      <c r="F142" s="13">
+        <f>'Cash Flow Statement'!F38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="11" t="inlineStr">
+        <is>
+          <t>Intangible Payments (−reported)</t>
+        </is>
+      </c>
+      <c r="B143" s="16">
+        <f>-B142</f>
+        <v/>
+      </c>
+      <c r="C143" s="16">
+        <f>-C142</f>
+        <v/>
+      </c>
+      <c r="D143" s="16">
+        <f>-D142</f>
+        <v/>
+      </c>
+      <c r="E143" s="16">
+        <f>-E142</f>
+        <v/>
+      </c>
+      <c r="F143" s="16">
+        <f>-F142</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="11" t="inlineStr">
+        <is>
+          <t>Intangible Payments / Revenue</t>
+        </is>
+      </c>
+      <c r="B144" s="15">
+        <f>IF('Condensed Financials'!B44=0,NA(),B143/'Condensed Financials'!B44)</f>
+        <v/>
+      </c>
+      <c r="C144" s="15">
+        <f>IF('Condensed Financials'!C44=0,NA(),C143/'Condensed Financials'!C44)</f>
+        <v/>
+      </c>
+      <c r="D144" s="15">
+        <f>IF('Condensed Financials'!D44=0,NA(),D143/'Condensed Financials'!D44)</f>
+        <v/>
+      </c>
+      <c r="E144" s="15">
+        <f>IF('Condensed Financials'!E44=0,NA(),E143/'Condensed Financials'!E44)</f>
+        <v/>
+      </c>
+      <c r="F144" s="15">
+        <f>IF('Condensed Financials'!F44=0,NA(),F143/'Condensed Financials'!F44)</f>
         <v/>
       </c>
     </row>
